--- a/data/CS7/case9/case9_operational_data.xlsx
+++ b/data/CS7/case9/case9_operational_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case9\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case9/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B676F2BE-F5AC-4F1B-BAF8-8AECBE04EBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B67E7D-4B4B-734D-963C-F055D9A87923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="72375" yWindow="-11250" windowWidth="28800" windowHeight="15285" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -428,14 +428,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B7BE64-82AA-46B6-895E-9570C0781B75}">
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -449,223 +449,238 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2">
         <f>1/COUNT($A$2:$A$4)</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="1">
+        <v>90</v>
+      </c>
+      <c r="F2" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C3" s="1">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2">
         <f t="shared" ref="D3:D4" si="0">1/COUNT($A$2:$A$4)</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E3" s="1">
+        <v>100</v>
+      </c>
+      <c r="F3" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>62.5</v>
+        <v>125</v>
       </c>
       <c r="C4" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E4" s="1">
+        <v>125</v>
+      </c>
+      <c r="F4" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -680,12 +695,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97BA2E0A-46FB-4F4E-929C-1515BC129DD6}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -693,7 +708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -701,7 +716,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -709,10 +724,10 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
     </row>
   </sheetData>
@@ -723,9 +738,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31C2423-6FFC-4FCE-9489-228A5BC03001}">
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -808,7 +823,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -891,7 +906,7 @@
         <v>0.71336538190184817</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -974,7 +989,7 @@
         <v>0.61895037144583387</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1057,7 +1072,7 @@
         <v>0.74627823226991585</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1140,7 +1155,7 @@
         <v>0.7418999971779221</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1223,7 +1238,7 @@
         <v>0.64370838630366722</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1306,7 +1321,7 @@
         <v>0.77612936156071255</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1389,7 +1404,7 @@
         <v>0.70623172808282964</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1472,7 +1487,7 @@
         <v>0.6127608677313755</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1555,7 +1570,7 @@
         <v>0.73881544994721671</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1638,7 +1653,7 @@
         <v>0.74380357951225773</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1721,7 +1736,7 @@
         <v>0.64817076786567862</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>3</v>
       </c>
@@ -1804,7 +1819,7 @@
         <v>0.76492957272776008</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1</v>
       </c>
@@ -1887,7 +1902,7 @@
         <v>0.7444877685445167</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1970,7 +1985,7 @@
         <v>0.67420176057307402</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>3</v>
       </c>
@@ -2053,7 +2068,7 @@
         <v>0.76468472768925289</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1</v>
       </c>
@@ -2136,7 +2151,7 @@
         <v>0.74380357951225773</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2219,7 +2234,7 @@
         <v>0.65434396419981855</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
@@ -2302,7 +2317,7 @@
         <v>0.76308381762969679</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1</v>
       </c>
@@ -2385,7 +2400,7 @@
         <v>0.81985192260537454</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2468,7 +2483,7 @@
         <v>0.75558893286054651</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2551,7 +2566,7 @@
         <v>0.84122471818794531</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1</v>
       </c>
@@ -2634,7 +2649,7 @@
         <v>0.85264599950958953</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2</v>
       </c>
@@ -2717,7 +2732,7 @@
         <v>0.78581249017496835</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2800,7 +2815,7 @@
         <v>0.87487370691546318</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1</v>
       </c>
@@ -2883,7 +2898,7 @@
         <v>0.78705784570115955</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2</v>
       </c>
@@ -2966,7 +2981,7 @@
         <v>0.72536537554612468</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>3</v>
       </c>
@@ -3049,7 +3064,7 @@
         <v>0.80757572946042744</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1</v>
       </c>
@@ -3132,7 +3147,7 @@
         <v>0.73455903672620337</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2</v>
       </c>
@@ -3215,7 +3230,7 @@
         <v>0.66756108454883456</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>3</v>
       </c>
@@ -3298,7 +3313,7 @@
         <v>0.73497587599716452</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1</v>
       </c>
@@ -3381,7 +3396,7 @@
         <v>0.74176847450035721</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2</v>
       </c>
@@ -3464,7 +3479,7 @@
         <v>0.68305071689761454</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>3</v>
       </c>
@@ -3547,7 +3562,7 @@
         <v>0.73854976944591411</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1</v>
       </c>
@@ -3630,7 +3645,7 @@
         <v>0.68727082640817161</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2</v>
       </c>
@@ -3713,7 +3728,7 @@
         <v>0.61080046884544648</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>3</v>
       </c>
@@ -3804,9 +3819,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08205B29-B07B-4A1C-AC27-1D2057748C52}">
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -3889,7 +3904,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3972,7 +3987,7 @@
         <v>-0.72089207574330627</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4055,7 +4070,7 @@
         <v>0.74305111538796631</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4138,7 +4153,7 @@
         <v>0.49864852901755596</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4221,7 +4236,7 @@
         <v>-0.72089207574330627</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -4304,7 +4319,7 @@
         <v>0.74305111538796631</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -4387,7 +4402,7 @@
         <v>0.49864852901755596</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4470,7 +4485,7 @@
         <v>-0.69926531347100707</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -4553,7 +4568,7 @@
         <v>0.72075958192632728</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -4636,7 +4651,7 @@
         <v>0.48368907314702925</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
@@ -4719,7 +4734,7 @@
         <v>-0.4974490169571783</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
@@ -4802,7 +4817,7 @@
         <v>-0.18197839062806498</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>3</v>
       </c>
@@ -4885,7 +4900,7 @@
         <v>0.55113061727758028</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1</v>
       </c>
@@ -4968,7 +4983,7 @@
         <v>-0.55943805073227393</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5051,7 +5066,7 @@
         <v>-0.12591343054236132</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>3</v>
       </c>
@@ -5134,7 +5149,7 @@
         <v>0.57993998822592141</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1</v>
       </c>
@@ -5217,7 +5232,7 @@
         <v>-0.52214218068345564</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
@@ -5300,7 +5315,7 @@
         <v>-0.11593970683744471</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
@@ -5383,7 +5398,7 @@
         <v>0.5029774223110125</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1</v>
       </c>
@@ -5466,7 +5481,7 @@
         <v>-0.42122634657099428</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5549,7 +5564,7 @@
         <v>-0.76398900925398083</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
@@ -5632,7 +5647,7 @@
         <v>0.59808028175264938</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1</v>
       </c>
@@ -5715,7 +5730,7 @@
         <v>-0.42122634657099428</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2</v>
       </c>
@@ -5798,7 +5813,7 @@
         <v>-0.76398900925398083</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
@@ -5881,7 +5896,7 @@
         <v>0.59808028175264938</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1</v>
       </c>
@@ -5964,7 +5979,7 @@
         <v>-0.40437729270815448</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2</v>
       </c>
@@ -6047,7 +6062,7 @@
         <v>-0.73342944888382156</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>3</v>
       </c>
@@ -6130,7 +6145,7 @@
         <v>0.57415707048254339</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1</v>
       </c>
@@ -6213,7 +6228,7 @@
         <v>-0.56906341150687867</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2</v>
       </c>
@@ -6296,7 +6311,7 @@
         <v>0.12901626028869245</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>3</v>
       </c>
@@ -6379,7 +6394,7 @@
         <v>0.49235564052856051</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1</v>
       </c>
@@ -6462,7 +6477,7 @@
         <v>-0.61132769626185945</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2</v>
       </c>
@@ -6545,7 +6560,7 @@
         <v>0.12393203751053562</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>3</v>
       </c>
@@ -6628,7 +6643,7 @@
         <v>0.5064776052327925</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1</v>
       </c>
@@ -6711,7 +6726,7 @@
         <v>-0.57833496290942632</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2</v>
       </c>
@@ -6794,7 +6809,7 @@
         <v>0.1344189912504711</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>3</v>
       </c>
@@ -6885,9 +6900,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA03F9D-90DB-4249-93C0-9667E84EEC95}">
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -6970,7 +6985,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -7053,7 +7068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -7136,7 +7151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -7219,7 +7234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -7302,7 +7317,7 @@
         <v>0.5335206744279406</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -7385,7 +7400,7 @@
         <v>0.49739060618225611</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -7468,7 +7483,7 @@
         <v>0.40405459654757125</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -7551,7 +7566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -7634,7 +7649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -7717,7 +7732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -7800,7 +7815,7 @@
         <v>0.36852669610598154</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -7883,7 +7898,7 @@
         <v>0.23966278602970695</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -7966,7 +7981,7 @@
         <v>0.30931352870333201</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -8049,7 +8064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -8132,7 +8147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -8215,7 +8230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -8298,7 +8313,7 @@
         <v>0.4676836611802489</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -8381,7 +8396,7 @@
         <v>0.17442794058611</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -8464,7 +8479,7 @@
         <v>0.34263348052990766</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -8547,7 +8562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -8630,7 +8645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -8713,7 +8728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -8796,7 +8811,7 @@
         <v>0.44439983942191891</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -8879,7 +8894,7 @@
         <v>0.50040144520272978</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -8970,9 +8985,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA6B18B-4184-4364-B108-C86EC3A3FBA5}">
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -9055,7 +9070,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -9138,7 +9153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9221,7 +9236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -9304,7 +9319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -9387,7 +9402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -9470,7 +9485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -9553,7 +9568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -9636,7 +9651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -9719,7 +9734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -9802,7 +9817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -9885,7 +9900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -9968,7 +9983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -10051,7 +10066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -10134,7 +10149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -10217,7 +10232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -10300,7 +10315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -10383,7 +10398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -10466,7 +10481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -10549,7 +10564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -10632,7 +10647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -10715,7 +10730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -10798,7 +10813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -10881,7 +10896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -10964,7 +10979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -11055,14 +11070,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A692A72-59FD-4423-ADC4-03B36872E462}">
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -11145,7 +11160,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -11156,79 +11171,79 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>4.9164000000000003</v>
+        <v>16.388000000000002</v>
       </c>
       <c r="E2" s="1">
-        <v>5.0804</v>
+        <v>16.934666666666669</v>
       </c>
       <c r="F2" s="1">
-        <v>4.5491999999999999</v>
+        <v>15.164</v>
       </c>
       <c r="G2" s="1">
-        <v>4.3120000000000003</v>
+        <v>14.373333333333335</v>
       </c>
       <c r="H2" s="1">
-        <v>3.5327999999999999</v>
+        <v>11.776000000000002</v>
       </c>
       <c r="I2" s="1">
-        <v>2.9984000000000002</v>
+        <v>9.9946666666666673</v>
       </c>
       <c r="J2" s="1">
-        <v>3.6667999999999998</v>
+        <v>12.222666666666667</v>
       </c>
       <c r="K2" s="1">
-        <v>0.63680000000000003</v>
+        <v>2.1226666666666669</v>
       </c>
       <c r="L2" s="1">
-        <v>0.56000000000000005</v>
+        <v>1.8666666666666669</v>
       </c>
       <c r="M2" s="1">
-        <v>0.81640000000000001</v>
+        <v>2.7213333333333334</v>
       </c>
       <c r="N2" s="1">
-        <v>0.48080000000000001</v>
+        <v>1.6026666666666667</v>
       </c>
       <c r="O2" s="1">
-        <v>0.6008</v>
+        <v>2.0026666666666668</v>
       </c>
       <c r="P2" s="1">
-        <v>0.95720000000000005</v>
+        <v>3.190666666666667</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.7636000000000001</v>
+        <v>5.8786666666666667</v>
       </c>
       <c r="R2" s="1">
-        <v>1.8815999999999999</v>
+        <v>6.2719999999999994</v>
       </c>
       <c r="S2" s="1">
-        <v>1.8504</v>
+        <v>6.1680000000000001</v>
       </c>
       <c r="T2" s="1">
-        <v>1.038</v>
+        <v>3.4600000000000004</v>
       </c>
       <c r="U2" s="1">
-        <v>2.1143999999999998</v>
+        <v>7.0479999999999992</v>
       </c>
       <c r="V2" s="1">
-        <v>1.2407999999999999</v>
+        <v>4.1360000000000001</v>
       </c>
       <c r="W2" s="1">
-        <v>0.87239999999999995</v>
+        <v>2.9079999999999999</v>
       </c>
       <c r="X2" s="1">
-        <v>1.3248</v>
+        <v>4.4159999999999995</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.81879999999999997</v>
+        <v>2.7293333333333329</v>
       </c>
       <c r="Z2" s="1">
-        <v>3.7372000000000001</v>
+        <v>12.457333333333333</v>
       </c>
       <c r="AA2" s="1">
-        <v>4.5052000000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+        <v>15.017333333333335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -11239,79 +11254,79 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-11.1</v>
+        <v>-37</v>
       </c>
       <c r="E3" s="1">
-        <v>-11.8696</v>
+        <v>-39.565333333333335</v>
       </c>
       <c r="F3" s="1">
-        <v>-13.349600000000001</v>
+        <v>-44.498666666666672</v>
       </c>
       <c r="G3" s="1">
-        <v>-14.400399999999999</v>
+        <v>-48.001333333333328</v>
       </c>
       <c r="H3" s="1">
-        <v>-15.391999999999999</v>
+        <v>-51.306666666666665</v>
       </c>
       <c r="I3" s="1">
-        <v>-16.797999999999998</v>
+        <v>-55.993333333333332</v>
       </c>
       <c r="J3" s="1">
-        <v>-16.028400000000001</v>
+        <v>-53.428000000000004</v>
       </c>
       <c r="K3" s="1">
-        <v>-17.979759999999999</v>
+        <v>-59.932533333333332</v>
       </c>
       <c r="L3" s="1">
-        <v>-16.307359999999999</v>
+        <v>-54.357866666666666</v>
       </c>
       <c r="M3" s="1">
-        <v>-23.952839999999998</v>
+        <v>-79.842799999999997</v>
       </c>
       <c r="N3" s="1">
-        <v>-23.707360000000001</v>
+        <v>-79.024533333333338</v>
       </c>
       <c r="O3" s="1">
-        <v>-21.672160000000002</v>
+        <v>-72.240533333333346</v>
       </c>
       <c r="P3" s="1">
-        <v>-20.774560000000001</v>
+        <v>-69.248533333333341</v>
       </c>
       <c r="Q3" s="1">
-        <v>-20.057480000000002</v>
+        <v>-66.858266666666665</v>
       </c>
       <c r="R3" s="1">
-        <v>-18.90568</v>
+        <v>-63.018933333333337</v>
       </c>
       <c r="S3" s="1">
-        <v>-17.204239999999999</v>
+        <v>-57.347466666666662</v>
       </c>
       <c r="T3" s="1">
-        <v>-16.086960000000001</v>
+        <v>-53.623200000000004</v>
       </c>
       <c r="U3" s="1">
-        <v>-14.396240000000001</v>
+        <v>-47.98746666666667</v>
       </c>
       <c r="V3" s="1">
-        <v>-9.1377199999999998</v>
+        <v>-30.459066666666669</v>
       </c>
       <c r="W3" s="1">
-        <v>-10.22648</v>
+        <v>-34.088266666666669</v>
       </c>
       <c r="X3" s="1">
-        <v>-10.809839999999999</v>
+        <v>-36.032800000000002</v>
       </c>
       <c r="Y3" s="1">
-        <v>-11.605399999999999</v>
+        <v>-38.684666666666665</v>
       </c>
       <c r="Z3" s="1">
-        <v>-9.2203999999999997</v>
+        <v>-30.734666666666666</v>
       </c>
       <c r="AA3" s="1">
-        <v>-9.7975999999999992</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-32.658666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -11322,79 +11337,79 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>10.69356</v>
+        <v>35.645199999999996</v>
       </c>
       <c r="E4" s="1">
-        <v>11.44032</v>
+        <v>38.134399999999999</v>
       </c>
       <c r="F4" s="1">
-        <v>12.82724</v>
+        <v>42.757466666666666</v>
       </c>
       <c r="G4" s="1">
-        <v>13.802440000000001</v>
+        <v>46.00813333333334</v>
       </c>
       <c r="H4" s="1">
-        <v>14.6914</v>
+        <v>48.971333333333327</v>
       </c>
       <c r="I4" s="1">
-        <v>16.042000000000002</v>
+        <v>53.473333333333336</v>
       </c>
       <c r="J4" s="1">
-        <v>15.294</v>
+        <v>50.98</v>
       </c>
       <c r="K4" s="1">
-        <v>17.259160000000001</v>
+        <v>57.530533333333345</v>
       </c>
       <c r="L4" s="1">
-        <v>15.80916</v>
+        <v>52.697200000000002</v>
       </c>
       <c r="M4" s="1">
-        <v>18.039439999999999</v>
+        <v>60.131466666666661</v>
       </c>
       <c r="N4" s="1">
-        <v>18.181480000000001</v>
+        <v>60.604933333333328</v>
       </c>
       <c r="O4" s="1">
-        <v>17.019639999999999</v>
+        <v>56.73213333333333</v>
       </c>
       <c r="P4" s="1">
-        <v>16.446000000000002</v>
+        <v>54.82</v>
       </c>
       <c r="Q4" s="1">
-        <v>16.02328</v>
+        <v>53.410933333333332</v>
       </c>
       <c r="R4" s="1">
-        <v>15.01632</v>
+        <v>50.054400000000008</v>
       </c>
       <c r="S4" s="1">
-        <v>13.671480000000001</v>
+        <v>45.571599999999997</v>
       </c>
       <c r="T4" s="1">
-        <v>12.736039999999999</v>
+        <v>42.453466666666664</v>
       </c>
       <c r="U4" s="1">
-        <v>11.38288</v>
+        <v>37.942933333333336</v>
       </c>
       <c r="V4" s="1">
-        <v>8.9093599999999995</v>
+        <v>29.697866666666666</v>
       </c>
       <c r="W4" s="1">
-        <v>9.9721600000000006</v>
+        <v>33.240533333333339</v>
       </c>
       <c r="X4" s="1">
-        <v>10.59656</v>
+        <v>35.321866666666665</v>
       </c>
       <c r="Y4" s="1">
-        <v>11.41456</v>
+        <v>38.048533333333332</v>
       </c>
       <c r="Z4" s="1">
-        <v>8.8819999999999997</v>
+        <v>29.606666666666666</v>
       </c>
       <c r="AA4" s="1">
-        <v>9.4448000000000008</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+        <v>31.48266666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -11405,79 +11420,79 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>4.9655640000000005</v>
+        <v>16.551880000000001</v>
       </c>
       <c r="E5" s="1">
-        <v>4.9787920000000003</v>
+        <v>16.595973333333333</v>
       </c>
       <c r="F5" s="1">
-        <v>4.5037079999999996</v>
+        <v>15.012359999999999</v>
       </c>
       <c r="G5" s="1">
-        <v>4.4413600000000004</v>
+        <v>14.804533333333334</v>
       </c>
       <c r="H5" s="1">
-        <v>3.4974720000000001</v>
+        <v>11.658240000000001</v>
       </c>
       <c r="I5" s="1">
-        <v>2.9684160000000004</v>
+        <v>9.8947200000000013</v>
       </c>
       <c r="J5" s="1">
-        <v>3.7034679999999995</v>
+        <v>12.344893333333331</v>
       </c>
       <c r="K5" s="1">
-        <v>0.6304320000000001</v>
+        <v>2.1014400000000002</v>
       </c>
       <c r="L5" s="1">
-        <v>0.57680000000000009</v>
+        <v>1.922666666666667</v>
       </c>
       <c r="M5" s="1">
-        <v>0.82456400000000007</v>
+        <v>2.7485466666666674</v>
       </c>
       <c r="N5" s="1">
-        <v>0.46156800000000003</v>
+        <v>1.5385600000000001</v>
       </c>
       <c r="O5" s="1">
-        <v>0.61281600000000003</v>
+        <v>2.0427200000000001</v>
       </c>
       <c r="P5" s="1">
-        <v>0.90934000000000015</v>
+        <v>3.0311333333333335</v>
       </c>
       <c r="Q5" s="1">
-        <v>1.6930559999999999</v>
+        <v>5.6435199999999996</v>
       </c>
       <c r="R5" s="1">
-        <v>1.9568639999999999</v>
+        <v>6.5228799999999998</v>
       </c>
       <c r="S5" s="1">
-        <v>1.8318960000000002</v>
+        <v>6.1063200000000002</v>
       </c>
       <c r="T5" s="1">
-        <v>1.0587600000000001</v>
+        <v>3.5292000000000008</v>
       </c>
       <c r="U5" s="1">
-        <v>2.0509679999999997</v>
+        <v>6.8365599999999986</v>
       </c>
       <c r="V5" s="1">
-        <v>1.2159839999999997</v>
+        <v>4.0532799999999991</v>
       </c>
       <c r="W5" s="1">
-        <v>0.88112399999999991</v>
+        <v>2.9370799999999999</v>
       </c>
       <c r="X5" s="1">
-        <v>1.2983039999999999</v>
+        <v>4.32768</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.81879999999999997</v>
+        <v>2.7293333333333329</v>
       </c>
       <c r="Z5" s="1">
-        <v>3.6250839999999998</v>
+        <v>12.083613333333332</v>
       </c>
       <c r="AA5" s="1">
-        <v>4.3249919999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+        <v>14.416640000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -11488,79 +11503,79 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-11.654999999999999</v>
+        <v>-38.85</v>
       </c>
       <c r="E6" s="1">
-        <v>-11.8696</v>
+        <v>-39.565333333333335</v>
       </c>
       <c r="F6" s="1">
-        <v>-13.483096</v>
+        <v>-44.943653333333337</v>
       </c>
       <c r="G6" s="1">
-        <v>-14.544404</v>
+        <v>-48.481346666666667</v>
       </c>
       <c r="H6" s="1">
-        <v>-15.69984</v>
+        <v>-52.332799999999999</v>
       </c>
       <c r="I6" s="1">
-        <v>-17.133959999999998</v>
+        <v>-57.113199999999999</v>
       </c>
       <c r="J6" s="1">
-        <v>-16.348968000000003</v>
+        <v>-54.496560000000009</v>
       </c>
       <c r="K6" s="1">
-        <v>-18.698950399999998</v>
+        <v>-62.329834666666663</v>
       </c>
       <c r="L6" s="1">
-        <v>-15.491992</v>
+        <v>-51.63997333333333</v>
       </c>
       <c r="M6" s="1">
-        <v>-22.755198</v>
+        <v>-75.850660000000005</v>
       </c>
       <c r="N6" s="1">
-        <v>-23.707360000000005</v>
+        <v>-79.024533333333352</v>
       </c>
       <c r="O6" s="1">
-        <v>-20.588552</v>
+        <v>-68.628506666666667</v>
       </c>
       <c r="P6" s="1">
-        <v>-20.359068799999999</v>
+        <v>-67.863562666666667</v>
       </c>
       <c r="Q6" s="1">
-        <v>-19.255180800000002</v>
+        <v>-64.183936000000003</v>
       </c>
       <c r="R6" s="1">
-        <v>-19.661907200000002</v>
+        <v>-65.539690666666672</v>
       </c>
       <c r="S6" s="1">
-        <v>-17.5483248</v>
+        <v>-58.494416000000001</v>
       </c>
       <c r="T6" s="1">
-        <v>-16.891308000000002</v>
+        <v>-56.30436000000001</v>
       </c>
       <c r="U6" s="1">
-        <v>-14.972089600000002</v>
+        <v>-49.906965333333339</v>
       </c>
       <c r="V6" s="1">
-        <v>-8.8635883999999994</v>
+        <v>-29.545294666666663</v>
       </c>
       <c r="W6" s="1">
-        <v>-9.9196856000000011</v>
+        <v>-33.065618666666673</v>
       </c>
       <c r="X6" s="1">
-        <v>-10.593643199999999</v>
+        <v>-35.312143999999996</v>
       </c>
       <c r="Y6" s="1">
-        <v>-11.721454</v>
+        <v>-39.071513333333336</v>
       </c>
       <c r="Z6" s="1">
-        <v>-9.5892160000000004</v>
+        <v>-31.964053333333336</v>
       </c>
       <c r="AA6" s="1">
-        <v>-10.189503999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-33.965013333333332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -11571,79 +11586,79 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>10.3727532</v>
+        <v>34.575843999999996</v>
       </c>
       <c r="E7" s="1">
-        <v>11.8979328</v>
+        <v>39.659776000000001</v>
       </c>
       <c r="F7" s="1">
-        <v>13.3403296</v>
+        <v>44.46776533333334</v>
       </c>
       <c r="G7" s="1">
-        <v>13.940464400000002</v>
+        <v>46.468214666666675</v>
       </c>
       <c r="H7" s="1">
-        <v>14.250658000000001</v>
+        <v>47.502193333333338</v>
       </c>
       <c r="I7" s="1">
-        <v>16.683680000000003</v>
+        <v>55.612266666666677</v>
       </c>
       <c r="J7" s="1">
-        <v>15.905760000000001</v>
+        <v>53.019200000000005</v>
       </c>
       <c r="K7" s="1">
-        <v>16.396202000000002</v>
+        <v>54.654006666666675</v>
       </c>
       <c r="L7" s="1">
-        <v>15.018702000000001</v>
+        <v>50.062340000000006</v>
       </c>
       <c r="M7" s="1">
-        <v>17.678651200000001</v>
+        <v>58.928837333333341</v>
       </c>
       <c r="N7" s="1">
-        <v>18.908739199999999</v>
+        <v>63.029130666666667</v>
       </c>
       <c r="O7" s="1">
-        <v>17.189836400000001</v>
+        <v>57.299454666666669</v>
       </c>
       <c r="P7" s="1">
-        <v>15.788160000000003</v>
+        <v>52.627200000000009</v>
       </c>
       <c r="Q7" s="1">
-        <v>16.503978400000001</v>
+        <v>55.013261333333332</v>
       </c>
       <c r="R7" s="1">
-        <v>14.715993599999999</v>
+        <v>49.053311999999998</v>
       </c>
       <c r="S7" s="1">
-        <v>13.261335600000001</v>
+        <v>44.204452000000003</v>
       </c>
       <c r="T7" s="1">
-        <v>13.118121199999997</v>
+        <v>43.727070666666656</v>
       </c>
       <c r="U7" s="1">
-        <v>11.838195199999999</v>
+        <v>39.460650666666666</v>
       </c>
       <c r="V7" s="1">
-        <v>9.0875471999999995</v>
+        <v>30.291824000000002</v>
       </c>
       <c r="W7" s="1">
-        <v>9.6729952000000008</v>
+        <v>32.243317333333337</v>
       </c>
       <c r="X7" s="1">
-        <v>10.808491200000001</v>
+        <v>36.028303999999999</v>
       </c>
       <c r="Y7" s="1">
-        <v>10.9579776</v>
+        <v>36.526592000000001</v>
       </c>
       <c r="Z7" s="1">
-        <v>8.7931799999999996</v>
+        <v>29.310599999999997</v>
       </c>
       <c r="AA7" s="1">
-        <v>9.255904000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+        <v>30.853013333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -11654,79 +11669,79 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>5.164186560000001</v>
+        <v>17.213955200000004</v>
       </c>
       <c r="E8" s="1">
-        <v>5.0783678400000003</v>
+        <v>16.927892799999999</v>
       </c>
       <c r="F8" s="1">
-        <v>4.5937821599999999</v>
+        <v>15.3126072</v>
       </c>
       <c r="G8" s="1">
-        <v>4.5746008000000007</v>
+        <v>15.248669333333334</v>
       </c>
       <c r="H8" s="1">
-        <v>3.46249728</v>
+        <v>11.541657600000001</v>
       </c>
       <c r="I8" s="1">
-        <v>2.8199952000000001</v>
+        <v>9.3999840000000017</v>
       </c>
       <c r="J8" s="1">
-        <v>3.8516067199999999</v>
+        <v>12.838689066666667</v>
       </c>
       <c r="K8" s="1">
-        <v>0.60521472000000009</v>
+        <v>2.0173824000000002</v>
       </c>
       <c r="L8" s="1">
-        <v>0.60564000000000007</v>
+        <v>2.0188000000000001</v>
       </c>
       <c r="M8" s="1">
-        <v>0.79158144000000008</v>
+        <v>2.6386048</v>
       </c>
       <c r="N8" s="1">
-        <v>0.45233664000000007</v>
+        <v>1.5077888000000002</v>
       </c>
       <c r="O8" s="1">
-        <v>0.63120048000000006</v>
+        <v>2.1040016000000001</v>
       </c>
       <c r="P8" s="1">
-        <v>0.88205980000000006</v>
+        <v>2.9401993333333336</v>
       </c>
       <c r="Q8" s="1">
-        <v>1.7099865599999999</v>
+        <v>5.6999552000000007</v>
       </c>
       <c r="R8" s="1">
-        <v>2.03513856</v>
+        <v>6.7837952000000001</v>
       </c>
       <c r="S8" s="1">
-        <v>1.7952580800000002</v>
+        <v>5.9841936000000011</v>
       </c>
       <c r="T8" s="1">
-        <v>1.0375848000000003</v>
+        <v>3.458616000000001</v>
       </c>
       <c r="U8" s="1">
-        <v>2.0509679999999997</v>
+        <v>6.8365599999999986</v>
       </c>
       <c r="V8" s="1">
-        <v>1.2646233599999996</v>
+        <v>4.2154111999999992</v>
       </c>
       <c r="W8" s="1">
-        <v>0.88112399999999991</v>
+        <v>2.9370799999999999</v>
       </c>
       <c r="X8" s="1">
-        <v>1.27233792</v>
+        <v>4.2411263999999997</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.81879999999999997</v>
+        <v>2.7293333333333329</v>
       </c>
       <c r="Z8" s="1">
-        <v>3.6975856799999995</v>
+        <v>12.325285599999999</v>
       </c>
       <c r="AA8" s="1">
-        <v>4.4114918400000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+        <v>14.7049728</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -11737,79 +11752,79 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-12.237749999999998</v>
+        <v>-40.792499999999997</v>
       </c>
       <c r="E9" s="1">
-        <v>-11.394816</v>
+        <v>-37.98272</v>
       </c>
       <c r="F9" s="1">
-        <v>-13.61792696</v>
+        <v>-45.393089866666664</v>
       </c>
       <c r="G9" s="1">
-        <v>-14.835292079999999</v>
+        <v>-49.450973599999998</v>
       </c>
       <c r="H9" s="1">
-        <v>-15.228844799999999</v>
+        <v>-50.762815999999994</v>
       </c>
       <c r="I9" s="1">
-        <v>-16.448601599999996</v>
+        <v>-54.828671999999983</v>
       </c>
       <c r="J9" s="1">
-        <v>-17.166416400000003</v>
+        <v>-57.221388000000012</v>
       </c>
       <c r="K9" s="1">
-        <v>-17.950992383999996</v>
+        <v>-59.836641279999981</v>
       </c>
       <c r="L9" s="1">
-        <v>-15.646911920000001</v>
+        <v>-52.156373066666674</v>
       </c>
       <c r="M9" s="1">
-        <v>-21.844990079999999</v>
+        <v>-72.816633600000003</v>
       </c>
       <c r="N9" s="1">
-        <v>-24.181507200000006</v>
+        <v>-80.605024000000014</v>
       </c>
       <c r="O9" s="1">
-        <v>-19.559124400000002</v>
+        <v>-65.197081333333344</v>
       </c>
       <c r="P9" s="1">
-        <v>-21.173431551999997</v>
+        <v>-70.578105173333327</v>
       </c>
       <c r="Q9" s="1">
-        <v>-19.447732608000003</v>
+        <v>-64.825775360000009</v>
       </c>
       <c r="R9" s="1">
-        <v>-20.055145344000003</v>
+        <v>-66.85048448000002</v>
       </c>
       <c r="S9" s="1">
-        <v>-17.372841552000001</v>
+        <v>-57.909471840000002</v>
       </c>
       <c r="T9" s="1">
-        <v>-16.553481840000003</v>
+        <v>-55.178272800000009</v>
       </c>
       <c r="U9" s="1">
-        <v>-15.121810496000002</v>
+        <v>-50.406034986666668</v>
       </c>
       <c r="V9" s="1">
-        <v>-9.2181319359999989</v>
+        <v>-30.727106453333331</v>
       </c>
       <c r="W9" s="1">
-        <v>-10.217276168000001</v>
+        <v>-34.057587226666669</v>
       </c>
       <c r="X9" s="1">
-        <v>-10.063961039999999</v>
+        <v>-33.546536799999991</v>
       </c>
       <c r="Y9" s="1">
-        <v>-12.190312159999998</v>
+        <v>-40.634373866666657</v>
       </c>
       <c r="Z9" s="1">
-        <v>-9.4933238400000004</v>
+        <v>-31.644412800000001</v>
       </c>
       <c r="AA9" s="1">
-        <v>-9.9857139200000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-33.285713066666666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -11820,79 +11835,79 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>9.9578430720000011</v>
+        <v>33.192810240000007</v>
       </c>
       <c r="E10" s="1">
-        <v>11.778953472000001</v>
+        <v>39.263178240000002</v>
       </c>
       <c r="F10" s="1">
-        <v>13.473732896000001</v>
+        <v>44.912442986666669</v>
       </c>
       <c r="G10" s="1">
-        <v>14.079869044000002</v>
+        <v>46.932896813333343</v>
       </c>
       <c r="H10" s="1">
-        <v>14.108151420000002</v>
+        <v>47.027171400000007</v>
       </c>
       <c r="I10" s="1">
-        <v>16.016332800000001</v>
+        <v>53.387776000000002</v>
       </c>
       <c r="J10" s="1">
-        <v>16.5419904</v>
+        <v>55.139968000000003</v>
       </c>
       <c r="K10" s="1">
-        <v>15.904315940000002</v>
+        <v>53.014386466666672</v>
       </c>
       <c r="L10" s="1">
-        <v>15.319076040000002</v>
+        <v>51.063586800000003</v>
       </c>
       <c r="M10" s="1">
-        <v>17.678651200000001</v>
+        <v>58.928837333333341</v>
       </c>
       <c r="N10" s="1">
-        <v>19.286913984000002</v>
+        <v>64.289713280000001</v>
       </c>
       <c r="O10" s="1">
-        <v>17.877429856000003</v>
+        <v>59.591432853333345</v>
       </c>
       <c r="P10" s="1">
-        <v>16.577568000000003</v>
+        <v>55.25856000000001</v>
       </c>
       <c r="Q10" s="1">
-        <v>16.999097752000001</v>
+        <v>56.663659173333336</v>
       </c>
       <c r="R10" s="1">
-        <v>13.98019392</v>
+        <v>46.600646399999995</v>
       </c>
       <c r="S10" s="1">
-        <v>12.730882176</v>
+        <v>42.436273919999998</v>
       </c>
       <c r="T10" s="1">
-        <v>13.380483623999996</v>
+        <v>44.601612079999988</v>
       </c>
       <c r="U10" s="1">
-        <v>11.838195199999999</v>
+        <v>39.460650666666666</v>
       </c>
       <c r="V10" s="1">
-        <v>9.4510490879999995</v>
+        <v>31.503496959999996</v>
       </c>
       <c r="W10" s="1">
-        <v>9.5762652480000003</v>
+        <v>31.92088416</v>
       </c>
       <c r="X10" s="1">
-        <v>11.348915760000001</v>
+        <v>37.8297192</v>
       </c>
       <c r="Y10" s="1">
-        <v>11.177137152</v>
+        <v>37.257123839999998</v>
       </c>
       <c r="Z10" s="1">
-        <v>8.4414528000000004</v>
+        <v>28.138176000000001</v>
       </c>
       <c r="AA10" s="1">
-        <v>9.5335811200000009</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+        <v>31.778603733333338</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -11903,79 +11918,79 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>4.8613363200000004</v>
+        <v>16.204454399999999</v>
       </c>
       <c r="E11" s="1">
-        <v>4.6820966400000001</v>
+        <v>15.606988800000002</v>
       </c>
       <c r="F11" s="1">
-        <v>4.1925427199999996</v>
+        <v>13.975142399999998</v>
       </c>
       <c r="G11" s="1">
-        <v>4.3464960000000001</v>
+        <v>14.488320000000002</v>
       </c>
       <c r="H11" s="1">
-        <v>3.4593177599999994</v>
+        <v>11.531059199999996</v>
       </c>
       <c r="I11" s="1">
-        <v>2.9072486400000002</v>
+        <v>9.6908288000000002</v>
       </c>
       <c r="J11" s="1">
-        <v>3.4497254399999999</v>
+        <v>11.4990848</v>
       </c>
       <c r="K11" s="1">
-        <v>0.64189440000000009</v>
+        <v>2.1396480000000002</v>
       </c>
       <c r="L11" s="1">
-        <v>0.53760000000000008</v>
+        <v>1.7920000000000005</v>
       </c>
       <c r="M11" s="1">
-        <v>0.81509376</v>
+        <v>2.7169792000000004</v>
       </c>
       <c r="N11" s="1">
-        <v>0.43848959999999998</v>
+        <v>1.4616319999999998</v>
       </c>
       <c r="O11" s="1">
-        <v>0.58830335999999994</v>
+        <v>1.9610111999999997</v>
       </c>
       <c r="P11" s="1">
-        <v>0.93729024000000005</v>
+        <v>3.1243008000000003</v>
       </c>
       <c r="Q11" s="1">
-        <v>1.6422643199999998</v>
+        <v>5.4742143999999984</v>
       </c>
       <c r="R11" s="1">
-        <v>1.8605260799999999</v>
+        <v>6.2017536</v>
       </c>
       <c r="S11" s="1">
-        <v>1.776384</v>
+        <v>5.9212799999999994</v>
       </c>
       <c r="T11" s="1">
-        <v>1.0463040000000001</v>
+        <v>3.4876800000000006</v>
       </c>
       <c r="U11" s="1">
-        <v>2.1110169599999993</v>
+        <v>7.0367231999999973</v>
       </c>
       <c r="V11" s="1">
-        <v>1.2149913599999997</v>
+        <v>4.049971199999999</v>
       </c>
       <c r="W11" s="1">
-        <v>0.82075391999999991</v>
+        <v>2.7358463999999998</v>
       </c>
       <c r="X11" s="1">
-        <v>1.2845260799999998</v>
+        <v>4.2817535999999992</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.77032703999999996</v>
+        <v>2.5677567999999997</v>
       </c>
       <c r="Z11" s="1">
-        <v>3.5877119999999998</v>
+        <v>11.95904</v>
       </c>
       <c r="AA11" s="1">
-        <v>4.2384921599999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+        <v>14.1283072</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -11986,79 +12001,79 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-10.762559999999999</v>
+        <v>-35.8752</v>
       </c>
       <c r="E12" s="1">
-        <v>-11.166919680000001</v>
+        <v>-37.223065600000005</v>
       </c>
       <c r="F12" s="1">
-        <v>-12.559303680000001</v>
+        <v>-41.8643456</v>
       </c>
       <c r="G12" s="1">
-        <v>-13.686140159999997</v>
+        <v>-45.620467199999986</v>
       </c>
       <c r="H12" s="1">
-        <v>-14.185267199999998</v>
+        <v>-47.284223999999995</v>
       </c>
       <c r="I12" s="1">
-        <v>-16.126079999999998</v>
+        <v>-53.753599999999999</v>
       </c>
       <c r="J12" s="1">
-        <v>-15.848881920000002</v>
+        <v>-52.82960640000001</v>
       </c>
       <c r="K12" s="1">
-        <v>-17.605780991999996</v>
+        <v>-58.685936639999987</v>
       </c>
       <c r="L12" s="1">
-        <v>-15.185413631999998</v>
+        <v>-50.618045439999996</v>
       </c>
       <c r="M12" s="1">
-        <v>-21.844990079999999</v>
+        <v>-72.816633600000003</v>
       </c>
       <c r="N12" s="1">
-        <v>-22.076293632000002</v>
+        <v>-73.587645440000003</v>
       </c>
       <c r="O12" s="1">
-        <v>-20.181115391999999</v>
+        <v>-67.270384639999989</v>
       </c>
       <c r="P12" s="1">
-        <v>-19.544706048000002</v>
+        <v>-65.149020160000006</v>
       </c>
       <c r="Q12" s="1">
-        <v>-20.025388032000002</v>
+        <v>-66.751293439999998</v>
       </c>
       <c r="R12" s="1">
-        <v>-18.330947328000001</v>
+        <v>-61.103157760000009</v>
       </c>
       <c r="S12" s="1">
-        <v>-17.011552511999994</v>
+        <v>-56.705175039999979</v>
       </c>
       <c r="T12" s="1">
-        <v>-14.825742336000001</v>
+        <v>-49.419141120000006</v>
       </c>
       <c r="U12" s="1">
-        <v>-13.129370880000002</v>
+        <v>-43.764569600000009</v>
       </c>
       <c r="V12" s="1">
-        <v>-8.4213227519999982</v>
+        <v>-28.071075839999992</v>
       </c>
       <c r="W12" s="1">
-        <v>-10.111943424000001</v>
+        <v>-33.706478080000004</v>
       </c>
       <c r="X12" s="1">
-        <v>-10.688769791999999</v>
+        <v>-35.629232639999998</v>
       </c>
       <c r="Y12" s="1">
-        <v>-10.5841248</v>
+        <v>-35.280415999999995</v>
       </c>
       <c r="Z12" s="1">
-        <v>-8.851583999999999</v>
+        <v>-29.505279999999999</v>
       </c>
       <c r="AA12" s="1">
-        <v>-9.2175820799999979</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-30.725273599999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -12069,79 +12084,79 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>9.7525267199999988</v>
+        <v>32.508422399999994</v>
       </c>
       <c r="E13" s="1">
-        <v>10.543398912000001</v>
+        <v>35.144663040000005</v>
       </c>
       <c r="F13" s="1">
-        <v>11.821584383999998</v>
+        <v>39.40528127999999</v>
       </c>
       <c r="G13" s="1">
-        <v>12.985335552000002</v>
+        <v>43.28445184000001</v>
       </c>
       <c r="H13" s="1">
-        <v>14.385818879999999</v>
+        <v>47.952729599999998</v>
       </c>
       <c r="I13" s="1">
-        <v>15.554323200000001</v>
+        <v>51.847744000000006</v>
       </c>
       <c r="J13" s="1">
-        <v>15.2695296</v>
+        <v>50.898432000000007</v>
       </c>
       <c r="K13" s="1">
-        <v>16.568793599999999</v>
+        <v>55.229311999999993</v>
       </c>
       <c r="L13" s="1">
-        <v>15.935633279999999</v>
+        <v>53.118777599999994</v>
       </c>
       <c r="M13" s="1">
-        <v>17.837398271999998</v>
+        <v>59.457994239999998</v>
       </c>
       <c r="N13" s="1">
-        <v>18.152389631999998</v>
+        <v>60.507965439999992</v>
       </c>
       <c r="O13" s="1">
-        <v>15.685300223999997</v>
+        <v>52.284334079999986</v>
       </c>
       <c r="P13" s="1">
-        <v>16.577567999999999</v>
+        <v>55.258559999999996</v>
       </c>
       <c r="Q13" s="1">
-        <v>14.767054847999997</v>
+        <v>49.223516159999996</v>
       </c>
       <c r="R13" s="1">
-        <v>13.694883839999999</v>
+        <v>45.6496128</v>
       </c>
       <c r="S13" s="1">
-        <v>13.78085184</v>
+        <v>45.936172800000001</v>
       </c>
       <c r="T13" s="1">
-        <v>12.471130367999999</v>
+        <v>41.570434559999995</v>
       </c>
       <c r="U13" s="1">
-        <v>10.490462207999999</v>
+        <v>34.968207359999994</v>
       </c>
       <c r="V13" s="1">
-        <v>8.5529855999999995</v>
+        <v>28.509951999999998</v>
       </c>
       <c r="W13" s="1">
-        <v>9.8604718079999998</v>
+        <v>32.868239359999997</v>
       </c>
       <c r="X13" s="1">
-        <v>10.376151552</v>
+        <v>34.587171839999996</v>
       </c>
       <c r="Y13" s="1">
-        <v>11.067557376</v>
+        <v>36.89185792</v>
       </c>
       <c r="Z13" s="1">
-        <v>8.9530559999999983</v>
+        <v>29.843519999999994</v>
       </c>
       <c r="AA13" s="1">
-        <v>8.9763379199999989</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+        <v>29.921126399999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -12152,79 +12167,79 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>4.5762637823999999</v>
+        <v>15.254212607999998</v>
       </c>
       <c r="E14" s="1">
-        <v>4.8274367231999999</v>
+        <v>16.091455744000001</v>
       </c>
       <c r="F14" s="1">
-        <v>4.4100308736000002</v>
+        <v>14.700102912</v>
       </c>
       <c r="G14" s="1">
-        <v>4.0931573760000006</v>
+        <v>13.643857920000002</v>
       </c>
       <c r="H14" s="1">
-        <v>3.3575731200000001</v>
+        <v>11.191910399999999</v>
       </c>
       <c r="I14" s="1">
-        <v>2.8781761536000001</v>
+        <v>9.5939205120000004</v>
       </c>
       <c r="J14" s="1">
-        <v>3.4842226943999997</v>
+        <v>11.614075647999998</v>
       </c>
       <c r="K14" s="1">
-        <v>0.57495398400000008</v>
+        <v>1.9165132800000002</v>
       </c>
       <c r="L14" s="1">
-        <v>0.54265344000000015</v>
+        <v>1.8088448000000004</v>
       </c>
       <c r="M14" s="1">
-        <v>0.75200236800000009</v>
+        <v>2.5066745600000004</v>
       </c>
       <c r="N14" s="1">
-        <v>0.44310527999999999</v>
+        <v>1.4770175999999999</v>
       </c>
       <c r="O14" s="1">
-        <v>0.55888819200000006</v>
+        <v>1.8629606400000001</v>
       </c>
       <c r="P14" s="1">
-        <v>0.82931808000000018</v>
+        <v>2.7643936000000005</v>
       </c>
       <c r="Q14" s="1">
-        <v>1.6090804223999999</v>
+        <v>5.3636014080000001</v>
       </c>
       <c r="R14" s="1">
-        <v>1.8410176511999998</v>
+        <v>6.1367255040000002</v>
       </c>
       <c r="S14" s="1">
-        <v>1.7234477568000002</v>
+        <v>5.7448258560000012</v>
       </c>
       <c r="T14" s="1">
-        <v>1.006245504</v>
+        <v>3.3541516799999997</v>
       </c>
       <c r="U14" s="1">
-        <v>1.9098614015999997</v>
+        <v>6.3662046719999994</v>
       </c>
       <c r="V14" s="1">
-        <v>1.1206508543999996</v>
+        <v>3.7355028479999981</v>
       </c>
       <c r="W14" s="1">
-        <v>0.8205026688</v>
+        <v>2.7350088960000001</v>
       </c>
       <c r="X14" s="1">
-        <v>1.3086904319999999</v>
+        <v>4.3623014399999995</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.80176895999999997</v>
+        <v>2.6725632000000004</v>
       </c>
       <c r="Z14" s="1">
-        <v>3.4800806399999997</v>
+        <v>11.6002688</v>
       </c>
       <c r="AA14" s="1">
-        <v>4.1935122431999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+        <v>13.978374144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -12235,79 +12250,79 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-10.629359999999998</v>
+        <v>-35.431199999999997</v>
       </c>
       <c r="E15" s="1">
-        <v>-11.736660480000001</v>
+        <v>-39.122201600000004</v>
       </c>
       <c r="F15" s="1">
-        <v>-13.0732098816</v>
+        <v>-43.577366272000006</v>
       </c>
       <c r="G15" s="1">
-        <v>-13.264496447999999</v>
+        <v>-44.214988159999997</v>
       </c>
       <c r="H15" s="1">
-        <v>-15.0718464</v>
+        <v>-50.239488000000001</v>
       </c>
       <c r="I15" s="1">
-        <v>-15.955143551999997</v>
+        <v>-53.183811839999997</v>
       </c>
       <c r="J15" s="1">
-        <v>-16.008909465600002</v>
+        <v>-53.363031552000002</v>
       </c>
       <c r="K15" s="1">
-        <v>-17.412462612479995</v>
+        <v>-58.041542041599989</v>
       </c>
       <c r="L15" s="1">
-        <v>-15.169758566399999</v>
+        <v>-50.565861887999993</v>
       </c>
       <c r="M15" s="1">
-        <v>-22.937239584</v>
+        <v>-76.457465279999994</v>
       </c>
       <c r="N15" s="1">
-        <v>-21.621112320000002</v>
+        <v>-72.070374400000006</v>
       </c>
       <c r="O15" s="1">
-        <v>-20.160310118400002</v>
+        <v>-67.201033728000013</v>
       </c>
       <c r="P15" s="1">
-        <v>-19.935600168959997</v>
+        <v>-66.452000563199988</v>
       </c>
       <c r="Q15" s="1">
-        <v>-18.854673039360001</v>
+        <v>-62.8489101312</v>
       </c>
       <c r="R15" s="1">
-        <v>-17.931659366400002</v>
+        <v>-59.772197888000001</v>
       </c>
       <c r="S15" s="1">
-        <v>-16.509463971839999</v>
+        <v>-55.031546572800004</v>
       </c>
       <c r="T15" s="1">
-        <v>-15.891342566400001</v>
+        <v>-52.971141888000005</v>
       </c>
       <c r="U15" s="1">
-        <v>-14.948134256640001</v>
+        <v>-49.827114188800003</v>
       </c>
       <c r="V15" s="1">
-        <v>-8.33886396672</v>
+        <v>-27.796213222399999</v>
       </c>
       <c r="W15" s="1">
-        <v>-9.1419822489599998</v>
+        <v>-30.473274163199999</v>
       </c>
       <c r="X15" s="1">
-        <v>-10.373295421439998</v>
+        <v>-34.577651404799994</v>
       </c>
       <c r="Y15" s="1">
-        <v>-11.4776477568</v>
+        <v>-38.258825855999994</v>
       </c>
       <c r="Z15" s="1">
-        <v>-9.2977038336000017</v>
+        <v>-30.992346112000007</v>
       </c>
       <c r="AA15" s="1">
-        <v>-9.4884661248000004</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-31.628220416000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -12318,79 +12333,79 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>9.4599509184000006</v>
+        <v>31.533169728000001</v>
       </c>
       <c r="E16" s="1">
-        <v>11.993116262399999</v>
+        <v>39.977054207999998</v>
       </c>
       <c r="F16" s="1">
-        <v>12.934783580160001</v>
+        <v>43.115945267200004</v>
       </c>
       <c r="G16" s="1">
-        <v>13.918159656960002</v>
+        <v>46.393865523200013</v>
       </c>
       <c r="H16" s="1">
-        <v>13.4070190464</v>
+        <v>44.690063488</v>
       </c>
       <c r="I16" s="1">
-        <v>16.656986111999998</v>
+        <v>55.523287039999992</v>
       </c>
       <c r="J16" s="1">
-        <v>15.574920192</v>
+        <v>51.916400640000006</v>
       </c>
       <c r="K16" s="1">
-        <v>14.953336224000003</v>
+        <v>49.844454080000013</v>
       </c>
       <c r="L16" s="1">
-        <v>15.138851616</v>
+        <v>50.462838720000001</v>
       </c>
       <c r="M16" s="1">
-        <v>16.46235999744</v>
+        <v>54.874533324800005</v>
       </c>
       <c r="N16" s="1">
-        <v>17.244770150399997</v>
+        <v>57.482567167999996</v>
       </c>
       <c r="O16" s="1">
-        <v>17.327355091200001</v>
+        <v>57.757850304000009</v>
       </c>
       <c r="P16" s="1">
-        <v>15.308199936000003</v>
+        <v>51.027333120000009</v>
       </c>
       <c r="Q16" s="1">
-        <v>16.319133841919999</v>
+        <v>54.397112806400003</v>
       </c>
       <c r="R16" s="1">
-        <v>13.986080317439999</v>
+        <v>46.620267724799994</v>
       </c>
       <c r="S16" s="1">
-        <v>13.240117463039999</v>
+        <v>44.133724876799995</v>
       </c>
       <c r="T16" s="1">
-        <v>13.223066169599997</v>
+        <v>44.07688723199999</v>
       </c>
       <c r="U16" s="1">
-        <v>11.819254087679999</v>
+        <v>39.397513625599998</v>
       </c>
       <c r="V16" s="1">
-        <v>8.6368048588799997</v>
+        <v>28.789349529599999</v>
       </c>
       <c r="W16" s="1">
-        <v>9.0074931302400003</v>
+        <v>30.024977100800001</v>
       </c>
       <c r="X16" s="1">
-        <v>9.9611054899199996</v>
+        <v>33.203684966399997</v>
       </c>
       <c r="Y16" s="1">
-        <v>10.835248250879999</v>
+        <v>36.1174941696</v>
       </c>
       <c r="Z16" s="1">
-        <v>8.1037946879999989</v>
+        <v>27.012648959999996</v>
       </c>
       <c r="AA16" s="1">
-        <v>9.3299512319999991</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+        <v>31.099837439999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -12401,79 +12416,79 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>5.1063476705280006</v>
+        <v>17.021158901760003</v>
       </c>
       <c r="E17" s="1">
-        <v>5.1189947827200006</v>
+        <v>17.063315942400003</v>
       </c>
       <c r="F17" s="1">
-        <v>4.1895293299199992</v>
+        <v>13.965097766399998</v>
       </c>
       <c r="G17" s="1">
-        <v>4.4794491033600004</v>
+        <v>14.931497011200001</v>
       </c>
       <c r="H17" s="1">
-        <v>3.257517441024</v>
+        <v>10.858391470080001</v>
       </c>
       <c r="I17" s="1">
-        <v>2.7884112537599997</v>
+        <v>9.2947041791999983</v>
       </c>
       <c r="J17" s="1">
-        <v>3.623591602176</v>
+        <v>12.078638673919999</v>
       </c>
       <c r="K17" s="1">
-        <v>0.58100613120000011</v>
+        <v>1.9366871040000004</v>
       </c>
       <c r="L17" s="1">
-        <v>0.57560025599999998</v>
+        <v>1.9186675199999998</v>
       </c>
       <c r="M17" s="1">
-        <v>0.78271572787200017</v>
+        <v>2.6090524262400003</v>
       </c>
       <c r="N17" s="1">
-        <v>0.44292803788800006</v>
+        <v>1.4764267929600001</v>
       </c>
       <c r="O17" s="1">
-        <v>0.58777388697600008</v>
+        <v>1.9592462899200003</v>
       </c>
       <c r="P17" s="1">
-        <v>0.80443853759999995</v>
+        <v>2.6814617919999999</v>
       </c>
       <c r="Q17" s="1">
-        <v>1.6908347105279997</v>
+        <v>5.6361157017599988</v>
       </c>
       <c r="R17" s="1">
-        <v>2.0123450081279999</v>
+        <v>6.707816693759999</v>
       </c>
       <c r="S17" s="1">
-        <v>1.8096201446400002</v>
+        <v>6.0320671488000004</v>
       </c>
       <c r="T17" s="1">
-        <v>0.98612059392000018</v>
+        <v>3.2870686464000003</v>
       </c>
       <c r="U17" s="1">
-        <v>2.0083078655999995</v>
+        <v>6.6943595519999981</v>
       </c>
       <c r="V17" s="1">
-        <v>1.2625999626239996</v>
+        <v>4.2086665420799987</v>
       </c>
       <c r="W17" s="1">
-        <v>0.84587903999999992</v>
+        <v>2.8195967999999998</v>
       </c>
       <c r="X17" s="1">
-        <v>1.172586627072</v>
+        <v>3.9086220902400002</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.77818752000000002</v>
+        <v>2.5939584</v>
       </c>
       <c r="Z17" s="1">
-        <v>3.5496822527999994</v>
+        <v>11.832274175999999</v>
       </c>
       <c r="AA17" s="1">
-        <v>4.2773824880640001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+        <v>14.257941626879999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -12484,79 +12499,79 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-11.748239999999999</v>
+        <v>-39.160799999999995</v>
       </c>
       <c r="E18" s="1">
-        <v>-11.1578038272</v>
+        <v>-37.192679423999998</v>
       </c>
       <c r="F18" s="1">
-        <v>-13.465406178048001</v>
+        <v>-44.884687260160007</v>
       </c>
       <c r="G18" s="1">
-        <v>-13.814623984895997</v>
+        <v>-46.048746616319988</v>
       </c>
       <c r="H18" s="1">
-        <v>-15.058281738239998</v>
+        <v>-50.194272460799993</v>
       </c>
       <c r="I18" s="1">
-        <v>-15.316937809919995</v>
+        <v>-51.056459366399984</v>
       </c>
       <c r="J18" s="1">
-        <v>-16.809354938880002</v>
+        <v>-56.031183129600009</v>
       </c>
       <c r="K18" s="1">
-        <v>-16.543634581094395</v>
+        <v>-55.145448603647985</v>
       </c>
       <c r="L18" s="1">
-        <v>-15.621876860928001</v>
+        <v>-52.072922869759999</v>
       </c>
       <c r="M18" s="1">
-        <v>-21.390614286335996</v>
+        <v>-71.302047621119982</v>
       </c>
       <c r="N18" s="1">
-        <v>-22.053534566400003</v>
+        <v>-73.511781888000016</v>
       </c>
       <c r="O18" s="1">
-        <v>-17.8379214528</v>
+        <v>-59.459738176000002</v>
       </c>
       <c r="P18" s="1">
-        <v>-19.919964404121597</v>
+        <v>-66.399881347071997</v>
       </c>
       <c r="Q18" s="1">
-        <v>-19.416616235827199</v>
+        <v>-64.722054119424001</v>
       </c>
       <c r="R18" s="1">
-        <v>-19.445468925542404</v>
+        <v>-64.818229751808005</v>
       </c>
       <c r="S18" s="1">
-        <v>-16.844707168819198</v>
+        <v>-56.149023896063994</v>
       </c>
       <c r="T18" s="1">
-        <v>-16.368082843392003</v>
+        <v>-54.560276144640007</v>
       </c>
       <c r="U18" s="1">
-        <v>-15.097615599206401</v>
+        <v>-50.325385330688</v>
       </c>
       <c r="V18" s="1">
-        <v>-8.6724185253887978</v>
+        <v>-28.908061751295993</v>
       </c>
       <c r="W18" s="1">
-        <v>-10.299014377344001</v>
+        <v>-34.330047924480006</v>
       </c>
       <c r="X18" s="1">
-        <v>-9.178332468479999</v>
+        <v>-30.594441561599997</v>
       </c>
       <c r="Y18" s="1">
-        <v>-11.234591686656</v>
+        <v>-37.448638955520003</v>
       </c>
       <c r="Z18" s="1">
-        <v>-9.2047267952640013</v>
+        <v>-30.682422650880003</v>
       </c>
       <c r="AA18" s="1">
-        <v>-9.7780110704640002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-32.593370234880005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -12567,79 +12582,79 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>9.2727434686464001</v>
+        <v>30.909144895487998</v>
       </c>
       <c r="E19" s="1">
-        <v>11.194717379788802</v>
+        <v>37.315724599296004</v>
       </c>
       <c r="F19" s="1">
-        <v>12.546740072755201</v>
+        <v>41.822466909184001</v>
       </c>
       <c r="G19" s="1">
-        <v>13.922174510707203</v>
+        <v>46.407248369024011</v>
       </c>
       <c r="H19" s="1">
-        <v>13.137510602304001</v>
+        <v>43.791702007680009</v>
       </c>
       <c r="I19" s="1">
-        <v>15.22192269312</v>
+        <v>50.739742310400004</v>
       </c>
       <c r="J19" s="1">
-        <v>15.72150767616</v>
+        <v>52.405025587199994</v>
       </c>
       <c r="K19" s="1">
-        <v>15.878869034496001</v>
+        <v>52.929563448320003</v>
       </c>
       <c r="L19" s="1">
-        <v>14.265123608448002</v>
+        <v>47.550412028160004</v>
       </c>
       <c r="M19" s="1">
-        <v>16.971505151999999</v>
+        <v>56.571683839999992</v>
       </c>
       <c r="N19" s="1">
-        <v>19.0709005473792</v>
+        <v>63.569668491263997</v>
       </c>
       <c r="O19" s="1">
-        <v>17.505579314995199</v>
+        <v>58.351931049983996</v>
       </c>
       <c r="P19" s="1">
-        <v>15.914465280000002</v>
+        <v>53.048217600000008</v>
       </c>
       <c r="Q19" s="1">
-        <v>15.666368488243199</v>
+        <v>52.221228294143998</v>
       </c>
       <c r="R19" s="1">
-        <v>14.092035471359997</v>
+        <v>46.973451571199995</v>
       </c>
       <c r="S19" s="1">
-        <v>11.854997482291198</v>
+        <v>39.516658274303992</v>
       </c>
       <c r="T19" s="1">
-        <v>12.973716921830396</v>
+        <v>43.245723072767987</v>
       </c>
       <c r="U19" s="1">
-        <v>11.705607413759999</v>
+        <v>39.0186913792</v>
       </c>
       <c r="V19" s="1">
-        <v>8.7100868395007982</v>
+        <v>29.033622798335994</v>
       </c>
       <c r="W19" s="1">
-        <v>9.3770789308416003</v>
+        <v>31.256929769471999</v>
       </c>
       <c r="X19" s="1">
-        <v>10.786009538303999</v>
+        <v>35.953365127679994</v>
       </c>
       <c r="Y19" s="1">
-        <v>11.266554249215998</v>
+        <v>37.555180830719998</v>
       </c>
       <c r="Z19" s="1">
-        <v>7.7796429004800007</v>
+        <v>25.9321430016</v>
       </c>
       <c r="AA19" s="1">
-        <v>9.6098497689600002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+        <v>32.032832563200003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -12650,79 +12665,79 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>5.1569055682560005</v>
+        <v>17.189685227520002</v>
       </c>
       <c r="E20" s="1">
-        <v>5.112849530880001</v>
+        <v>17.042831769600003</v>
       </c>
       <c r="F20" s="1">
-        <v>4.4474493173759999</v>
+        <v>14.824831057919999</v>
       </c>
       <c r="G20" s="1">
-        <v>4.3847451648</v>
+        <v>14.615817216000002</v>
       </c>
       <c r="H20" s="1">
-        <v>3.7415980892159997</v>
+        <v>12.471993630719998</v>
       </c>
       <c r="I20" s="1">
-        <v>3.1747155148800004</v>
+        <v>10.582385049600001</v>
       </c>
       <c r="J20" s="1">
-        <v>3.623591602176</v>
+        <v>12.078638673919999</v>
       </c>
       <c r="K20" s="1">
-        <v>0.65421877248000015</v>
+        <v>2.1807292416000004</v>
       </c>
       <c r="L20" s="1">
-        <v>0.54792192000000006</v>
+        <v>1.8264064000000004</v>
       </c>
       <c r="M20" s="1">
-        <v>0.80531263488000004</v>
+        <v>2.6843754496000005</v>
       </c>
       <c r="N20" s="1">
-        <v>0.46058947583999993</v>
+        <v>1.5352982527999997</v>
       </c>
       <c r="O20" s="1">
-        <v>0.58124371967999999</v>
+        <v>1.9374790655999998</v>
       </c>
       <c r="P20" s="1">
-        <v>1.0235209420800002</v>
+        <v>3.4117364736000009</v>
       </c>
       <c r="Q20" s="1">
-        <v>1.7250344417279999</v>
+        <v>5.7501148057599991</v>
       </c>
       <c r="R20" s="1">
-        <v>1.8381997670399999</v>
+        <v>6.127332556799999</v>
       </c>
       <c r="S20" s="1">
-        <v>1.7735417856</v>
+        <v>5.911805951999999</v>
       </c>
       <c r="T20" s="1">
-        <v>1.0337483520000001</v>
+        <v>3.4458278400000002</v>
       </c>
       <c r="U20" s="1">
-        <v>2.1295939092479994</v>
+        <v>7.0986463641599977</v>
       </c>
       <c r="V20" s="1">
-        <v>1.2888628346879998</v>
+        <v>4.2962094489599991</v>
       </c>
       <c r="W20" s="1">
-        <v>0.87919159910400002</v>
+        <v>2.9306386636799999</v>
       </c>
       <c r="X20" s="1">
-        <v>1.322548051968</v>
+        <v>4.4084935065600002</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.80114012160000003</v>
+        <v>2.6704670719999997</v>
       </c>
       <c r="Z20" s="1">
-        <v>3.6565960703999996</v>
+        <v>12.188653567999999</v>
       </c>
       <c r="AA20" s="1">
-        <v>4.3198712094720007</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+        <v>14.399570698240003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -12733,79 +12748,79 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-11.640784895999998</v>
+        <v>-38.802616319999991</v>
       </c>
       <c r="E21" s="1">
-        <v>-12.194276290560003</v>
+        <v>-40.647587635200011</v>
       </c>
       <c r="F21" s="1">
-        <v>-12.408592035840002</v>
+        <v>-41.361973452800008</v>
       </c>
       <c r="G21" s="1">
-        <v>-14.518257481727996</v>
+        <v>-48.394191605759993</v>
       </c>
       <c r="H21" s="1">
-        <v>-14.31009755136</v>
+        <v>-47.700325171199999</v>
       </c>
       <c r="I21" s="1">
-        <v>-17.274256895999997</v>
+        <v>-57.580856319999988</v>
       </c>
       <c r="J21" s="1">
-        <v>-15.658695336960001</v>
+        <v>-52.195651123200001</v>
       </c>
       <c r="K21" s="1">
-        <v>-18.859312598630396</v>
+        <v>-62.864375328767984</v>
       </c>
       <c r="L21" s="1">
-        <v>-15.1611169701888</v>
+        <v>-50.537056567295998</v>
       </c>
       <c r="M21" s="1">
-        <v>-22.718789683200001</v>
+        <v>-75.729298944000007</v>
       </c>
       <c r="N21" s="1">
-        <v>-23.877719192371202</v>
+        <v>-79.592397307904008</v>
       </c>
       <c r="O21" s="1">
-        <v>-20.5685928075264</v>
+        <v>-68.561976025088001</v>
       </c>
       <c r="P21" s="1">
-        <v>-20.936289118617601</v>
+        <v>-69.787630395392</v>
       </c>
       <c r="Q21" s="1">
-        <v>-20.618139517747203</v>
+        <v>-68.727131725824009</v>
       </c>
       <c r="R21" s="1">
-        <v>-18.492259664486404</v>
+        <v>-61.640865548288012</v>
       </c>
       <c r="S21" s="1">
-        <v>-18.576615343103995</v>
+        <v>-61.922051143679987</v>
       </c>
       <c r="T21" s="1">
-        <v>-15.110396588851202</v>
+        <v>-50.367988629504005</v>
       </c>
       <c r="U21" s="1">
-        <v>-14.064182086656004</v>
+        <v>-46.880606955520015</v>
       </c>
       <c r="V21" s="1">
-        <v>-8.5830121488383995</v>
+        <v>-28.610040496127997</v>
       </c>
       <c r="W21" s="1">
-        <v>-10.306092737740803</v>
+        <v>-34.353642459136012</v>
       </c>
       <c r="X21" s="1">
-        <v>-11.116320583679999</v>
+        <v>-37.054401945599999</v>
       </c>
       <c r="Y21" s="1">
-        <v>-10.567190200319999</v>
+        <v>-35.223967334399994</v>
       </c>
       <c r="Z21" s="1">
-        <v>-9.4818167807999991</v>
+        <v>-31.606055936000001</v>
       </c>
       <c r="AA21" s="1">
-        <v>-9.8738739240959976</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-32.912913080319989</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -12816,79 +12831,79 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>10.244054066687999</v>
+        <v>34.146846888959999</v>
       </c>
       <c r="E22" s="1">
-        <v>11.074786217164801</v>
+        <v>36.915954057216005</v>
       </c>
       <c r="F22" s="1">
-        <v>12.909170147327998</v>
+        <v>43.030567157759997</v>
       </c>
       <c r="G22" s="1">
-        <v>14.179986422784005</v>
+        <v>47.266621409280013</v>
       </c>
       <c r="H22" s="1">
-        <v>14.811639118847998</v>
+        <v>49.372130396159996</v>
       </c>
       <c r="I22" s="1">
-        <v>16.985320934400001</v>
+        <v>56.617736447999995</v>
       </c>
       <c r="J22" s="1">
-        <v>15.880310784000001</v>
+        <v>52.934369279999999</v>
       </c>
       <c r="K22" s="1">
-        <v>16.542283530240002</v>
+        <v>55.140945100800003</v>
       </c>
       <c r="L22" s="1">
-        <v>15.910136266752001</v>
+        <v>53.033787555840007</v>
       </c>
       <c r="M22" s="1">
-        <v>17.623349492736001</v>
+        <v>58.744498309119997</v>
       </c>
       <c r="N22" s="1">
-        <v>18.878485217279998</v>
+        <v>62.928284057599996</v>
       </c>
       <c r="O22" s="1">
-        <v>17.128347844608001</v>
+        <v>57.094492815360006</v>
       </c>
       <c r="P22" s="1">
-        <v>16.8958573056</v>
+        <v>56.319524352000002</v>
       </c>
       <c r="Q22" s="1">
-        <v>16.125623894015998</v>
+        <v>53.752079646719999</v>
       </c>
       <c r="R22" s="1">
-        <v>14.100252401663999</v>
+        <v>47.000841338880001</v>
       </c>
       <c r="S22" s="1">
-        <v>13.758802477056001</v>
+        <v>45.862674923520011</v>
       </c>
       <c r="T22" s="1">
-        <v>13.359074850201601</v>
+        <v>44.530249500672006</v>
       </c>
       <c r="U22" s="1">
-        <v>11.2373831172096</v>
+        <v>37.457943724031999</v>
       </c>
       <c r="V22" s="1">
-        <v>8.5393008230399996</v>
+        <v>28.464336076799999</v>
       </c>
       <c r="W22" s="1">
-        <v>10.254890680319999</v>
+        <v>34.182968934400002</v>
       </c>
       <c r="X22" s="1">
-        <v>10.79119761408</v>
+        <v>35.970658713599995</v>
       </c>
       <c r="Y22" s="1">
-        <v>10.934746687487999</v>
+        <v>36.449155624959999</v>
       </c>
       <c r="Z22" s="1">
-        <v>9.4974018047999991</v>
+        <v>31.658006015999998</v>
       </c>
       <c r="AA22" s="1">
-        <v>9.3353914367999984</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+        <v>31.117971455999992</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -12899,79 +12914,79 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>4.9972800503807999</v>
+        <v>16.657600167936</v>
       </c>
       <c r="E23" s="1">
-        <v>5.1209448759705607</v>
+        <v>17.069816253235203</v>
       </c>
       <c r="F23" s="1">
-        <v>4.7240250718003214</v>
+        <v>15.746750239334403</v>
       </c>
       <c r="G23" s="1">
-        <v>4.1717459976192002</v>
+        <v>13.905819992064002</v>
       </c>
       <c r="H23" s="1">
-        <v>3.3172822425600001</v>
+        <v>11.057607475200001</v>
       </c>
       <c r="I23" s="1">
-        <v>3.0232362317414401</v>
+        <v>10.077454105804799</v>
       </c>
       <c r="J23" s="1">
-        <v>3.5511197701324799</v>
+        <v>11.837065900441599</v>
       </c>
       <c r="K23" s="1">
-        <v>0.59795214336000013</v>
+        <v>1.9931738112000004</v>
       </c>
       <c r="L23" s="1">
-        <v>0.57000317337600026</v>
+        <v>1.9000105779200009</v>
       </c>
       <c r="M23" s="1">
-        <v>0.77426163809280013</v>
+        <v>2.5808721269760002</v>
       </c>
       <c r="N23" s="1">
-        <v>0.4608294912</v>
+        <v>1.536098304</v>
       </c>
       <c r="O23" s="1">
-        <v>0.58705615687680013</v>
+        <v>1.9568538562560003</v>
       </c>
       <c r="P23" s="1">
-        <v>0.87111571123200027</v>
+        <v>2.9037190374400006</v>
       </c>
       <c r="Q23" s="1">
-        <v>1.70691251208192</v>
+        <v>5.6897083736064005</v>
       </c>
       <c r="R23" s="1">
-        <v>1.8189254393855998</v>
+        <v>6.0630847979519986</v>
       </c>
       <c r="S23" s="1">
-        <v>1.7565379537305603</v>
+        <v>5.8551265124352012</v>
       </c>
       <c r="T23" s="1">
-        <v>1.0569602774016003</v>
+        <v>3.5232009246720009</v>
       </c>
       <c r="U23" s="1">
-        <v>1.9465307405107197</v>
+        <v>6.4884358017023986</v>
       </c>
       <c r="V23" s="1">
-        <v>1.1421673508044796</v>
+        <v>3.8072245026815987</v>
       </c>
       <c r="W23" s="1">
-        <v>0.87892245881856002</v>
+        <v>2.9297415293952001</v>
       </c>
       <c r="X23" s="1">
-        <v>1.2929861468160002</v>
+        <v>4.3099538227200007</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.83383971840000004</v>
+        <v>2.7794657279999999</v>
       </c>
       <c r="Z23" s="1">
-        <v>3.546898188288</v>
+        <v>11.82299396096</v>
       </c>
       <c r="AA23" s="1">
-        <v>4.5357028422451195</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+        <v>15.119009474150397</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -12982,79 +12997,79 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-10.501807679999997</v>
+        <v>-35.006025599999994</v>
       </c>
       <c r="E24" s="1">
-        <v>-11.717881823232</v>
+        <v>-39.059606077440002</v>
       </c>
       <c r="F24" s="1">
-        <v>-14.139983807938561</v>
+        <v>-47.133279359795203</v>
       </c>
       <c r="G24" s="1">
-        <v>-13.381224016742401</v>
+        <v>-44.604080055808005</v>
       </c>
       <c r="H24" s="1">
-        <v>-15.20447864832</v>
+        <v>-50.6815954944</v>
       </c>
       <c r="I24" s="1">
-        <v>-16.593349294079999</v>
+        <v>-55.311164313599996</v>
       </c>
       <c r="J24" s="1">
-        <v>-17.148743819550724</v>
+        <v>-57.16247939850242</v>
       </c>
       <c r="K24" s="1">
-        <v>-19.014409172828156</v>
+        <v>-63.381363909427186</v>
       </c>
       <c r="L24" s="1">
-        <v>-16.092079887237119</v>
+        <v>-53.6402662907904</v>
       </c>
       <c r="M24" s="1">
-        <v>-23.377634584012803</v>
+        <v>-77.92544861337602</v>
       </c>
       <c r="N24" s="1">
-        <v>-22.261097244672001</v>
+        <v>-74.203657482240004</v>
       </c>
       <c r="O24" s="1">
-        <v>-21.595724198830084</v>
+        <v>-71.985747329433607</v>
       </c>
       <c r="P24" s="1">
-        <v>-19.696372966932479</v>
+        <v>-65.654576556441597</v>
       </c>
       <c r="Q24" s="1">
-        <v>-20.589302958981126</v>
+        <v>-68.631009863270421</v>
       </c>
       <c r="R24" s="1">
-        <v>-19.021904255877121</v>
+        <v>-63.406347519590405</v>
       </c>
       <c r="S24" s="1">
-        <v>-18.028334657249278</v>
+        <v>-60.094448857497589</v>
       </c>
       <c r="T24" s="1">
-        <v>-16.692266231746562</v>
+        <v>-55.6408874391552</v>
       </c>
       <c r="U24" s="1">
-        <v>-16.012441415712772</v>
+        <v>-53.374804719042572</v>
       </c>
       <c r="V24" s="1">
-        <v>-8.4122459696271363</v>
+        <v>-28.040819898757121</v>
       </c>
       <c r="W24" s="1">
-        <v>-9.602738154307584</v>
+        <v>-32.009127181025285</v>
       </c>
       <c r="X24" s="1">
-        <v>-10.572462693531644</v>
+        <v>-35.24154231177215</v>
       </c>
       <c r="Y24" s="1">
-        <v>-11.57865105705984</v>
+        <v>-38.595503523532805</v>
       </c>
       <c r="Z24" s="1">
-        <v>-9.4762197472051213</v>
+        <v>-31.587399157350404</v>
       </c>
       <c r="AA24" s="1">
-        <v>-10.16404491288576</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-33.880149709619197</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -13065,79 +13080,79 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>9.8383489551360004</v>
+        <v>32.794496517120002</v>
       </c>
       <c r="E25" s="1">
-        <v>12.84702614028288</v>
+        <v>42.823420467609601</v>
       </c>
       <c r="F25" s="1">
-        <v>14.124783669534722</v>
+        <v>47.082612231782406</v>
       </c>
       <c r="G25" s="1">
-        <v>14.764383764103171</v>
+        <v>49.214612547010567</v>
       </c>
       <c r="H25" s="1">
-        <v>13.664433812090881</v>
+        <v>45.548112706969597</v>
       </c>
       <c r="I25" s="1">
-        <v>18.0161961787392</v>
+        <v>60.053987262463998</v>
       </c>
       <c r="J25" s="1">
-        <v>16.521875339673599</v>
+        <v>55.072917798911995</v>
       </c>
       <c r="K25" s="1">
-        <v>15.551469672960003</v>
+        <v>51.838232243200004</v>
       </c>
       <c r="L25" s="1">
-        <v>15.429517567027201</v>
+        <v>51.431725223424003</v>
       </c>
       <c r="M25" s="1">
-        <v>17.805688573231109</v>
+        <v>59.352295244103694</v>
       </c>
       <c r="N25" s="1">
-        <v>18.293252175544318</v>
+        <v>60.977507251814394</v>
       </c>
       <c r="O25" s="1">
-        <v>17.660040308951043</v>
+        <v>58.866801029836807</v>
       </c>
       <c r="P25" s="1">
-        <v>15.442912095436805</v>
+        <v>51.476373651456015</v>
       </c>
       <c r="Q25" s="1">
-        <v>16.632461211684866</v>
+        <v>55.441537372282887</v>
       </c>
       <c r="R25" s="1">
-        <v>15.272799706644477</v>
+        <v>50.909332355481588</v>
       </c>
       <c r="S25" s="1">
-        <v>14.182813826408447</v>
+        <v>47.276046088028153</v>
       </c>
       <c r="T25" s="1">
-        <v>14.164548480875517</v>
+        <v>47.215161602918386</v>
       </c>
       <c r="U25" s="1">
-        <v>12.414944493699073</v>
+        <v>41.383148312330242</v>
       </c>
       <c r="V25" s="1">
-        <v>8.6229859711057912</v>
+        <v>28.743286570352637</v>
       </c>
       <c r="W25" s="1">
-        <v>8.9930811412316167</v>
+        <v>29.976937137438721</v>
       </c>
       <c r="X25" s="1">
-        <v>10.670336200802303</v>
+        <v>35.567787336007676</v>
       </c>
       <c r="Y25" s="1">
-        <v>11.719404508151808</v>
+        <v>39.064681693839361</v>
       </c>
       <c r="Z25" s="1">
-        <v>8.7650643345407993</v>
+        <v>29.216881115135994</v>
       </c>
       <c r="AA25" s="1">
-        <v>9.3150233100288009</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+        <v>31.050077700096001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -13148,79 +13163,79 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>5.2043895458021385</v>
+        <v>17.347965152673794</v>
       </c>
       <c r="E26" s="1">
-        <v>5.4302296655093762</v>
+        <v>18.100765551697922</v>
       </c>
       <c r="F26" s="1">
-        <v>4.4006816081479672</v>
+        <v>14.668938693826556</v>
       </c>
       <c r="G26" s="1">
-        <v>4.7517996088442889</v>
+        <v>15.839332029480962</v>
       </c>
       <c r="H26" s="1">
-        <v>3.4894526828249086</v>
+        <v>11.631508942749695</v>
       </c>
       <c r="I26" s="1">
-        <v>2.9289471809495042</v>
+        <v>9.7631572698316802</v>
       </c>
       <c r="J26" s="1">
-        <v>3.7308499136004101</v>
+        <v>12.436166378668034</v>
       </c>
       <c r="K26" s="1">
-        <v>0.5921614489190401</v>
+        <v>1.9738714963968003</v>
       </c>
       <c r="L26" s="1">
-        <v>0.61658299422719998</v>
+        <v>2.0552766474239998</v>
       </c>
       <c r="M26" s="1">
-        <v>0.78960362627727376</v>
+        <v>2.6320120875909123</v>
       </c>
       <c r="N26" s="1">
-        <v>0.44682580462141447</v>
+        <v>1.4894193487380483</v>
       </c>
       <c r="O26" s="1">
-        <v>0.58072060033228812</v>
+        <v>1.9357353344409605</v>
       </c>
       <c r="P26" s="1">
-        <v>0.87008072226816002</v>
+        <v>2.9002690742272002</v>
       </c>
       <c r="Q26" s="1">
-        <v>1.8112221419175933</v>
+        <v>6.0374071397253113</v>
       </c>
       <c r="R26" s="1">
-        <v>2.0719104203685887</v>
+        <v>6.9063680678952961</v>
       </c>
       <c r="S26" s="1">
-        <v>1.8631849009213441</v>
+        <v>6.2106163364044802</v>
       </c>
       <c r="T26" s="1">
-        <v>0.97428714679296036</v>
+        <v>3.247623822643201</v>
       </c>
       <c r="U26" s="1">
-        <v>2.0886401802239996</v>
+        <v>6.9621339340799979</v>
       </c>
       <c r="V26" s="1">
-        <v>1.2737108422950909</v>
+        <v>4.2457028076503027</v>
       </c>
       <c r="W26" s="1">
-        <v>0.91490276966399986</v>
+        <v>3.0496758988799999</v>
       </c>
       <c r="X26" s="1">
-        <v>1.1829053893902337</v>
+        <v>3.9430179646341124</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.83359447142400001</v>
+        <v>2.7786482380800002</v>
       </c>
       <c r="Z26" s="1">
-        <v>3.6916695429119994</v>
+        <v>12.305565143039999</v>
       </c>
       <c r="AA26" s="1">
-        <v>4.3595082318348286</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+        <v>14.531694106116097</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -13231,79 +13246,79 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-12.2181696</v>
+        <v>-40.727231999999994</v>
       </c>
       <c r="E27" s="1">
-        <v>-11.72015714009088</v>
+        <v>-39.067190466969599</v>
       </c>
       <c r="F27" s="1">
-        <v>-13.443861528163124</v>
+        <v>-44.812871760543743</v>
       </c>
       <c r="G27" s="1">
-        <v>-13.792520586520164</v>
+        <v>-45.975068621733875</v>
       </c>
       <c r="H27" s="1">
-        <v>-15.660613007769598</v>
+        <v>-52.202043359231993</v>
       </c>
       <c r="I27" s="1">
-        <v>-16.4075037819863</v>
+        <v>-54.691679273287662</v>
       </c>
       <c r="J27" s="1">
-        <v>-16.782459970977794</v>
+        <v>-55.941533236592647</v>
       </c>
       <c r="K27" s="1">
-        <v>-17.893595162911698</v>
+        <v>-59.645317209705659</v>
       </c>
       <c r="L27" s="1">
-        <v>-16.896622012779726</v>
+        <v>-56.322073375932426</v>
       </c>
       <c r="M27" s="1">
-        <v>-21.133926914899963</v>
+        <v>-70.446423049666535</v>
       </c>
       <c r="N27" s="1">
-        <v>-22.247605670584324</v>
+        <v>-74.158685568614416</v>
       </c>
       <c r="O27" s="1">
-        <v>-17.623866395366402</v>
+        <v>-58.746221317888008</v>
       </c>
       <c r="P27" s="1">
-        <v>-20.302427720680733</v>
+        <v>-67.674759068935771</v>
       </c>
       <c r="Q27" s="1">
-        <v>-19.587482458702478</v>
+        <v>-65.291608195674925</v>
       </c>
       <c r="R27" s="1">
-        <v>-19.818821928912822</v>
+        <v>-66.062739763042742</v>
       </c>
       <c r="S27" s="1">
-        <v>-16.642570682793366</v>
+        <v>-55.47523560931122</v>
       </c>
       <c r="T27" s="1">
-        <v>-17.70371840341279</v>
+        <v>-59.012394678042632</v>
       </c>
       <c r="U27" s="1">
-        <v>-15.23047461647942</v>
+        <v>-50.76824872159807</v>
       </c>
       <c r="V27" s="1">
-        <v>-8.7487358084122189</v>
+        <v>-29.162452694707397</v>
       </c>
       <c r="W27" s="1">
-        <v>-11.246523700059649</v>
+        <v>-37.48841233353216</v>
       </c>
       <c r="X27" s="1">
-        <v>-9.259101794202623</v>
+        <v>-30.863672647342074</v>
       </c>
       <c r="Y27" s="1">
-        <v>-12.034494614745906</v>
+        <v>-40.114982049153021</v>
       </c>
       <c r="Z27" s="1">
-        <v>-9.8601033430867986</v>
+        <v>-32.867011143622662</v>
       </c>
       <c r="AA27" s="1">
-        <v>-10.16913151328256</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-33.8971050442752</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -13314,79 +13329,79 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>9.5472166753183334</v>
+        <v>31.824055584394443</v>
       </c>
       <c r="E28" s="1">
-        <v>11.060380771231337</v>
+        <v>36.867935904104456</v>
       </c>
       <c r="F28" s="1">
-        <v>13.44006796593537</v>
+        <v>44.800226553117902</v>
       </c>
       <c r="G28" s="1">
-        <v>14.044689646401425</v>
+        <v>46.81563215467142</v>
       </c>
       <c r="H28" s="1">
-        <v>13.936271246924084</v>
+        <v>46.454237489746951</v>
       </c>
       <c r="I28" s="1">
-        <v>15.355875612819457</v>
+        <v>51.186252042731525</v>
       </c>
       <c r="J28" s="1">
-        <v>17.167886382366721</v>
+        <v>57.226287941222402</v>
       </c>
       <c r="K28" s="1">
-        <v>16.018603081999565</v>
+        <v>53.395343606665222</v>
       </c>
       <c r="L28" s="1">
-        <v>14.093942125146627</v>
+        <v>46.979807083822095</v>
       </c>
       <c r="M28" s="1">
-        <v>17.826869011660801</v>
+        <v>59.422896705536004</v>
       </c>
       <c r="N28" s="1">
-        <v>18.842049740810651</v>
+        <v>62.806832469368835</v>
       </c>
       <c r="O28" s="1">
-        <v>18.751976562222858</v>
+        <v>62.506588540742861</v>
       </c>
       <c r="P28" s="1">
-        <v>17.378596085760002</v>
+        <v>57.928653619199999</v>
       </c>
       <c r="Q28" s="1">
-        <v>16.781813924606116</v>
+        <v>55.939379748687053</v>
       </c>
       <c r="R28" s="1">
-        <v>14.36260255241011</v>
+        <v>47.875341841367032</v>
       </c>
       <c r="S28" s="1">
-        <v>12.205905407767018</v>
+        <v>40.686351359223394</v>
       </c>
       <c r="T28" s="1">
-        <v>12.818032318768433</v>
+        <v>42.726774395894779</v>
       </c>
       <c r="U28" s="1">
-        <v>12.295570027413502</v>
+        <v>40.985233424711673</v>
       </c>
       <c r="V28" s="1">
-        <v>9.4208299256040622</v>
+        <v>31.402766418680205</v>
       </c>
       <c r="W28" s="1">
-        <v>9.3620756045522526</v>
+        <v>31.206918681840843</v>
       </c>
       <c r="X28" s="1">
-        <v>11.553973417431244</v>
+        <v>38.513244724770814</v>
       </c>
       <c r="Y28" s="1">
-        <v>11.95156074756833</v>
+        <v>39.838535825227765</v>
       </c>
       <c r="Z28" s="1">
-        <v>8.4144617611591688</v>
+        <v>28.048205870530563</v>
       </c>
       <c r="AA28" s="1">
-        <v>9.7943588845240335</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+        <v>32.64786294841344</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -13397,79 +13412,79 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>4.9011230520705027</v>
+        <v>16.33707684023501</v>
       </c>
       <c r="E29" s="1">
-        <v>5.1537523271270409</v>
+        <v>17.179174423756802</v>
       </c>
       <c r="F29" s="1">
-        <v>4.1841603177873408</v>
+        <v>13.947201059291137</v>
       </c>
       <c r="G29" s="1">
-        <v>4.3777295725363192</v>
+        <v>14.592431908454396</v>
       </c>
       <c r="H29" s="1">
-        <v>3.4841761406779388</v>
+        <v>11.613920468926464</v>
       </c>
       <c r="I29" s="1">
-        <v>3.0172496253419525</v>
+        <v>10.057498751139841</v>
       </c>
       <c r="J29" s="1">
-        <v>3.4438614587080703</v>
+        <v>11.479538195693566</v>
       </c>
       <c r="K29" s="1">
-        <v>0.6468915222282241</v>
+        <v>2.1563050740940803</v>
       </c>
       <c r="L29" s="1">
-        <v>0.52600504320000008</v>
+        <v>1.7533501440000003</v>
       </c>
       <c r="M29" s="1">
-        <v>0.76536912818995206</v>
+        <v>2.5512304272998403</v>
       </c>
       <c r="N29" s="1">
-        <v>0.45543087371059188</v>
+        <v>1.5181029123686394</v>
       </c>
       <c r="O29" s="1">
-        <v>0.54125415176601599</v>
+        <v>1.80418050588672</v>
       </c>
       <c r="P29" s="1">
-        <v>1.0218833085726722</v>
+        <v>3.4062776952422404</v>
       </c>
       <c r="Q29" s="1">
-        <v>1.5897917414965246</v>
+        <v>5.299305804988415</v>
       </c>
       <c r="R29" s="1">
-        <v>1.7999652118855678</v>
+        <v>5.9998840396185598</v>
       </c>
       <c r="S29" s="1">
-        <v>1.6515221107507199</v>
+        <v>5.5050737025023997</v>
       </c>
       <c r="T29" s="1">
-        <v>0.94277849702400007</v>
+        <v>3.1425949900800005</v>
       </c>
       <c r="U29" s="1">
-        <v>1.962633746762956</v>
+        <v>6.5421124892098534</v>
       </c>
       <c r="V29" s="1">
-        <v>1.2991737373655039</v>
+        <v>4.3305791245516794</v>
       </c>
       <c r="W29" s="1">
-        <v>0.87778489254543357</v>
+        <v>2.9259496418181121</v>
       </c>
       <c r="X29" s="1">
-        <v>1.2696461298892798</v>
+        <v>4.232153766297599</v>
       </c>
       <c r="Y29" s="1">
-        <v>0.73833073606655997</v>
+        <v>2.4611024535552</v>
       </c>
       <c r="Z29" s="1">
-        <v>3.4050222607564797</v>
+        <v>11.350074202521599</v>
       </c>
       <c r="AA29" s="1">
-        <v>4.2300178883149826</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+        <v>14.100059627716609</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -13480,79 +13495,79 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-11.398656570163196</v>
+        <v>-37.995521900543984</v>
       </c>
       <c r="E30" s="1">
-        <v>-11.940635343716353</v>
+        <v>-39.802117812387841</v>
       </c>
       <c r="F30" s="1">
-        <v>-11.316635936686081</v>
+        <v>-37.722119788953606</v>
       </c>
       <c r="G30" s="1">
-        <v>-14.355652997932641</v>
+        <v>-47.852176659775466</v>
       </c>
       <c r="H30" s="1">
-        <v>-13.325562839826432</v>
+        <v>-44.418542799421438</v>
       </c>
       <c r="I30" s="1">
-        <v>-16.914952352563194</v>
+        <v>-56.383174508543981</v>
       </c>
       <c r="J30" s="1">
-        <v>-15.633641424420864</v>
+        <v>-52.112138081402883</v>
       </c>
       <c r="K30" s="1">
-        <v>-17.561791891844624</v>
+        <v>-58.539306306148745</v>
       </c>
       <c r="L30" s="1">
-        <v>-13.826938676812185</v>
+        <v>-46.089795589373949</v>
       </c>
       <c r="M30" s="1">
-        <v>-22.68243961970688</v>
+        <v>-75.608132065689603</v>
       </c>
       <c r="N30" s="1">
-        <v>-22.464158216182827</v>
+        <v>-74.880527387276089</v>
       </c>
       <c r="O30" s="1">
-        <v>-20.338224568082104</v>
+        <v>-67.794081893607014</v>
       </c>
       <c r="P30" s="1">
-        <v>-19.49587242725671</v>
+        <v>-64.986241424189032</v>
       </c>
       <c r="Q30" s="1">
-        <v>-20.189282215778061</v>
+        <v>-67.297607385926867</v>
       </c>
       <c r="R30" s="1">
-        <v>-17.397517892348809</v>
+        <v>-57.991726307829367</v>
       </c>
       <c r="S30" s="1">
-        <v>-18.725228265848827</v>
+        <v>-62.417427552829423</v>
       </c>
       <c r="T30" s="1">
-        <v>-14.941160147056069</v>
+        <v>-49.803867156853563</v>
       </c>
       <c r="U30" s="1">
-        <v>-13.231582507125967</v>
+        <v>-44.105275023753222</v>
       </c>
       <c r="V30" s="1">
-        <v>-8.4868824127714095</v>
+        <v>-28.289608042571363</v>
       </c>
       <c r="W30" s="1">
-        <v>-9.5970335573842362</v>
+        <v>-31.990111857947454</v>
       </c>
       <c r="X30" s="1">
-        <v>-10.671667760332799</v>
+        <v>-35.572225867775991</v>
       </c>
       <c r="Y30" s="1">
-        <v>-10.448837670076413</v>
+        <v>-34.829458900254714</v>
       </c>
       <c r="Z30" s="1">
-        <v>-9.4666458739507178</v>
+        <v>-31.555486246502394</v>
       </c>
       <c r="AA30" s="1">
-        <v>-9.2893405877895141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-30.964468625965043</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -13563,79 +13578,79 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>9.7359489849802738</v>
+        <v>32.453163283267578</v>
       </c>
       <c r="E31" s="1">
-        <v>10.738112716162991</v>
+        <v>35.793709053876633</v>
       </c>
       <c r="F31" s="1">
-        <v>12.021019241191832</v>
+        <v>40.070064137306105</v>
       </c>
       <c r="G31" s="1">
-        <v>14.293426314166277</v>
+        <v>47.644754380554254</v>
       </c>
       <c r="H31" s="1">
-        <v>13.792598347471255</v>
+        <v>45.975327824904184</v>
       </c>
       <c r="I31" s="1">
-        <v>16.958144420904961</v>
+        <v>56.5271480696832</v>
       </c>
       <c r="J31" s="1">
-        <v>15.397549336166399</v>
+        <v>51.325164453888</v>
       </c>
       <c r="K31" s="1">
-        <v>15.404174423359491</v>
+        <v>51.347248077864968</v>
       </c>
       <c r="L31" s="1">
-        <v>15.884680048725198</v>
+        <v>52.948933495750659</v>
       </c>
       <c r="M31" s="1">
-        <v>16.410863047635761</v>
+        <v>54.702876825452535</v>
       </c>
       <c r="N31" s="1">
-        <v>19.029513099018239</v>
+        <v>63.431710330060788</v>
       </c>
       <c r="O31" s="1">
-        <v>16.772078209440156</v>
+        <v>55.906927364800517</v>
       </c>
       <c r="P31" s="1">
-        <v>16.544423473643519</v>
+        <v>55.148078245478395</v>
       </c>
       <c r="Q31" s="1">
-        <v>15.325792948872804</v>
+        <v>51.085976496242687</v>
       </c>
       <c r="R31" s="1">
-        <v>14.213054420877311</v>
+        <v>47.376848069591034</v>
       </c>
       <c r="S31" s="1">
-        <v>13.208450377973758</v>
+        <v>44.028167926579194</v>
       </c>
       <c r="T31" s="1">
-        <v>12.696464737631603</v>
+        <v>42.321549125438672</v>
       </c>
       <c r="U31" s="1">
-        <v>10.57213003667079</v>
+        <v>35.240433455569303</v>
       </c>
       <c r="V31" s="1">
-        <v>7.8698196385136638</v>
+        <v>26.232732128378881</v>
       </c>
       <c r="W31" s="1">
-        <v>10.336929805762558</v>
+        <v>34.456432685875193</v>
       </c>
       <c r="X31" s="1">
-        <v>10.877527194992638</v>
+        <v>36.258423983308795</v>
       </c>
       <c r="Y31" s="1">
-        <v>10.707303956388248</v>
+        <v>35.691013187960827</v>
       </c>
       <c r="Z31" s="1">
-        <v>9.026330675281919</v>
+        <v>30.087768917606397</v>
       </c>
       <c r="AA31" s="1">
-        <v>8.6034967481548783</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+        <v>28.678322493849596</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -13646,79 +13661,79 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>4.9413105138165347</v>
+        <v>16.471035046055118</v>
       </c>
       <c r="E32" s="1">
-        <v>4.9652681517410553</v>
+        <v>16.550893839136851</v>
       </c>
       <c r="F32" s="1">
-        <v>4.6711159909961575</v>
+        <v>15.570386636653858</v>
       </c>
       <c r="G32" s="1">
-        <v>4.1250224424458652</v>
+        <v>13.750074808152883</v>
       </c>
       <c r="H32" s="1">
-        <v>3.3438205005004802</v>
+        <v>11.146068335001601</v>
       </c>
       <c r="I32" s="1">
-        <v>2.757191443348193</v>
+        <v>9.1906381444939758</v>
       </c>
       <c r="J32" s="1">
-        <v>3.2727119801540936</v>
+        <v>10.909039933846978</v>
       </c>
       <c r="K32" s="1">
-        <v>0.60273576050688016</v>
+        <v>2.0091192016896007</v>
       </c>
       <c r="L32" s="1">
-        <v>0.57456319876300821</v>
+        <v>1.9152106625433607</v>
       </c>
       <c r="M32" s="1">
-        <v>0.75815699602046971</v>
+        <v>2.527189986734899</v>
       </c>
       <c r="N32" s="1">
-        <v>0.43354838532095996</v>
+        <v>1.4451612844032</v>
       </c>
       <c r="O32" s="1">
-        <v>0.58048112791978002</v>
+        <v>1.9349370930659333</v>
       </c>
       <c r="P32" s="1">
-        <v>0.8529965044383746</v>
+        <v>2.8433216814612483</v>
       </c>
       <c r="Q32" s="1">
-        <v>1.5730905711346974</v>
+        <v>5.243635237115658</v>
       </c>
       <c r="R32" s="1">
-        <v>1.6763216849377687</v>
+        <v>5.5877389497925627</v>
       </c>
       <c r="S32" s="1">
-        <v>1.7368647286487779</v>
+        <v>5.7895490954959259</v>
       </c>
       <c r="T32" s="1">
-        <v>1.0654159596208128</v>
+        <v>3.551386532069376</v>
       </c>
       <c r="U32" s="1">
-        <v>1.8873562059991937</v>
+        <v>6.2911873533306455</v>
       </c>
       <c r="V32" s="1">
-        <v>1.0526214305014086</v>
+        <v>3.5087381016713621</v>
       </c>
       <c r="W32" s="1">
-        <v>0.81845259365184309</v>
+        <v>2.7281753121728105</v>
       </c>
       <c r="X32" s="1">
-        <v>1.2909173689810947</v>
+        <v>4.303057896603649</v>
       </c>
       <c r="Y32" s="1">
-        <v>0.76846668447744004</v>
+        <v>2.5615556149248002</v>
       </c>
       <c r="Z32" s="1">
-        <v>3.3709720381489148</v>
+        <v>11.236573460496382</v>
       </c>
       <c r="AA32" s="1">
-        <v>4.5284457176975277</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+        <v>15.09481905899176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -13729,79 +13744,79 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-9.7792833116159983</v>
+        <v>-32.597611038719997</v>
       </c>
       <c r="E33" s="1">
-        <v>-10.686708222787583</v>
+        <v>-35.622360742625283</v>
       </c>
       <c r="F33" s="1">
-        <v>-13.574384455621018</v>
+        <v>-45.247948185403395</v>
       </c>
       <c r="G33" s="1">
-        <v>-13.102894557194158</v>
+        <v>-43.676315190647195</v>
       </c>
       <c r="H33" s="1">
-        <v>-14.888225492434945</v>
+        <v>-49.627418308116482</v>
       </c>
       <c r="I33" s="1">
-        <v>-16.407503781986303</v>
+        <v>-54.691679273287683</v>
       </c>
       <c r="J33" s="1">
-        <v>-16.462794066768694</v>
+        <v>-54.875980222562312</v>
       </c>
       <c r="K33" s="1">
-        <v>-18.436371133974177</v>
+        <v>-61.45457044658059</v>
       </c>
       <c r="L33" s="1">
-        <v>-15.602880658665111</v>
+        <v>-52.009602195550372</v>
       </c>
       <c r="M33" s="1">
-        <v>-21.769253324632722</v>
+        <v>-72.564177748775748</v>
       </c>
       <c r="N33" s="1">
-        <v>-21.370653354885121</v>
+        <v>-71.235511182950404</v>
       </c>
       <c r="O33" s="1">
-        <v>-21.561171040111955</v>
+        <v>-71.870570133706522</v>
       </c>
       <c r="P33" s="1">
-        <v>-18.341262506807524</v>
+        <v>-61.137541689358414</v>
       </c>
       <c r="Q33" s="1">
-        <v>-19.172758915403225</v>
+        <v>-63.909196384677415</v>
       </c>
       <c r="R33" s="1">
-        <v>-17.713197243072774</v>
+        <v>-59.043990810242576</v>
       </c>
       <c r="S33" s="1">
-        <v>-17.4802732836689</v>
+        <v>-58.267577612229672</v>
       </c>
       <c r="T33" s="1">
-        <v>-16.665558605775768</v>
+        <v>-55.55186201925256</v>
       </c>
       <c r="U33" s="1">
-        <v>-15.833102071856787</v>
+        <v>-52.777006906189293</v>
       </c>
       <c r="V33" s="1">
-        <v>-7.6719683242999475</v>
+        <v>-25.573227747666493</v>
       </c>
       <c r="W33" s="1">
-        <v>-9.6795600595420428</v>
+        <v>-32.265200198473472</v>
       </c>
       <c r="X33" s="1">
-        <v>-10.149564185790378</v>
+        <v>-33.831880619301266</v>
       </c>
       <c r="Y33" s="1">
-        <v>-11.337815115072994</v>
+        <v>-37.792717050243311</v>
       </c>
       <c r="Z33" s="1">
-        <v>-8.7332841190242387</v>
+        <v>-29.11094706341413</v>
       </c>
       <c r="AA33" s="1">
-        <v>-9.3671837917155152</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-31.223945972385053</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -13812,79 +13827,79 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>9.5392631468998665</v>
+        <v>31.797543822999558</v>
       </c>
       <c r="E34" s="1">
-        <v>12.086482192778133</v>
+        <v>40.288273975927112</v>
       </c>
       <c r="F34" s="1">
-        <v>13.424194399525799</v>
+        <v>44.747314665086002</v>
       </c>
       <c r="G34" s="1">
-        <v>13.890332245268263</v>
+        <v>46.301107484227543</v>
       </c>
       <c r="H34" s="1">
-        <v>12.593142201222953</v>
+        <v>41.977140670743175</v>
       </c>
       <c r="I34" s="1">
-        <v>16.949637364957837</v>
+        <v>56.498791216526122</v>
       </c>
       <c r="J34" s="1">
-        <v>16.49544033913012</v>
+        <v>54.984801130433731</v>
       </c>
       <c r="K34" s="1">
-        <v>15.675881430343681</v>
+        <v>52.25293810114561</v>
       </c>
       <c r="L34" s="1">
-        <v>14.219843389772269</v>
+        <v>47.399477965907558</v>
       </c>
       <c r="M34" s="1">
-        <v>16.580657199392807</v>
+        <v>55.268857331309356</v>
       </c>
       <c r="N34" s="1">
-        <v>18.439598192948672</v>
+        <v>61.465327309828901</v>
       </c>
       <c r="O34" s="1">
-        <v>17.631784244456718</v>
+        <v>58.772614148189064</v>
       </c>
       <c r="P34" s="1">
-        <v>14.528691699386945</v>
+        <v>48.42897233128982</v>
       </c>
       <c r="Q34" s="1">
-        <v>15.647819507953123</v>
+        <v>52.159398359843749</v>
       </c>
       <c r="R34" s="1">
-        <v>14.222031086827338</v>
+        <v>47.406770289424458</v>
       </c>
       <c r="S34" s="1">
-        <v>13.615501273352109</v>
+        <v>45.38500424450703</v>
       </c>
       <c r="T34" s="1">
-        <v>13.054047879974876</v>
+        <v>43.513492933249587</v>
       </c>
       <c r="U34" s="1">
-        <v>11.918346713951109</v>
+        <v>39.727822379837029</v>
       </c>
       <c r="V34" s="1">
-        <v>7.8641632056484818</v>
+        <v>26.213877352161607</v>
       </c>
       <c r="W34" s="1">
-        <v>8.7196914745381751</v>
+        <v>29.065638248460584</v>
       </c>
       <c r="X34" s="1">
-        <v>9.8337818426594019</v>
+        <v>32.779272808864675</v>
       </c>
       <c r="Y34" s="1">
-        <v>11.13812204454748</v>
+        <v>37.12707348182493</v>
       </c>
       <c r="Z34" s="1">
-        <v>8.3303171435475765</v>
+        <v>27.767723811825253</v>
       </c>
       <c r="AA34" s="1">
-        <v>8.6741497062988202</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+        <v>28.913832354329401</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -13895,79 +13910,79 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>5.0461761036097537</v>
+        <v>16.820587012032512</v>
       </c>
       <c r="E35" s="1">
-        <v>5.4215412980445601</v>
+        <v>18.071804326815201</v>
       </c>
       <c r="F35" s="1">
-        <v>4.3513939741367098</v>
+        <v>14.504646580455699</v>
       </c>
       <c r="G35" s="1">
-        <v>4.470493072000707</v>
+        <v>14.90164357333569</v>
       </c>
       <c r="H35" s="1">
-        <v>3.5173683042875075</v>
+        <v>11.724561014291693</v>
       </c>
       <c r="I35" s="1">
-        <v>2.8680250795857547</v>
+        <v>9.5600835986191814</v>
       </c>
       <c r="J35" s="1">
-        <v>3.6532482353975215</v>
+        <v>12.177494117991737</v>
       </c>
       <c r="K35" s="1">
-        <v>0.55710549114303287</v>
+        <v>1.8570183038101096</v>
       </c>
       <c r="L35" s="1">
-        <v>0.56824288747978757</v>
+        <v>1.8941429582659586</v>
       </c>
       <c r="M35" s="1">
-        <v>0.72011850716487358</v>
+        <v>2.4003950238829117</v>
       </c>
       <c r="N35" s="1">
-        <v>0.41179466153909561</v>
+        <v>1.3726488717969854</v>
       </c>
       <c r="O35" s="1">
-        <v>0.5407670230294267</v>
+        <v>1.8025567434314222</v>
       </c>
       <c r="P35" s="1">
-        <v>0.83527749337743362</v>
+        <v>2.7842583112581121</v>
       </c>
       <c r="Q35" s="1">
-        <v>1.7909364539281163</v>
+        <v>5.9697881797603882</v>
       </c>
       <c r="R35" s="1">
-        <v>2.0884857037315374</v>
+        <v>6.961619012438458</v>
       </c>
       <c r="S35" s="1">
-        <v>1.7886575048844904</v>
+        <v>5.9621916829483013</v>
       </c>
       <c r="T35" s="1">
-        <v>0.93531566092124185</v>
+        <v>3.1177188697374731</v>
       </c>
       <c r="U35" s="1">
-        <v>2.0050945730150396</v>
+        <v>6.6836485767167986</v>
       </c>
       <c r="V35" s="1">
-        <v>1.2349900326893202</v>
+        <v>4.1166334422977338</v>
       </c>
       <c r="W35" s="1">
-        <v>0.85195745911111675</v>
+        <v>2.839858197037056</v>
       </c>
       <c r="X35" s="1">
-        <v>1.1810127407672091</v>
+        <v>3.9367091358906969</v>
       </c>
       <c r="Y35" s="1">
-        <v>0.76824066486435838</v>
+        <v>2.5608022162145279</v>
       </c>
       <c r="Z35" s="1">
-        <v>3.6857628716433402</v>
+        <v>12.285876238811134</v>
       </c>
       <c r="AA35" s="1">
-        <v>4.2688304606126639</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+        <v>14.229434868708879</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -13978,79 +13993,79 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-11.260265103359998</v>
+        <v>-37.534217011199992</v>
       </c>
       <c r="E36" s="1">
-        <v>-11.813918397211605</v>
+        <v>-39.379727990705355</v>
       </c>
       <c r="F36" s="1">
-        <v>-13.422351349718063</v>
+        <v>-44.741171165726882</v>
       </c>
       <c r="G36" s="1">
-        <v>-12.843595170167575</v>
+        <v>-42.81198390055858</v>
       </c>
       <c r="H36" s="1">
-        <v>-14.883846602584224</v>
+        <v>-49.612822008614081</v>
       </c>
       <c r="I36" s="1">
-        <v>-15.908715667013917</v>
+        <v>-53.029052223379722</v>
       </c>
       <c r="J36" s="1">
-        <v>-16.433384803581454</v>
+        <v>-54.777949345271509</v>
       </c>
       <c r="K36" s="1">
-        <v>-16.662515815703372</v>
+        <v>-55.541719385677908</v>
       </c>
       <c r="L36" s="1">
-        <v>-16.545172274913909</v>
+        <v>-55.150574249713031</v>
       </c>
       <c r="M36" s="1">
-        <v>-20.085684139920925</v>
+        <v>-66.952280466403082</v>
       </c>
       <c r="N36" s="1">
-        <v>-20.289816371572904</v>
+        <v>-67.632721238576337</v>
       </c>
       <c r="O36" s="1">
-        <v>-17.595668209133816</v>
+        <v>-58.652227363779389</v>
       </c>
       <c r="P36" s="1">
-        <v>-20.075040530209105</v>
+        <v>-66.91680176736368</v>
       </c>
       <c r="Q36" s="1">
-        <v>-18.051823833940201</v>
+        <v>-60.172746113134004</v>
       </c>
       <c r="R36" s="1">
-        <v>-18.074765599168494</v>
+        <v>-60.249218663894986</v>
       </c>
       <c r="S36" s="1">
-        <v>-16.136636534036448</v>
+        <v>-53.788788446788168</v>
       </c>
       <c r="T36" s="1">
-        <v>-17.67539245396733</v>
+        <v>-58.917974846557769</v>
       </c>
       <c r="U36" s="1">
-        <v>-15.352318413411254</v>
+        <v>-51.174394711370844</v>
       </c>
       <c r="V36" s="1">
-        <v>-8.7347378311187587</v>
+        <v>-29.11579277039586</v>
       </c>
       <c r="W36" s="1">
-        <v>-10.580729497016115</v>
+        <v>-35.269098323387048</v>
       </c>
       <c r="X36" s="1">
-        <v>-8.977625099658864</v>
+        <v>-29.925416998862882</v>
       </c>
       <c r="Y36" s="1">
-        <v>-11.553114830156069</v>
+        <v>-38.510382767186897</v>
       </c>
       <c r="Z36" s="1">
-        <v>-8.9924142488951588</v>
+        <v>-29.974714162983862</v>
       </c>
       <c r="AA36" s="1">
-        <v>-9.9576135778062813</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-33.192045259354273</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -14061,76 +14076,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>8.8903681680564315</v>
+        <v>29.634560560188106</v>
       </c>
       <c r="E37" s="1">
-        <v>11.042684161997368</v>
+        <v>36.808947206657898</v>
       </c>
       <c r="F37" s="1">
-        <v>12.257341984933056</v>
+        <v>40.857806616443519</v>
       </c>
       <c r="G37" s="1">
-        <v>13.078414998729006</v>
+        <v>43.594716662430017</v>
       </c>
       <c r="H37" s="1">
-        <v>14.047761416899474</v>
+        <v>46.825871389664911</v>
       </c>
       <c r="I37" s="1">
-        <v>15.036473400072811</v>
+        <v>50.1215780002427</v>
       </c>
       <c r="J37" s="1">
-        <v>16.316359217801331</v>
+        <v>54.387864059337772</v>
       </c>
       <c r="K37" s="1">
-        <v>16.14675190665556</v>
+        <v>53.822506355518534</v>
       </c>
       <c r="L37" s="1">
-        <v>12.853675218133723</v>
+        <v>42.845584060445752</v>
       </c>
       <c r="M37" s="1">
-        <v>16.600380423658535</v>
+        <v>55.33460141219512</v>
       </c>
       <c r="N37" s="1">
-        <v>18.992786138737138</v>
+        <v>63.309287129123788</v>
       </c>
       <c r="O37" s="1">
-        <v>18.36193544972862</v>
+        <v>61.206451499095401</v>
       </c>
       <c r="P37" s="1">
-        <v>16.850286764752898</v>
+        <v>56.167622549176322</v>
       </c>
       <c r="Q37" s="1">
-        <v>16.754963022326745</v>
+        <v>55.849876741089155</v>
       </c>
       <c r="R37" s="1">
-        <v>14.201741403823116</v>
+        <v>47.339138012743717</v>
       </c>
       <c r="S37" s="1">
-        <v>11.366139115712647</v>
+        <v>37.887130385708822</v>
       </c>
       <c r="T37" s="1">
-        <v>12.305311026017694</v>
+        <v>41.017703420058979</v>
       </c>
       <c r="U37" s="1">
-        <v>11.567672281790621</v>
+        <v>38.558907605968734</v>
       </c>
       <c r="V37" s="1">
-        <v>9.0439967285798986</v>
+        <v>30.146655761932994</v>
       </c>
       <c r="W37" s="1">
-        <v>9.436972209388669</v>
+        <v>31.456574031295563</v>
       </c>
       <c r="X37" s="1">
-        <v>11.535487059963355</v>
+        <v>38.451623533211183</v>
       </c>
       <c r="Y37" s="1">
-        <v>11.702968284018906</v>
+        <v>39.009894280063023</v>
       </c>
       <c r="Z37" s="1">
-        <v>7.916325624898545</v>
+        <v>26.387752082995149</v>
       </c>
       <c r="AA37" s="1">
-        <v>9.6846620650173634</v>
+        <v>32.282206883391211</v>
       </c>
     </row>
   </sheetData>

--- a/data/CS7/case9/case9_operational_data.xlsx
+++ b/data/CS7/case9/case9_operational_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case9/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B67E7D-4B4B-734D-963C-F055D9A87923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A64C71-3F13-5649-BE46-8E31DD3BC0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -454,7 +454,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C2" s="1">
         <v>30</v>
@@ -475,10 +475,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2">
         <f t="shared" ref="D3:D4" si="0">1/COUNT($A$2:$A$4)</f>
@@ -496,10 +496,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="C4" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" si="0"/>
@@ -11171,76 +11171,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>16.388000000000002</v>
+        <v>20.485000000000003</v>
       </c>
       <c r="E2" s="1">
-        <v>16.934666666666669</v>
+        <v>21.168333333333337</v>
       </c>
       <c r="F2" s="1">
-        <v>15.164</v>
+        <v>18.954999999999998</v>
       </c>
       <c r="G2" s="1">
-        <v>14.373333333333335</v>
+        <v>17.966666666666669</v>
       </c>
       <c r="H2" s="1">
-        <v>11.776000000000002</v>
+        <v>14.720000000000002</v>
       </c>
       <c r="I2" s="1">
-        <v>9.9946666666666673</v>
+        <v>12.493333333333334</v>
       </c>
       <c r="J2" s="1">
-        <v>12.222666666666667</v>
+        <v>15.278333333333334</v>
       </c>
       <c r="K2" s="1">
-        <v>2.1226666666666669</v>
+        <v>2.6533333333333338</v>
       </c>
       <c r="L2" s="1">
-        <v>1.8666666666666669</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="M2" s="1">
-        <v>2.7213333333333334</v>
+        <v>3.4016666666666668</v>
       </c>
       <c r="N2" s="1">
-        <v>1.6026666666666667</v>
+        <v>2.0033333333333334</v>
       </c>
       <c r="O2" s="1">
-        <v>2.0026666666666668</v>
+        <v>2.5033333333333334</v>
       </c>
       <c r="P2" s="1">
-        <v>3.190666666666667</v>
+        <v>3.9883333333333337</v>
       </c>
       <c r="Q2" s="1">
-        <v>5.8786666666666667</v>
+        <v>7.3483333333333336</v>
       </c>
       <c r="R2" s="1">
-        <v>6.2719999999999994</v>
+        <v>7.839999999999999</v>
       </c>
       <c r="S2" s="1">
-        <v>6.1680000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="T2" s="1">
-        <v>3.4600000000000004</v>
+        <v>4.3250000000000002</v>
       </c>
       <c r="U2" s="1">
-        <v>7.0479999999999992</v>
+        <v>8.8099999999999987</v>
       </c>
       <c r="V2" s="1">
-        <v>4.1360000000000001</v>
+        <v>5.17</v>
       </c>
       <c r="W2" s="1">
-        <v>2.9079999999999999</v>
+        <v>3.6349999999999998</v>
       </c>
       <c r="X2" s="1">
-        <v>4.4159999999999995</v>
+        <v>5.52</v>
       </c>
       <c r="Y2" s="1">
-        <v>2.7293333333333329</v>
+        <v>3.4116666666666662</v>
       </c>
       <c r="Z2" s="1">
-        <v>12.457333333333333</v>
+        <v>15.571666666666665</v>
       </c>
       <c r="AA2" s="1">
-        <v>15.017333333333335</v>
+        <v>18.771666666666668</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -11254,76 +11254,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-37</v>
+        <v>-46.25</v>
       </c>
       <c r="E3" s="1">
-        <v>-39.565333333333335</v>
+        <v>-49.456666666666671</v>
       </c>
       <c r="F3" s="1">
-        <v>-44.498666666666672</v>
+        <v>-55.623333333333342</v>
       </c>
       <c r="G3" s="1">
-        <v>-48.001333333333328</v>
+        <v>-60.001666666666658</v>
       </c>
       <c r="H3" s="1">
-        <v>-51.306666666666665</v>
+        <v>-64.133333333333326</v>
       </c>
       <c r="I3" s="1">
-        <v>-55.993333333333332</v>
+        <v>-69.99166666666666</v>
       </c>
       <c r="J3" s="1">
-        <v>-53.428000000000004</v>
+        <v>-66.785000000000011</v>
       </c>
       <c r="K3" s="1">
-        <v>-59.932533333333332</v>
+        <v>-74.915666666666667</v>
       </c>
       <c r="L3" s="1">
-        <v>-54.357866666666666</v>
+        <v>-67.947333333333333</v>
       </c>
       <c r="M3" s="1">
-        <v>-79.842799999999997</v>
+        <v>-99.8035</v>
       </c>
       <c r="N3" s="1">
-        <v>-79.024533333333338</v>
+        <v>-98.780666666666676</v>
       </c>
       <c r="O3" s="1">
-        <v>-72.240533333333346</v>
+        <v>-90.300666666666686</v>
       </c>
       <c r="P3" s="1">
-        <v>-69.248533333333341</v>
+        <v>-86.560666666666677</v>
       </c>
       <c r="Q3" s="1">
-        <v>-66.858266666666665</v>
+        <v>-83.572833333333335</v>
       </c>
       <c r="R3" s="1">
-        <v>-63.018933333333337</v>
+        <v>-78.773666666666671</v>
       </c>
       <c r="S3" s="1">
-        <v>-57.347466666666662</v>
+        <v>-71.684333333333328</v>
       </c>
       <c r="T3" s="1">
-        <v>-53.623200000000004</v>
+        <v>-67.029000000000011</v>
       </c>
       <c r="U3" s="1">
-        <v>-47.98746666666667</v>
+        <v>-59.984333333333339</v>
       </c>
       <c r="V3" s="1">
-        <v>-30.459066666666669</v>
+        <v>-38.073833333333333</v>
       </c>
       <c r="W3" s="1">
-        <v>-34.088266666666669</v>
+        <v>-42.610333333333337</v>
       </c>
       <c r="X3" s="1">
-        <v>-36.032800000000002</v>
+        <v>-45.041000000000004</v>
       </c>
       <c r="Y3" s="1">
-        <v>-38.684666666666665</v>
+        <v>-48.355833333333329</v>
       </c>
       <c r="Z3" s="1">
-        <v>-30.734666666666666</v>
+        <v>-38.418333333333329</v>
       </c>
       <c r="AA3" s="1">
-        <v>-32.658666666666669</v>
+        <v>-40.823333333333338</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -11337,76 +11337,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>35.645199999999996</v>
+        <v>44.556499999999993</v>
       </c>
       <c r="E4" s="1">
-        <v>38.134399999999999</v>
+        <v>47.667999999999999</v>
       </c>
       <c r="F4" s="1">
-        <v>42.757466666666666</v>
+        <v>53.446833333333331</v>
       </c>
       <c r="G4" s="1">
-        <v>46.00813333333334</v>
+        <v>57.510166666666677</v>
       </c>
       <c r="H4" s="1">
-        <v>48.971333333333327</v>
+        <v>61.214166666666657</v>
       </c>
       <c r="I4" s="1">
-        <v>53.473333333333336</v>
+        <v>66.841666666666669</v>
       </c>
       <c r="J4" s="1">
-        <v>50.98</v>
+        <v>63.724999999999994</v>
       </c>
       <c r="K4" s="1">
-        <v>57.530533333333345</v>
+        <v>71.913166666666683</v>
       </c>
       <c r="L4" s="1">
-        <v>52.697200000000002</v>
+        <v>65.871499999999997</v>
       </c>
       <c r="M4" s="1">
-        <v>60.131466666666661</v>
+        <v>75.164333333333332</v>
       </c>
       <c r="N4" s="1">
-        <v>60.604933333333328</v>
+        <v>75.756166666666658</v>
       </c>
       <c r="O4" s="1">
-        <v>56.73213333333333</v>
+        <v>70.915166666666664</v>
       </c>
       <c r="P4" s="1">
-        <v>54.82</v>
+        <v>68.525000000000006</v>
       </c>
       <c r="Q4" s="1">
-        <v>53.410933333333332</v>
+        <v>66.763666666666666</v>
       </c>
       <c r="R4" s="1">
-        <v>50.054400000000008</v>
+        <v>62.568000000000012</v>
       </c>
       <c r="S4" s="1">
-        <v>45.571599999999997</v>
+        <v>56.964499999999994</v>
       </c>
       <c r="T4" s="1">
-        <v>42.453466666666664</v>
+        <v>53.066833333333328</v>
       </c>
       <c r="U4" s="1">
-        <v>37.942933333333336</v>
+        <v>47.428666666666672</v>
       </c>
       <c r="V4" s="1">
-        <v>29.697866666666666</v>
+        <v>37.12233333333333</v>
       </c>
       <c r="W4" s="1">
-        <v>33.240533333333339</v>
+        <v>41.550666666666672</v>
       </c>
       <c r="X4" s="1">
-        <v>35.321866666666665</v>
+        <v>44.152333333333331</v>
       </c>
       <c r="Y4" s="1">
-        <v>38.048533333333332</v>
+        <v>47.560666666666663</v>
       </c>
       <c r="Z4" s="1">
-        <v>29.606666666666666</v>
+        <v>37.008333333333333</v>
       </c>
       <c r="AA4" s="1">
-        <v>31.48266666666667</v>
+        <v>39.353333333333339</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -11420,76 +11420,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>16.551880000000001</v>
+        <v>20.68985</v>
       </c>
       <c r="E5" s="1">
-        <v>16.595973333333333</v>
+        <v>20.744966666666667</v>
       </c>
       <c r="F5" s="1">
-        <v>15.012359999999999</v>
+        <v>18.765449999999998</v>
       </c>
       <c r="G5" s="1">
-        <v>14.804533333333334</v>
+        <v>18.505666666666666</v>
       </c>
       <c r="H5" s="1">
-        <v>11.658240000000001</v>
+        <v>14.572800000000001</v>
       </c>
       <c r="I5" s="1">
-        <v>9.8947200000000013</v>
+        <v>12.368400000000001</v>
       </c>
       <c r="J5" s="1">
-        <v>12.344893333333331</v>
+        <v>15.431116666666664</v>
       </c>
       <c r="K5" s="1">
-        <v>2.1014400000000002</v>
+        <v>2.6268000000000002</v>
       </c>
       <c r="L5" s="1">
-        <v>1.922666666666667</v>
+        <v>2.4033333333333338</v>
       </c>
       <c r="M5" s="1">
-        <v>2.7485466666666674</v>
+        <v>3.4356833333333343</v>
       </c>
       <c r="N5" s="1">
-        <v>1.5385600000000001</v>
+        <v>1.9232000000000002</v>
       </c>
       <c r="O5" s="1">
-        <v>2.0427200000000001</v>
+        <v>2.5533999999999999</v>
       </c>
       <c r="P5" s="1">
-        <v>3.0311333333333335</v>
+        <v>3.7889166666666667</v>
       </c>
       <c r="Q5" s="1">
-        <v>5.6435199999999996</v>
+        <v>7.0543999999999993</v>
       </c>
       <c r="R5" s="1">
-        <v>6.5228799999999998</v>
+        <v>8.1535999999999991</v>
       </c>
       <c r="S5" s="1">
-        <v>6.1063200000000002</v>
+        <v>7.6329000000000002</v>
       </c>
       <c r="T5" s="1">
-        <v>3.5292000000000008</v>
+        <v>4.4115000000000011</v>
       </c>
       <c r="U5" s="1">
-        <v>6.8365599999999986</v>
+        <v>8.5456999999999983</v>
       </c>
       <c r="V5" s="1">
-        <v>4.0532799999999991</v>
+        <v>5.0665999999999993</v>
       </c>
       <c r="W5" s="1">
-        <v>2.9370799999999999</v>
+        <v>3.6713499999999999</v>
       </c>
       <c r="X5" s="1">
-        <v>4.32768</v>
+        <v>5.4096000000000002</v>
       </c>
       <c r="Y5" s="1">
-        <v>2.7293333333333329</v>
+        <v>3.4116666666666662</v>
       </c>
       <c r="Z5" s="1">
-        <v>12.083613333333332</v>
+        <v>15.104516666666665</v>
       </c>
       <c r="AA5" s="1">
-        <v>14.416640000000001</v>
+        <v>18.020800000000001</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -11503,76 +11503,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-38.85</v>
+        <v>-48.5625</v>
       </c>
       <c r="E6" s="1">
-        <v>-39.565333333333335</v>
+        <v>-49.456666666666671</v>
       </c>
       <c r="F6" s="1">
-        <v>-44.943653333333337</v>
+        <v>-56.179566666666673</v>
       </c>
       <c r="G6" s="1">
-        <v>-48.481346666666667</v>
+        <v>-60.601683333333334</v>
       </c>
       <c r="H6" s="1">
-        <v>-52.332799999999999</v>
+        <v>-65.415999999999997</v>
       </c>
       <c r="I6" s="1">
-        <v>-57.113199999999999</v>
+        <v>-71.391499999999994</v>
       </c>
       <c r="J6" s="1">
-        <v>-54.496560000000009</v>
+        <v>-68.120700000000014</v>
       </c>
       <c r="K6" s="1">
-        <v>-62.329834666666663</v>
+        <v>-77.912293333333324</v>
       </c>
       <c r="L6" s="1">
-        <v>-51.63997333333333</v>
+        <v>-64.549966666666663</v>
       </c>
       <c r="M6" s="1">
-        <v>-75.850660000000005</v>
+        <v>-94.813325000000006</v>
       </c>
       <c r="N6" s="1">
-        <v>-79.024533333333352</v>
+        <v>-98.78066666666669</v>
       </c>
       <c r="O6" s="1">
-        <v>-68.628506666666667</v>
+        <v>-85.785633333333337</v>
       </c>
       <c r="P6" s="1">
-        <v>-67.863562666666667</v>
+        <v>-84.829453333333333</v>
       </c>
       <c r="Q6" s="1">
-        <v>-64.183936000000003</v>
+        <v>-80.229920000000007</v>
       </c>
       <c r="R6" s="1">
-        <v>-65.539690666666672</v>
+        <v>-81.92461333333334</v>
       </c>
       <c r="S6" s="1">
-        <v>-58.494416000000001</v>
+        <v>-73.118020000000001</v>
       </c>
       <c r="T6" s="1">
-        <v>-56.30436000000001</v>
+        <v>-70.38045000000001</v>
       </c>
       <c r="U6" s="1">
-        <v>-49.906965333333339</v>
+        <v>-62.383706666666676</v>
       </c>
       <c r="V6" s="1">
-        <v>-29.545294666666663</v>
+        <v>-36.931618333333333</v>
       </c>
       <c r="W6" s="1">
-        <v>-33.065618666666673</v>
+        <v>-41.332023333333339</v>
       </c>
       <c r="X6" s="1">
-        <v>-35.312143999999996</v>
+        <v>-44.140179999999994</v>
       </c>
       <c r="Y6" s="1">
-        <v>-39.071513333333336</v>
+        <v>-48.839391666666671</v>
       </c>
       <c r="Z6" s="1">
-        <v>-31.964053333333336</v>
+        <v>-39.955066666666667</v>
       </c>
       <c r="AA6" s="1">
-        <v>-33.965013333333332</v>
+        <v>-42.456266666666664</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -11586,76 +11586,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>34.575843999999996</v>
+        <v>43.219804999999994</v>
       </c>
       <c r="E7" s="1">
-        <v>39.659776000000001</v>
+        <v>49.574719999999999</v>
       </c>
       <c r="F7" s="1">
-        <v>44.46776533333334</v>
+        <v>55.584706666666676</v>
       </c>
       <c r="G7" s="1">
-        <v>46.468214666666675</v>
+        <v>58.085268333333346</v>
       </c>
       <c r="H7" s="1">
-        <v>47.502193333333338</v>
+        <v>59.377741666666672</v>
       </c>
       <c r="I7" s="1">
-        <v>55.612266666666677</v>
+        <v>69.515333333333345</v>
       </c>
       <c r="J7" s="1">
-        <v>53.019200000000005</v>
+        <v>66.274000000000001</v>
       </c>
       <c r="K7" s="1">
-        <v>54.654006666666675</v>
+        <v>68.317508333333336</v>
       </c>
       <c r="L7" s="1">
-        <v>50.062340000000006</v>
+        <v>62.577925000000008</v>
       </c>
       <c r="M7" s="1">
-        <v>58.928837333333341</v>
+        <v>73.661046666666678</v>
       </c>
       <c r="N7" s="1">
-        <v>63.029130666666667</v>
+        <v>78.786413333333329</v>
       </c>
       <c r="O7" s="1">
-        <v>57.299454666666669</v>
+        <v>71.624318333333335</v>
       </c>
       <c r="P7" s="1">
-        <v>52.627200000000009</v>
+        <v>65.784000000000006</v>
       </c>
       <c r="Q7" s="1">
-        <v>55.013261333333332</v>
+        <v>68.766576666666666</v>
       </c>
       <c r="R7" s="1">
-        <v>49.053311999999998</v>
+        <v>61.31664</v>
       </c>
       <c r="S7" s="1">
-        <v>44.204452000000003</v>
+        <v>55.255565000000004</v>
       </c>
       <c r="T7" s="1">
-        <v>43.727070666666656</v>
+        <v>54.658838333333321</v>
       </c>
       <c r="U7" s="1">
-        <v>39.460650666666666</v>
+        <v>49.325813333333329</v>
       </c>
       <c r="V7" s="1">
-        <v>30.291824000000002</v>
+        <v>37.864780000000003</v>
       </c>
       <c r="W7" s="1">
-        <v>32.243317333333337</v>
+        <v>40.304146666666668</v>
       </c>
       <c r="X7" s="1">
-        <v>36.028303999999999</v>
+        <v>45.035379999999996</v>
       </c>
       <c r="Y7" s="1">
-        <v>36.526592000000001</v>
+        <v>45.658239999999999</v>
       </c>
       <c r="Z7" s="1">
-        <v>29.310599999999997</v>
+        <v>36.638249999999999</v>
       </c>
       <c r="AA7" s="1">
-        <v>30.853013333333337</v>
+        <v>38.566266666666671</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -11669,76 +11669,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>17.213955200000004</v>
+        <v>21.517444000000005</v>
       </c>
       <c r="E8" s="1">
-        <v>16.927892799999999</v>
+        <v>21.159865999999997</v>
       </c>
       <c r="F8" s="1">
-        <v>15.3126072</v>
+        <v>19.140758999999999</v>
       </c>
       <c r="G8" s="1">
-        <v>15.248669333333334</v>
+        <v>19.060836666666667</v>
       </c>
       <c r="H8" s="1">
-        <v>11.541657600000001</v>
+        <v>14.427072000000001</v>
       </c>
       <c r="I8" s="1">
-        <v>9.3999840000000017</v>
+        <v>11.749980000000003</v>
       </c>
       <c r="J8" s="1">
-        <v>12.838689066666667</v>
+        <v>16.048361333333332</v>
       </c>
       <c r="K8" s="1">
-        <v>2.0173824000000002</v>
+        <v>2.5217280000000004</v>
       </c>
       <c r="L8" s="1">
-        <v>2.0188000000000001</v>
+        <v>2.5235000000000003</v>
       </c>
       <c r="M8" s="1">
-        <v>2.6386048</v>
+        <v>3.2982559999999999</v>
       </c>
       <c r="N8" s="1">
-        <v>1.5077888000000002</v>
+        <v>1.8847360000000002</v>
       </c>
       <c r="O8" s="1">
-        <v>2.1040016000000001</v>
+        <v>2.6300020000000002</v>
       </c>
       <c r="P8" s="1">
-        <v>2.9401993333333336</v>
+        <v>3.6752491666666671</v>
       </c>
       <c r="Q8" s="1">
-        <v>5.6999552000000007</v>
+        <v>7.1249440000000011</v>
       </c>
       <c r="R8" s="1">
-        <v>6.7837952000000001</v>
+        <v>8.4797440000000002</v>
       </c>
       <c r="S8" s="1">
-        <v>5.9841936000000011</v>
+        <v>7.4802420000000014</v>
       </c>
       <c r="T8" s="1">
-        <v>3.458616000000001</v>
+        <v>4.3232700000000008</v>
       </c>
       <c r="U8" s="1">
-        <v>6.8365599999999986</v>
+        <v>8.5456999999999983</v>
       </c>
       <c r="V8" s="1">
-        <v>4.2154111999999992</v>
+        <v>5.2692639999999988</v>
       </c>
       <c r="W8" s="1">
-        <v>2.9370799999999999</v>
+        <v>3.6713499999999999</v>
       </c>
       <c r="X8" s="1">
-        <v>4.2411263999999997</v>
+        <v>5.3014079999999995</v>
       </c>
       <c r="Y8" s="1">
-        <v>2.7293333333333329</v>
+        <v>3.4116666666666662</v>
       </c>
       <c r="Z8" s="1">
-        <v>12.325285599999999</v>
+        <v>15.406606999999999</v>
       </c>
       <c r="AA8" s="1">
-        <v>14.7049728</v>
+        <v>18.381216000000002</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -11752,76 +11752,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-40.792499999999997</v>
+        <v>-50.990624999999994</v>
       </c>
       <c r="E9" s="1">
-        <v>-37.98272</v>
+        <v>-47.478400000000001</v>
       </c>
       <c r="F9" s="1">
-        <v>-45.393089866666664</v>
+        <v>-56.741362333333328</v>
       </c>
       <c r="G9" s="1">
-        <v>-49.450973599999998</v>
+        <v>-61.813716999999997</v>
       </c>
       <c r="H9" s="1">
-        <v>-50.762815999999994</v>
+        <v>-63.45351999999999</v>
       </c>
       <c r="I9" s="1">
-        <v>-54.828671999999983</v>
+        <v>-68.535839999999979</v>
       </c>
       <c r="J9" s="1">
-        <v>-57.221388000000012</v>
+        <v>-71.526735000000016</v>
       </c>
       <c r="K9" s="1">
-        <v>-59.836641279999981</v>
+        <v>-74.795801599999976</v>
       </c>
       <c r="L9" s="1">
-        <v>-52.156373066666674</v>
+        <v>-65.195466333333343</v>
       </c>
       <c r="M9" s="1">
-        <v>-72.816633600000003</v>
+        <v>-91.020792</v>
       </c>
       <c r="N9" s="1">
-        <v>-80.605024000000014</v>
+        <v>-100.75628000000002</v>
       </c>
       <c r="O9" s="1">
-        <v>-65.197081333333344</v>
+        <v>-81.496351666666683</v>
       </c>
       <c r="P9" s="1">
-        <v>-70.578105173333327</v>
+        <v>-88.222631466666655</v>
       </c>
       <c r="Q9" s="1">
-        <v>-64.825775360000009</v>
+        <v>-81.032219200000014</v>
       </c>
       <c r="R9" s="1">
-        <v>-66.85048448000002</v>
+        <v>-83.563105600000029</v>
       </c>
       <c r="S9" s="1">
-        <v>-57.909471840000002</v>
+        <v>-72.386839800000004</v>
       </c>
       <c r="T9" s="1">
-        <v>-55.178272800000009</v>
+        <v>-68.972841000000017</v>
       </c>
       <c r="U9" s="1">
-        <v>-50.406034986666668</v>
+        <v>-63.007543733333335</v>
       </c>
       <c r="V9" s="1">
-        <v>-30.727106453333331</v>
+        <v>-38.408883066666661</v>
       </c>
       <c r="W9" s="1">
-        <v>-34.057587226666669</v>
+        <v>-42.571984033333337</v>
       </c>
       <c r="X9" s="1">
-        <v>-33.546536799999991</v>
+        <v>-41.933170999999987</v>
       </c>
       <c r="Y9" s="1">
-        <v>-40.634373866666657</v>
+        <v>-50.792967333333323</v>
       </c>
       <c r="Z9" s="1">
-        <v>-31.644412800000001</v>
+        <v>-39.555516000000004</v>
       </c>
       <c r="AA9" s="1">
-        <v>-33.285713066666666</v>
+        <v>-41.607141333333331</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -11835,76 +11835,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>33.192810240000007</v>
+        <v>41.491012800000007</v>
       </c>
       <c r="E10" s="1">
-        <v>39.263178240000002</v>
+        <v>49.078972800000003</v>
       </c>
       <c r="F10" s="1">
-        <v>44.912442986666669</v>
+        <v>56.140553733333334</v>
       </c>
       <c r="G10" s="1">
-        <v>46.932896813333343</v>
+        <v>58.666121016666679</v>
       </c>
       <c r="H10" s="1">
-        <v>47.027171400000007</v>
+        <v>58.783964250000011</v>
       </c>
       <c r="I10" s="1">
-        <v>53.387776000000002</v>
+        <v>66.73472000000001</v>
       </c>
       <c r="J10" s="1">
-        <v>55.139968000000003</v>
+        <v>68.924959999999999</v>
       </c>
       <c r="K10" s="1">
-        <v>53.014386466666672</v>
+        <v>66.267983083333334</v>
       </c>
       <c r="L10" s="1">
-        <v>51.063586800000003</v>
+        <v>63.829483500000002</v>
       </c>
       <c r="M10" s="1">
-        <v>58.928837333333341</v>
+        <v>73.661046666666678</v>
       </c>
       <c r="N10" s="1">
-        <v>64.289713280000001</v>
+        <v>80.362141600000001</v>
       </c>
       <c r="O10" s="1">
-        <v>59.591432853333345</v>
+        <v>74.489291066666681</v>
       </c>
       <c r="P10" s="1">
-        <v>55.25856000000001</v>
+        <v>69.073200000000014</v>
       </c>
       <c r="Q10" s="1">
-        <v>56.663659173333336</v>
+        <v>70.829573966666672</v>
       </c>
       <c r="R10" s="1">
-        <v>46.600646399999995</v>
+        <v>58.250807999999992</v>
       </c>
       <c r="S10" s="1">
-        <v>42.436273919999998</v>
+        <v>53.045342399999996</v>
       </c>
       <c r="T10" s="1">
-        <v>44.601612079999988</v>
+        <v>55.752015099999987</v>
       </c>
       <c r="U10" s="1">
-        <v>39.460650666666666</v>
+        <v>49.325813333333329</v>
       </c>
       <c r="V10" s="1">
-        <v>31.503496959999996</v>
+        <v>39.379371199999994</v>
       </c>
       <c r="W10" s="1">
-        <v>31.92088416</v>
+        <v>39.901105200000003</v>
       </c>
       <c r="X10" s="1">
-        <v>37.8297192</v>
+        <v>47.287148999999999</v>
       </c>
       <c r="Y10" s="1">
-        <v>37.257123839999998</v>
+        <v>46.571404799999996</v>
       </c>
       <c r="Z10" s="1">
-        <v>28.138176000000001</v>
+        <v>35.172719999999998</v>
       </c>
       <c r="AA10" s="1">
-        <v>31.778603733333338</v>
+        <v>39.723254666666669</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -11918,76 +11918,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>16.204454399999999</v>
+        <v>20.255568</v>
       </c>
       <c r="E11" s="1">
-        <v>15.606988800000002</v>
+        <v>19.508736000000003</v>
       </c>
       <c r="F11" s="1">
-        <v>13.975142399999998</v>
+        <v>17.468927999999998</v>
       </c>
       <c r="G11" s="1">
-        <v>14.488320000000002</v>
+        <v>18.110400000000002</v>
       </c>
       <c r="H11" s="1">
-        <v>11.531059199999996</v>
+        <v>14.413823999999995</v>
       </c>
       <c r="I11" s="1">
-        <v>9.6908288000000002</v>
+        <v>12.113536</v>
       </c>
       <c r="J11" s="1">
-        <v>11.4990848</v>
+        <v>14.373856</v>
       </c>
       <c r="K11" s="1">
-        <v>2.1396480000000002</v>
+        <v>2.6745600000000005</v>
       </c>
       <c r="L11" s="1">
-        <v>1.7920000000000005</v>
+        <v>2.2400000000000007</v>
       </c>
       <c r="M11" s="1">
-        <v>2.7169792000000004</v>
+        <v>3.3962240000000006</v>
       </c>
       <c r="N11" s="1">
-        <v>1.4616319999999998</v>
+        <v>1.8270399999999998</v>
       </c>
       <c r="O11" s="1">
-        <v>1.9610111999999997</v>
+        <v>2.4512639999999997</v>
       </c>
       <c r="P11" s="1">
-        <v>3.1243008000000003</v>
+        <v>3.9053760000000004</v>
       </c>
       <c r="Q11" s="1">
-        <v>5.4742143999999984</v>
+        <v>6.8427679999999977</v>
       </c>
       <c r="R11" s="1">
-        <v>6.2017536</v>
+        <v>7.752192</v>
       </c>
       <c r="S11" s="1">
-        <v>5.9212799999999994</v>
+        <v>7.4015999999999993</v>
       </c>
       <c r="T11" s="1">
-        <v>3.4876800000000006</v>
+        <v>4.3596000000000004</v>
       </c>
       <c r="U11" s="1">
-        <v>7.0367231999999973</v>
+        <v>8.7959039999999966</v>
       </c>
       <c r="V11" s="1">
-        <v>4.049971199999999</v>
+        <v>5.0624639999999985</v>
       </c>
       <c r="W11" s="1">
-        <v>2.7358463999999998</v>
+        <v>3.4198079999999997</v>
       </c>
       <c r="X11" s="1">
-        <v>4.2817535999999992</v>
+        <v>5.3521919999999987</v>
       </c>
       <c r="Y11" s="1">
-        <v>2.5677567999999997</v>
+        <v>3.2096959999999997</v>
       </c>
       <c r="Z11" s="1">
-        <v>11.95904</v>
+        <v>14.9488</v>
       </c>
       <c r="AA11" s="1">
-        <v>14.1283072</v>
+        <v>17.660384000000001</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -12001,76 +12001,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-35.8752</v>
+        <v>-44.844000000000001</v>
       </c>
       <c r="E12" s="1">
-        <v>-37.223065600000005</v>
+        <v>-46.528832000000008</v>
       </c>
       <c r="F12" s="1">
-        <v>-41.8643456</v>
+        <v>-52.330432000000002</v>
       </c>
       <c r="G12" s="1">
-        <v>-45.620467199999986</v>
+        <v>-57.025583999999981</v>
       </c>
       <c r="H12" s="1">
-        <v>-47.284223999999995</v>
+        <v>-59.105279999999993</v>
       </c>
       <c r="I12" s="1">
-        <v>-53.753599999999999</v>
+        <v>-67.191999999999993</v>
       </c>
       <c r="J12" s="1">
-        <v>-52.82960640000001</v>
+        <v>-66.037008000000014</v>
       </c>
       <c r="K12" s="1">
-        <v>-58.685936639999987</v>
+        <v>-73.357420799999986</v>
       </c>
       <c r="L12" s="1">
-        <v>-50.618045439999996</v>
+        <v>-63.272556799999997</v>
       </c>
       <c r="M12" s="1">
-        <v>-72.816633600000003</v>
+        <v>-91.020792</v>
       </c>
       <c r="N12" s="1">
-        <v>-73.587645440000003</v>
+        <v>-91.984556800000007</v>
       </c>
       <c r="O12" s="1">
-        <v>-67.270384639999989</v>
+        <v>-84.087980799999983</v>
       </c>
       <c r="P12" s="1">
-        <v>-65.149020160000006</v>
+        <v>-81.436275200000011</v>
       </c>
       <c r="Q12" s="1">
-        <v>-66.751293439999998</v>
+        <v>-83.439116799999994</v>
       </c>
       <c r="R12" s="1">
-        <v>-61.103157760000009</v>
+        <v>-76.378947200000013</v>
       </c>
       <c r="S12" s="1">
-        <v>-56.705175039999979</v>
+        <v>-70.881468799999979</v>
       </c>
       <c r="T12" s="1">
-        <v>-49.419141120000006</v>
+        <v>-61.773926400000008</v>
       </c>
       <c r="U12" s="1">
-        <v>-43.764569600000009</v>
+        <v>-54.705712000000013</v>
       </c>
       <c r="V12" s="1">
-        <v>-28.071075839999992</v>
+        <v>-35.08884479999999</v>
       </c>
       <c r="W12" s="1">
-        <v>-33.706478080000004</v>
+        <v>-42.133097600000006</v>
       </c>
       <c r="X12" s="1">
-        <v>-35.629232639999998</v>
+        <v>-44.536540799999997</v>
       </c>
       <c r="Y12" s="1">
-        <v>-35.280415999999995</v>
+        <v>-44.100519999999996</v>
       </c>
       <c r="Z12" s="1">
-        <v>-29.505279999999999</v>
+        <v>-36.881599999999999</v>
       </c>
       <c r="AA12" s="1">
-        <v>-30.725273599999994</v>
+        <v>-38.406591999999989</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -12084,76 +12084,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>32.508422399999994</v>
+        <v>40.635527999999994</v>
       </c>
       <c r="E13" s="1">
-        <v>35.144663040000005</v>
+        <v>43.930828800000008</v>
       </c>
       <c r="F13" s="1">
-        <v>39.40528127999999</v>
+        <v>49.256601599999989</v>
       </c>
       <c r="G13" s="1">
-        <v>43.28445184000001</v>
+        <v>54.10556480000001</v>
       </c>
       <c r="H13" s="1">
-        <v>47.952729599999998</v>
+        <v>59.940911999999997</v>
       </c>
       <c r="I13" s="1">
-        <v>51.847744000000006</v>
+        <v>64.809680000000014</v>
       </c>
       <c r="J13" s="1">
-        <v>50.898432000000007</v>
+        <v>63.62304000000001</v>
       </c>
       <c r="K13" s="1">
-        <v>55.229311999999993</v>
+        <v>69.036639999999991</v>
       </c>
       <c r="L13" s="1">
-        <v>53.118777599999994</v>
+        <v>66.398471999999998</v>
       </c>
       <c r="M13" s="1">
-        <v>59.457994239999998</v>
+        <v>74.322492799999992</v>
       </c>
       <c r="N13" s="1">
-        <v>60.507965439999992</v>
+        <v>75.634956799999998</v>
       </c>
       <c r="O13" s="1">
-        <v>52.284334079999986</v>
+        <v>65.355417599999981</v>
       </c>
       <c r="P13" s="1">
-        <v>55.258559999999996</v>
+        <v>69.0732</v>
       </c>
       <c r="Q13" s="1">
-        <v>49.223516159999996</v>
+        <v>61.529395199999996</v>
       </c>
       <c r="R13" s="1">
-        <v>45.6496128</v>
+        <v>57.062016</v>
       </c>
       <c r="S13" s="1">
-        <v>45.936172800000001</v>
+        <v>57.420216000000003</v>
       </c>
       <c r="T13" s="1">
-        <v>41.570434559999995</v>
+        <v>51.963043199999994</v>
       </c>
       <c r="U13" s="1">
-        <v>34.968207359999994</v>
+        <v>43.710259199999996</v>
       </c>
       <c r="V13" s="1">
-        <v>28.509951999999998</v>
+        <v>35.637439999999998</v>
       </c>
       <c r="W13" s="1">
-        <v>32.868239359999997</v>
+        <v>41.085299199999994</v>
       </c>
       <c r="X13" s="1">
-        <v>34.587171839999996</v>
+        <v>43.233964799999995</v>
       </c>
       <c r="Y13" s="1">
-        <v>36.89185792</v>
+        <v>46.114822400000001</v>
       </c>
       <c r="Z13" s="1">
-        <v>29.843519999999994</v>
+        <v>37.304399999999994</v>
       </c>
       <c r="AA13" s="1">
-        <v>29.921126399999995</v>
+        <v>37.401407999999996</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -12167,76 +12167,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>15.254212607999998</v>
+        <v>19.067765759999997</v>
       </c>
       <c r="E14" s="1">
-        <v>16.091455744000001</v>
+        <v>20.114319680000001</v>
       </c>
       <c r="F14" s="1">
-        <v>14.700102912</v>
+        <v>18.37512864</v>
       </c>
       <c r="G14" s="1">
-        <v>13.643857920000002</v>
+        <v>17.054822400000003</v>
       </c>
       <c r="H14" s="1">
-        <v>11.191910399999999</v>
+        <v>13.989887999999999</v>
       </c>
       <c r="I14" s="1">
-        <v>9.5939205120000004</v>
+        <v>11.99240064</v>
       </c>
       <c r="J14" s="1">
-        <v>11.614075647999998</v>
+        <v>14.517594559999997</v>
       </c>
       <c r="K14" s="1">
-        <v>1.9165132800000002</v>
+        <v>2.3956416000000003</v>
       </c>
       <c r="L14" s="1">
-        <v>1.8088448000000004</v>
+        <v>2.2610560000000004</v>
       </c>
       <c r="M14" s="1">
-        <v>2.5066745600000004</v>
+        <v>3.1333432000000006</v>
       </c>
       <c r="N14" s="1">
-        <v>1.4770175999999999</v>
+        <v>1.8462719999999999</v>
       </c>
       <c r="O14" s="1">
-        <v>1.8629606400000001</v>
+        <v>2.3287008</v>
       </c>
       <c r="P14" s="1">
-        <v>2.7643936000000005</v>
+        <v>3.4554920000000005</v>
       </c>
       <c r="Q14" s="1">
-        <v>5.3636014080000001</v>
+        <v>6.7045017600000003</v>
       </c>
       <c r="R14" s="1">
-        <v>6.1367255040000002</v>
+        <v>7.6709068800000004</v>
       </c>
       <c r="S14" s="1">
-        <v>5.7448258560000012</v>
+        <v>7.1810323200000017</v>
       </c>
       <c r="T14" s="1">
-        <v>3.3541516799999997</v>
+        <v>4.1926895999999996</v>
       </c>
       <c r="U14" s="1">
-        <v>6.3662046719999994</v>
+        <v>7.957755839999999</v>
       </c>
       <c r="V14" s="1">
-        <v>3.7355028479999981</v>
+        <v>4.6693785599999975</v>
       </c>
       <c r="W14" s="1">
-        <v>2.7350088960000001</v>
+        <v>3.4187611200000001</v>
       </c>
       <c r="X14" s="1">
-        <v>4.3623014399999995</v>
+        <v>5.4528767999999994</v>
       </c>
       <c r="Y14" s="1">
-        <v>2.6725632000000004</v>
+        <v>3.3407040000000006</v>
       </c>
       <c r="Z14" s="1">
-        <v>11.6002688</v>
+        <v>14.500336000000001</v>
       </c>
       <c r="AA14" s="1">
-        <v>13.978374144</v>
+        <v>17.47296768</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -12250,76 +12250,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-35.431199999999997</v>
+        <v>-44.288999999999994</v>
       </c>
       <c r="E15" s="1">
-        <v>-39.122201600000004</v>
+        <v>-48.902752000000007</v>
       </c>
       <c r="F15" s="1">
-        <v>-43.577366272000006</v>
+        <v>-54.471707840000008</v>
       </c>
       <c r="G15" s="1">
-        <v>-44.214988159999997</v>
+        <v>-55.268735199999995</v>
       </c>
       <c r="H15" s="1">
-        <v>-50.239488000000001</v>
+        <v>-62.79936</v>
       </c>
       <c r="I15" s="1">
-        <v>-53.183811839999997</v>
+        <v>-66.479764799999998</v>
       </c>
       <c r="J15" s="1">
-        <v>-53.363031552000002</v>
+        <v>-66.703789440000008</v>
       </c>
       <c r="K15" s="1">
-        <v>-58.041542041599989</v>
+        <v>-72.551927551999981</v>
       </c>
       <c r="L15" s="1">
-        <v>-50.565861887999993</v>
+        <v>-63.207327359999994</v>
       </c>
       <c r="M15" s="1">
-        <v>-76.457465279999994</v>
+        <v>-95.571831599999996</v>
       </c>
       <c r="N15" s="1">
-        <v>-72.070374400000006</v>
+        <v>-90.087968000000004</v>
       </c>
       <c r="O15" s="1">
-        <v>-67.201033728000013</v>
+        <v>-84.00129216000002</v>
       </c>
       <c r="P15" s="1">
-        <v>-66.452000563199988</v>
+        <v>-83.065000703999985</v>
       </c>
       <c r="Q15" s="1">
-        <v>-62.8489101312</v>
+        <v>-78.561137664</v>
       </c>
       <c r="R15" s="1">
-        <v>-59.772197888000001</v>
+        <v>-74.715247360000006</v>
       </c>
       <c r="S15" s="1">
-        <v>-55.031546572800004</v>
+        <v>-68.789433216000006</v>
       </c>
       <c r="T15" s="1">
-        <v>-52.971141888000005</v>
+        <v>-66.213927360000014</v>
       </c>
       <c r="U15" s="1">
-        <v>-49.827114188800003</v>
+        <v>-62.283892736000006</v>
       </c>
       <c r="V15" s="1">
-        <v>-27.796213222399999</v>
+        <v>-34.745266528000002</v>
       </c>
       <c r="W15" s="1">
-        <v>-30.473274163199999</v>
+        <v>-38.091592704</v>
       </c>
       <c r="X15" s="1">
-        <v>-34.577651404799994</v>
+        <v>-43.222064255999996</v>
       </c>
       <c r="Y15" s="1">
-        <v>-38.258825855999994</v>
+        <v>-47.823532319999991</v>
       </c>
       <c r="Z15" s="1">
-        <v>-30.992346112000007</v>
+        <v>-38.740432640000009</v>
       </c>
       <c r="AA15" s="1">
-        <v>-31.628220416000001</v>
+        <v>-39.535275519999999</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -12333,76 +12333,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>31.533169728000001</v>
+        <v>39.416462160000002</v>
       </c>
       <c r="E16" s="1">
-        <v>39.977054207999998</v>
+        <v>49.971317759999998</v>
       </c>
       <c r="F16" s="1">
-        <v>43.115945267200004</v>
+        <v>53.894931584000005</v>
       </c>
       <c r="G16" s="1">
-        <v>46.393865523200013</v>
+        <v>57.992331904000018</v>
       </c>
       <c r="H16" s="1">
-        <v>44.690063488</v>
+        <v>55.862579359999998</v>
       </c>
       <c r="I16" s="1">
-        <v>55.523287039999992</v>
+        <v>69.404108799999989</v>
       </c>
       <c r="J16" s="1">
-        <v>51.916400640000006</v>
+        <v>64.895500800000008</v>
       </c>
       <c r="K16" s="1">
-        <v>49.844454080000013</v>
+        <v>62.305567600000018</v>
       </c>
       <c r="L16" s="1">
-        <v>50.462838720000001</v>
+        <v>63.078548400000003</v>
       </c>
       <c r="M16" s="1">
-        <v>54.874533324800005</v>
+        <v>68.593166656000008</v>
       </c>
       <c r="N16" s="1">
-        <v>57.482567167999996</v>
+        <v>71.853208959999989</v>
       </c>
       <c r="O16" s="1">
-        <v>57.757850304000009</v>
+        <v>72.197312880000013</v>
       </c>
       <c r="P16" s="1">
-        <v>51.027333120000009</v>
+        <v>63.784166400000011</v>
       </c>
       <c r="Q16" s="1">
-        <v>54.397112806400003</v>
+        <v>67.996391008000003</v>
       </c>
       <c r="R16" s="1">
-        <v>46.620267724799994</v>
+        <v>58.275334655999991</v>
       </c>
       <c r="S16" s="1">
-        <v>44.133724876799995</v>
+        <v>55.167156095999992</v>
       </c>
       <c r="T16" s="1">
-        <v>44.07688723199999</v>
+        <v>55.096109039999988</v>
       </c>
       <c r="U16" s="1">
-        <v>39.397513625599998</v>
+        <v>49.246892031999998</v>
       </c>
       <c r="V16" s="1">
-        <v>28.789349529599999</v>
+        <v>35.986686911999996</v>
       </c>
       <c r="W16" s="1">
-        <v>30.024977100800001</v>
+        <v>37.531221376000005</v>
       </c>
       <c r="X16" s="1">
-        <v>33.203684966399997</v>
+        <v>41.504606207999998</v>
       </c>
       <c r="Y16" s="1">
-        <v>36.1174941696</v>
+        <v>45.146867712000002</v>
       </c>
       <c r="Z16" s="1">
-        <v>27.012648959999996</v>
+        <v>33.765811199999995</v>
       </c>
       <c r="AA16" s="1">
-        <v>31.099837439999998</v>
+        <v>38.874796799999999</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -12416,76 +12416,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>17.021158901760003</v>
+        <v>21.276448627200004</v>
       </c>
       <c r="E17" s="1">
-        <v>17.063315942400003</v>
+        <v>21.329144928000005</v>
       </c>
       <c r="F17" s="1">
-        <v>13.965097766399998</v>
+        <v>17.456372207999998</v>
       </c>
       <c r="G17" s="1">
-        <v>14.931497011200001</v>
+        <v>18.664371264000003</v>
       </c>
       <c r="H17" s="1">
-        <v>10.858391470080001</v>
+        <v>13.572989337600001</v>
       </c>
       <c r="I17" s="1">
-        <v>9.2947041791999983</v>
+        <v>11.618380223999997</v>
       </c>
       <c r="J17" s="1">
-        <v>12.078638673919999</v>
+        <v>15.098298342399998</v>
       </c>
       <c r="K17" s="1">
-        <v>1.9366871040000004</v>
+        <v>2.4208588800000004</v>
       </c>
       <c r="L17" s="1">
-        <v>1.9186675199999998</v>
+        <v>2.3983344</v>
       </c>
       <c r="M17" s="1">
-        <v>2.6090524262400003</v>
+        <v>3.2613155328000003</v>
       </c>
       <c r="N17" s="1">
-        <v>1.4764267929600001</v>
+        <v>1.8455334912000001</v>
       </c>
       <c r="O17" s="1">
-        <v>1.9592462899200003</v>
+        <v>2.4490578624000001</v>
       </c>
       <c r="P17" s="1">
-        <v>2.6814617919999999</v>
+        <v>3.35182724</v>
       </c>
       <c r="Q17" s="1">
-        <v>5.6361157017599988</v>
+        <v>7.0451446271999982</v>
       </c>
       <c r="R17" s="1">
-        <v>6.707816693759999</v>
+        <v>8.3847708671999985</v>
       </c>
       <c r="S17" s="1">
-        <v>6.0320671488000004</v>
+        <v>7.5400839360000003</v>
       </c>
       <c r="T17" s="1">
-        <v>3.2870686464000003</v>
+        <v>4.1088358080000003</v>
       </c>
       <c r="U17" s="1">
-        <v>6.6943595519999981</v>
+        <v>8.3679494399999967</v>
       </c>
       <c r="V17" s="1">
-        <v>4.2086665420799987</v>
+        <v>5.2608331775999986</v>
       </c>
       <c r="W17" s="1">
-        <v>2.8195967999999998</v>
+        <v>3.5244959999999996</v>
       </c>
       <c r="X17" s="1">
-        <v>3.9086220902400002</v>
+        <v>4.8857776128000001</v>
       </c>
       <c r="Y17" s="1">
-        <v>2.5939584</v>
+        <v>3.242448</v>
       </c>
       <c r="Z17" s="1">
-        <v>11.832274175999999</v>
+        <v>14.790342719999998</v>
       </c>
       <c r="AA17" s="1">
-        <v>14.257941626879999</v>
+        <v>17.8224270336</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -12499,76 +12499,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-39.160799999999995</v>
+        <v>-48.950999999999993</v>
       </c>
       <c r="E18" s="1">
-        <v>-37.192679423999998</v>
+        <v>-46.490849279999999</v>
       </c>
       <c r="F18" s="1">
-        <v>-44.884687260160007</v>
+        <v>-56.105859075200009</v>
       </c>
       <c r="G18" s="1">
-        <v>-46.048746616319988</v>
+        <v>-57.560933270399985</v>
       </c>
       <c r="H18" s="1">
-        <v>-50.194272460799993</v>
+        <v>-62.742840575999992</v>
       </c>
       <c r="I18" s="1">
-        <v>-51.056459366399984</v>
+        <v>-63.820574207999982</v>
       </c>
       <c r="J18" s="1">
-        <v>-56.031183129600009</v>
+        <v>-70.038978912000005</v>
       </c>
       <c r="K18" s="1">
-        <v>-55.145448603647985</v>
+        <v>-68.931810754559976</v>
       </c>
       <c r="L18" s="1">
-        <v>-52.072922869759999</v>
+        <v>-65.091153587199997</v>
       </c>
       <c r="M18" s="1">
-        <v>-71.302047621119982</v>
+        <v>-89.127559526399978</v>
       </c>
       <c r="N18" s="1">
-        <v>-73.511781888000016</v>
+        <v>-91.889727360000023</v>
       </c>
       <c r="O18" s="1">
-        <v>-59.459738176000002</v>
+        <v>-74.324672719999995</v>
       </c>
       <c r="P18" s="1">
-        <v>-66.399881347071997</v>
+        <v>-82.999851683839992</v>
       </c>
       <c r="Q18" s="1">
-        <v>-64.722054119424001</v>
+        <v>-80.902567649280002</v>
       </c>
       <c r="R18" s="1">
-        <v>-64.818229751808005</v>
+        <v>-81.02278718976001</v>
       </c>
       <c r="S18" s="1">
-        <v>-56.149023896063994</v>
+        <v>-70.18627987008</v>
       </c>
       <c r="T18" s="1">
-        <v>-54.560276144640007</v>
+        <v>-68.200345180800014</v>
       </c>
       <c r="U18" s="1">
-        <v>-50.325385330688</v>
+        <v>-62.906731663359999</v>
       </c>
       <c r="V18" s="1">
-        <v>-28.908061751295993</v>
+        <v>-36.13507718911999</v>
       </c>
       <c r="W18" s="1">
-        <v>-34.330047924480006</v>
+        <v>-42.912559905600006</v>
       </c>
       <c r="X18" s="1">
-        <v>-30.594441561599997</v>
+        <v>-38.243051951999995</v>
       </c>
       <c r="Y18" s="1">
-        <v>-37.448638955520003</v>
+        <v>-46.810798694400006</v>
       </c>
       <c r="Z18" s="1">
-        <v>-30.682422650880003</v>
+        <v>-38.353028313600007</v>
       </c>
       <c r="AA18" s="1">
-        <v>-32.593370234880005</v>
+        <v>-40.741712793600009</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -12582,76 +12582,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>30.909144895487998</v>
+        <v>38.636431119359997</v>
       </c>
       <c r="E19" s="1">
-        <v>37.315724599296004</v>
+        <v>46.644655749120005</v>
       </c>
       <c r="F19" s="1">
-        <v>41.822466909184001</v>
+        <v>52.278083636480005</v>
       </c>
       <c r="G19" s="1">
-        <v>46.407248369024011</v>
+        <v>58.009060461280015</v>
       </c>
       <c r="H19" s="1">
-        <v>43.791702007680009</v>
+        <v>54.739627509600012</v>
       </c>
       <c r="I19" s="1">
-        <v>50.739742310400004</v>
+        <v>63.424677888000005</v>
       </c>
       <c r="J19" s="1">
-        <v>52.405025587199994</v>
+        <v>65.506281983999997</v>
       </c>
       <c r="K19" s="1">
-        <v>52.929563448320003</v>
+        <v>66.161954310400006</v>
       </c>
       <c r="L19" s="1">
-        <v>47.550412028160004</v>
+        <v>59.438015035200003</v>
       </c>
       <c r="M19" s="1">
-        <v>56.571683839999992</v>
+        <v>70.714604799999989</v>
       </c>
       <c r="N19" s="1">
-        <v>63.569668491263997</v>
+        <v>79.462085614079996</v>
       </c>
       <c r="O19" s="1">
-        <v>58.351931049983996</v>
+        <v>72.93991381248</v>
       </c>
       <c r="P19" s="1">
-        <v>53.048217600000008</v>
+        <v>66.310272000000012</v>
       </c>
       <c r="Q19" s="1">
-        <v>52.221228294143998</v>
+        <v>65.276535367679998</v>
       </c>
       <c r="R19" s="1">
-        <v>46.973451571199995</v>
+        <v>58.716814463999995</v>
       </c>
       <c r="S19" s="1">
-        <v>39.516658274303992</v>
+        <v>49.395822842879994</v>
       </c>
       <c r="T19" s="1">
-        <v>43.245723072767987</v>
+        <v>54.057153840959984</v>
       </c>
       <c r="U19" s="1">
-        <v>39.0186913792</v>
+        <v>48.773364223999998</v>
       </c>
       <c r="V19" s="1">
-        <v>29.033622798335994</v>
+        <v>36.292028497919993</v>
       </c>
       <c r="W19" s="1">
-        <v>31.256929769471999</v>
+        <v>39.071162211839997</v>
       </c>
       <c r="X19" s="1">
-        <v>35.953365127679994</v>
+        <v>44.941706409599995</v>
       </c>
       <c r="Y19" s="1">
-        <v>37.555180830719998</v>
+        <v>46.943976038399995</v>
       </c>
       <c r="Z19" s="1">
-        <v>25.9321430016</v>
+        <v>32.415178752000003</v>
       </c>
       <c r="AA19" s="1">
-        <v>32.032832563200003</v>
+        <v>40.041040704000004</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -12665,76 +12665,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>17.189685227520002</v>
+        <v>21.487106534400002</v>
       </c>
       <c r="E20" s="1">
-        <v>17.042831769600003</v>
+        <v>21.303539712000003</v>
       </c>
       <c r="F20" s="1">
-        <v>14.824831057919999</v>
+        <v>18.531038822399999</v>
       </c>
       <c r="G20" s="1">
-        <v>14.615817216000002</v>
+        <v>18.269771520000003</v>
       </c>
       <c r="H20" s="1">
-        <v>12.471993630719998</v>
+        <v>15.589992038399998</v>
       </c>
       <c r="I20" s="1">
-        <v>10.582385049600001</v>
+        <v>13.227981312000001</v>
       </c>
       <c r="J20" s="1">
-        <v>12.078638673919999</v>
+        <v>15.098298342399998</v>
       </c>
       <c r="K20" s="1">
-        <v>2.1807292416000004</v>
+        <v>2.7259115520000003</v>
       </c>
       <c r="L20" s="1">
-        <v>1.8264064000000004</v>
+        <v>2.2830080000000006</v>
       </c>
       <c r="M20" s="1">
-        <v>2.6843754496000005</v>
+        <v>3.3554693120000008</v>
       </c>
       <c r="N20" s="1">
-        <v>1.5352982527999997</v>
+        <v>1.9191228159999996</v>
       </c>
       <c r="O20" s="1">
-        <v>1.9374790655999998</v>
+        <v>2.4218488319999998</v>
       </c>
       <c r="P20" s="1">
-        <v>3.4117364736000009</v>
+        <v>4.2646705920000008</v>
       </c>
       <c r="Q20" s="1">
-        <v>5.7501148057599991</v>
+        <v>7.1876435071999989</v>
       </c>
       <c r="R20" s="1">
-        <v>6.127332556799999</v>
+        <v>7.6591656959999987</v>
       </c>
       <c r="S20" s="1">
-        <v>5.911805951999999</v>
+        <v>7.3897574399999986</v>
       </c>
       <c r="T20" s="1">
-        <v>3.4458278400000002</v>
+        <v>4.3072848000000006</v>
       </c>
       <c r="U20" s="1">
-        <v>7.0986463641599977</v>
+        <v>8.8733079551999978</v>
       </c>
       <c r="V20" s="1">
-        <v>4.2962094489599991</v>
+        <v>5.3702618111999989</v>
       </c>
       <c r="W20" s="1">
-        <v>2.9306386636799999</v>
+        <v>3.6632983295999999</v>
       </c>
       <c r="X20" s="1">
-        <v>4.4084935065600002</v>
+        <v>5.5106168832</v>
       </c>
       <c r="Y20" s="1">
-        <v>2.6704670719999997</v>
+        <v>3.3380838399999995</v>
       </c>
       <c r="Z20" s="1">
-        <v>12.188653567999999</v>
+        <v>15.235816959999999</v>
       </c>
       <c r="AA20" s="1">
-        <v>14.399570698240003</v>
+        <v>17.999463372800005</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -12748,76 +12748,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-38.802616319999991</v>
+        <v>-48.503270399999991</v>
       </c>
       <c r="E21" s="1">
-        <v>-40.647587635200011</v>
+        <v>-50.809484544000014</v>
       </c>
       <c r="F21" s="1">
-        <v>-41.361973452800008</v>
+        <v>-51.702466816000012</v>
       </c>
       <c r="G21" s="1">
-        <v>-48.394191605759993</v>
+        <v>-60.492739507199992</v>
       </c>
       <c r="H21" s="1">
-        <v>-47.700325171199999</v>
+        <v>-59.625406464000001</v>
       </c>
       <c r="I21" s="1">
-        <v>-57.580856319999988</v>
+        <v>-71.976070399999983</v>
       </c>
       <c r="J21" s="1">
-        <v>-52.195651123200001</v>
+        <v>-65.244563904000003</v>
       </c>
       <c r="K21" s="1">
-        <v>-62.864375328767984</v>
+        <v>-78.580469160959979</v>
       </c>
       <c r="L21" s="1">
-        <v>-50.537056567295998</v>
+        <v>-63.171320709119996</v>
       </c>
       <c r="M21" s="1">
-        <v>-75.729298944000007</v>
+        <v>-94.661623680000005</v>
       </c>
       <c r="N21" s="1">
-        <v>-79.592397307904008</v>
+        <v>-99.490496634880003</v>
       </c>
       <c r="O21" s="1">
-        <v>-68.561976025088001</v>
+        <v>-85.702470031360008</v>
       </c>
       <c r="P21" s="1">
-        <v>-69.787630395392</v>
+        <v>-87.23453799424</v>
       </c>
       <c r="Q21" s="1">
-        <v>-68.727131725824009</v>
+        <v>-85.908914657280008</v>
       </c>
       <c r="R21" s="1">
-        <v>-61.640865548288012</v>
+        <v>-77.051081935360017</v>
       </c>
       <c r="S21" s="1">
-        <v>-61.922051143679987</v>
+        <v>-77.402563929599978</v>
       </c>
       <c r="T21" s="1">
-        <v>-50.367988629504005</v>
+        <v>-62.959985786880004</v>
       </c>
       <c r="U21" s="1">
-        <v>-46.880606955520015</v>
+        <v>-58.600758694400021</v>
       </c>
       <c r="V21" s="1">
-        <v>-28.610040496127997</v>
+        <v>-35.762550620159999</v>
       </c>
       <c r="W21" s="1">
-        <v>-34.353642459136012</v>
+        <v>-42.942053073920015</v>
       </c>
       <c r="X21" s="1">
-        <v>-37.054401945599999</v>
+        <v>-46.318002432</v>
       </c>
       <c r="Y21" s="1">
-        <v>-35.223967334399994</v>
+        <v>-44.029959167999991</v>
       </c>
       <c r="Z21" s="1">
-        <v>-31.606055936000001</v>
+        <v>-39.507569920000002</v>
       </c>
       <c r="AA21" s="1">
-        <v>-32.912913080319989</v>
+        <v>-41.141141350399984</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -12831,76 +12831,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>34.146846888959999</v>
+        <v>42.683558611199999</v>
       </c>
       <c r="E22" s="1">
-        <v>36.915954057216005</v>
+        <v>46.144942571520005</v>
       </c>
       <c r="F22" s="1">
-        <v>43.030567157759997</v>
+        <v>53.788208947199998</v>
       </c>
       <c r="G22" s="1">
-        <v>47.266621409280013</v>
+        <v>59.083276761600018</v>
       </c>
       <c r="H22" s="1">
-        <v>49.372130396159996</v>
+        <v>61.715162995199996</v>
       </c>
       <c r="I22" s="1">
-        <v>56.617736447999995</v>
+        <v>70.772170559999992</v>
       </c>
       <c r="J22" s="1">
-        <v>52.934369279999999</v>
+        <v>66.167961599999998</v>
       </c>
       <c r="K22" s="1">
-        <v>55.140945100800003</v>
+        <v>68.926181376000002</v>
       </c>
       <c r="L22" s="1">
-        <v>53.033787555840007</v>
+        <v>66.292234444800016</v>
       </c>
       <c r="M22" s="1">
-        <v>58.744498309119997</v>
+        <v>73.430622886400002</v>
       </c>
       <c r="N22" s="1">
-        <v>62.928284057599996</v>
+        <v>78.660355071999987</v>
       </c>
       <c r="O22" s="1">
-        <v>57.094492815360006</v>
+        <v>71.368116019200002</v>
       </c>
       <c r="P22" s="1">
-        <v>56.319524352000002</v>
+        <v>70.39940544000001</v>
       </c>
       <c r="Q22" s="1">
-        <v>53.752079646719999</v>
+        <v>67.190099558399993</v>
       </c>
       <c r="R22" s="1">
-        <v>47.000841338880001</v>
+        <v>58.751051673600003</v>
       </c>
       <c r="S22" s="1">
-        <v>45.862674923520011</v>
+        <v>57.328343654400015</v>
       </c>
       <c r="T22" s="1">
-        <v>44.530249500672006</v>
+        <v>55.662811875840006</v>
       </c>
       <c r="U22" s="1">
-        <v>37.457943724031999</v>
+        <v>46.822429655039997</v>
       </c>
       <c r="V22" s="1">
-        <v>28.464336076799999</v>
+        <v>35.580420095999997</v>
       </c>
       <c r="W22" s="1">
-        <v>34.182968934400002</v>
+        <v>42.728711168000004</v>
       </c>
       <c r="X22" s="1">
-        <v>35.970658713599995</v>
+        <v>44.963323391999992</v>
       </c>
       <c r="Y22" s="1">
-        <v>36.449155624959999</v>
+        <v>45.561444531199996</v>
       </c>
       <c r="Z22" s="1">
-        <v>31.658006015999998</v>
+        <v>39.572507519999995</v>
       </c>
       <c r="AA22" s="1">
-        <v>31.117971455999992</v>
+        <v>38.89746431999999</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -12914,76 +12914,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>16.657600167936</v>
+        <v>20.822000209919999</v>
       </c>
       <c r="E23" s="1">
-        <v>17.069816253235203</v>
+        <v>21.337270316544004</v>
       </c>
       <c r="F23" s="1">
-        <v>15.746750239334403</v>
+        <v>19.683437799168004</v>
       </c>
       <c r="G23" s="1">
-        <v>13.905819992064002</v>
+        <v>17.382274990080003</v>
       </c>
       <c r="H23" s="1">
-        <v>11.057607475200001</v>
+        <v>13.822009344000001</v>
       </c>
       <c r="I23" s="1">
-        <v>10.077454105804799</v>
+        <v>12.596817632255998</v>
       </c>
       <c r="J23" s="1">
-        <v>11.837065900441599</v>
+        <v>14.796332375552</v>
       </c>
       <c r="K23" s="1">
-        <v>1.9931738112000004</v>
+        <v>2.4914672640000006</v>
       </c>
       <c r="L23" s="1">
-        <v>1.9000105779200009</v>
+        <v>2.3750132224000011</v>
       </c>
       <c r="M23" s="1">
-        <v>2.5808721269760002</v>
+        <v>3.2260901587200004</v>
       </c>
       <c r="N23" s="1">
-        <v>1.536098304</v>
+        <v>1.9201228800000001</v>
       </c>
       <c r="O23" s="1">
-        <v>1.9568538562560003</v>
+        <v>2.4460673203200005</v>
       </c>
       <c r="P23" s="1">
-        <v>2.9037190374400006</v>
+        <v>3.6296487968000006</v>
       </c>
       <c r="Q23" s="1">
-        <v>5.6897083736064005</v>
+        <v>7.1121354670080006</v>
       </c>
       <c r="R23" s="1">
-        <v>6.0630847979519986</v>
+        <v>7.578855997439998</v>
       </c>
       <c r="S23" s="1">
-        <v>5.8551265124352012</v>
+        <v>7.3189081405440017</v>
       </c>
       <c r="T23" s="1">
-        <v>3.5232009246720009</v>
+        <v>4.4040011558400014</v>
       </c>
       <c r="U23" s="1">
-        <v>6.4884358017023986</v>
+        <v>8.1105447521279981</v>
       </c>
       <c r="V23" s="1">
-        <v>3.8072245026815987</v>
+        <v>4.7590306283519981</v>
       </c>
       <c r="W23" s="1">
-        <v>2.9297415293952001</v>
+        <v>3.662176911744</v>
       </c>
       <c r="X23" s="1">
-        <v>4.3099538227200007</v>
+        <v>5.3874422784000009</v>
       </c>
       <c r="Y23" s="1">
-        <v>2.7794657279999999</v>
+        <v>3.4743321599999999</v>
       </c>
       <c r="Z23" s="1">
-        <v>11.82299396096</v>
+        <v>14.778742451199999</v>
       </c>
       <c r="AA23" s="1">
-        <v>15.119009474150397</v>
+        <v>18.898761842687996</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -12997,76 +12997,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-35.006025599999994</v>
+        <v>-43.757531999999991</v>
       </c>
       <c r="E24" s="1">
-        <v>-39.059606077440002</v>
+        <v>-48.824507596800004</v>
       </c>
       <c r="F24" s="1">
-        <v>-47.133279359795203</v>
+        <v>-58.916599199744006</v>
       </c>
       <c r="G24" s="1">
-        <v>-44.604080055808005</v>
+        <v>-55.755100069760005</v>
       </c>
       <c r="H24" s="1">
-        <v>-50.6815954944</v>
+        <v>-63.351994368</v>
       </c>
       <c r="I24" s="1">
-        <v>-55.311164313599996</v>
+        <v>-69.138955392</v>
       </c>
       <c r="J24" s="1">
-        <v>-57.16247939850242</v>
+        <v>-71.453099248128026</v>
       </c>
       <c r="K24" s="1">
-        <v>-63.381363909427186</v>
+        <v>-79.226704886783978</v>
       </c>
       <c r="L24" s="1">
-        <v>-53.6402662907904</v>
+        <v>-67.050332863487995</v>
       </c>
       <c r="M24" s="1">
-        <v>-77.92544861337602</v>
+        <v>-97.406810766720028</v>
       </c>
       <c r="N24" s="1">
-        <v>-74.203657482240004</v>
+        <v>-92.754571852800012</v>
       </c>
       <c r="O24" s="1">
-        <v>-71.985747329433607</v>
+        <v>-89.982184161792006</v>
       </c>
       <c r="P24" s="1">
-        <v>-65.654576556441597</v>
+        <v>-82.068220695552</v>
       </c>
       <c r="Q24" s="1">
-        <v>-68.631009863270421</v>
+        <v>-85.78876232908803</v>
       </c>
       <c r="R24" s="1">
-        <v>-63.406347519590405</v>
+        <v>-79.257934399488008</v>
       </c>
       <c r="S24" s="1">
-        <v>-60.094448857497589</v>
+        <v>-75.118061071871992</v>
       </c>
       <c r="T24" s="1">
-        <v>-55.6408874391552</v>
+        <v>-69.551109298943999</v>
       </c>
       <c r="U24" s="1">
-        <v>-53.374804719042572</v>
+        <v>-66.718505898803215</v>
       </c>
       <c r="V24" s="1">
-        <v>-28.040819898757121</v>
+        <v>-35.051024873446401</v>
       </c>
       <c r="W24" s="1">
-        <v>-32.009127181025285</v>
+        <v>-40.011408976281608</v>
       </c>
       <c r="X24" s="1">
-        <v>-35.24154231177215</v>
+        <v>-44.051927889715188</v>
       </c>
       <c r="Y24" s="1">
-        <v>-38.595503523532805</v>
+        <v>-48.244379404416009</v>
       </c>
       <c r="Z24" s="1">
-        <v>-31.587399157350404</v>
+        <v>-39.484248946688005</v>
       </c>
       <c r="AA24" s="1">
-        <v>-33.880149709619197</v>
+        <v>-42.350187137023994</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -13080,76 +13080,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>32.794496517120002</v>
+        <v>40.993120646400001</v>
       </c>
       <c r="E25" s="1">
-        <v>42.823420467609601</v>
+        <v>53.529275584512</v>
       </c>
       <c r="F25" s="1">
-        <v>47.082612231782406</v>
+        <v>58.853265289728007</v>
       </c>
       <c r="G25" s="1">
-        <v>49.214612547010567</v>
+        <v>61.518265683763211</v>
       </c>
       <c r="H25" s="1">
-        <v>45.548112706969597</v>
+        <v>56.935140883711995</v>
       </c>
       <c r="I25" s="1">
-        <v>60.053987262463998</v>
+        <v>75.06748407808</v>
       </c>
       <c r="J25" s="1">
-        <v>55.072917798911995</v>
+        <v>68.841147248639999</v>
       </c>
       <c r="K25" s="1">
-        <v>51.838232243200004</v>
+        <v>64.797790304000003</v>
       </c>
       <c r="L25" s="1">
-        <v>51.431725223424003</v>
+        <v>64.289656529280009</v>
       </c>
       <c r="M25" s="1">
-        <v>59.352295244103694</v>
+        <v>74.190369055129622</v>
       </c>
       <c r="N25" s="1">
-        <v>60.977507251814394</v>
+        <v>76.221884064767991</v>
       </c>
       <c r="O25" s="1">
-        <v>58.866801029836807</v>
+        <v>73.583501287296002</v>
       </c>
       <c r="P25" s="1">
-        <v>51.476373651456015</v>
+        <v>64.345467064320019</v>
       </c>
       <c r="Q25" s="1">
-        <v>55.441537372282887</v>
+        <v>69.301921715353615</v>
       </c>
       <c r="R25" s="1">
-        <v>50.909332355481588</v>
+        <v>63.636665444351983</v>
       </c>
       <c r="S25" s="1">
-        <v>47.276046088028153</v>
+        <v>59.095057610035191</v>
       </c>
       <c r="T25" s="1">
-        <v>47.215161602918386</v>
+        <v>59.018952003647982</v>
       </c>
       <c r="U25" s="1">
-        <v>41.383148312330242</v>
+        <v>51.728935390412801</v>
       </c>
       <c r="V25" s="1">
-        <v>28.743286570352637</v>
+        <v>35.929108212940797</v>
       </c>
       <c r="W25" s="1">
-        <v>29.976937137438721</v>
+        <v>37.471171421798402</v>
       </c>
       <c r="X25" s="1">
-        <v>35.567787336007676</v>
+        <v>44.459734170009597</v>
       </c>
       <c r="Y25" s="1">
-        <v>39.064681693839361</v>
+        <v>48.830852117299202</v>
       </c>
       <c r="Z25" s="1">
-        <v>29.216881115135994</v>
+        <v>36.521101393919992</v>
       </c>
       <c r="AA25" s="1">
-        <v>31.050077700096001</v>
+        <v>38.81259712512</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -13163,76 +13163,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>17.347965152673794</v>
+        <v>21.684956440842242</v>
       </c>
       <c r="E26" s="1">
-        <v>18.100765551697922</v>
+        <v>22.625956939622402</v>
       </c>
       <c r="F26" s="1">
-        <v>14.668938693826556</v>
+        <v>18.336173367283195</v>
       </c>
       <c r="G26" s="1">
-        <v>15.839332029480962</v>
+        <v>19.799165036851203</v>
       </c>
       <c r="H26" s="1">
-        <v>11.631508942749695</v>
+        <v>14.53938617843712</v>
       </c>
       <c r="I26" s="1">
-        <v>9.7631572698316802</v>
+        <v>12.2039465872896</v>
       </c>
       <c r="J26" s="1">
-        <v>12.436166378668034</v>
+        <v>15.545207973335042</v>
       </c>
       <c r="K26" s="1">
-        <v>1.9738714963968003</v>
+        <v>2.4673393704960005</v>
       </c>
       <c r="L26" s="1">
-        <v>2.0552766474239998</v>
+        <v>2.5690958092799998</v>
       </c>
       <c r="M26" s="1">
-        <v>2.6320120875909123</v>
+        <v>3.2900151094886403</v>
       </c>
       <c r="N26" s="1">
-        <v>1.4894193487380483</v>
+        <v>1.8617741859225603</v>
       </c>
       <c r="O26" s="1">
-        <v>1.9357353344409605</v>
+        <v>2.4196691680512004</v>
       </c>
       <c r="P26" s="1">
-        <v>2.9002690742272002</v>
+        <v>3.6253363427840002</v>
       </c>
       <c r="Q26" s="1">
-        <v>6.0374071397253113</v>
+        <v>7.5467589246566389</v>
       </c>
       <c r="R26" s="1">
-        <v>6.9063680678952961</v>
+        <v>8.6329600848691204</v>
       </c>
       <c r="S26" s="1">
-        <v>6.2106163364044802</v>
+        <v>7.7632704205056005</v>
       </c>
       <c r="T26" s="1">
-        <v>3.247623822643201</v>
+        <v>4.0595297783040012</v>
       </c>
       <c r="U26" s="1">
-        <v>6.9621339340799979</v>
+        <v>8.7026674175999972</v>
       </c>
       <c r="V26" s="1">
-        <v>4.2457028076503027</v>
+        <v>5.3071285095628786</v>
       </c>
       <c r="W26" s="1">
-        <v>3.0496758988799999</v>
+        <v>3.8120948736</v>
       </c>
       <c r="X26" s="1">
-        <v>3.9430179646341124</v>
+        <v>4.9287724557926405</v>
       </c>
       <c r="Y26" s="1">
-        <v>2.7786482380800002</v>
+        <v>3.4733102976000003</v>
       </c>
       <c r="Z26" s="1">
-        <v>12.305565143039999</v>
+        <v>15.381956428799999</v>
       </c>
       <c r="AA26" s="1">
-        <v>14.531694106116097</v>
+        <v>18.164617632645122</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -13246,76 +13246,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-40.727231999999994</v>
+        <v>-50.90903999999999</v>
       </c>
       <c r="E27" s="1">
-        <v>-39.067190466969599</v>
+        <v>-48.833988083712001</v>
       </c>
       <c r="F27" s="1">
-        <v>-44.812871760543743</v>
+        <v>-56.016089700679679</v>
       </c>
       <c r="G27" s="1">
-        <v>-45.975068621733875</v>
+        <v>-57.468835777167342</v>
       </c>
       <c r="H27" s="1">
-        <v>-52.202043359231993</v>
+        <v>-65.252554199039992</v>
       </c>
       <c r="I27" s="1">
-        <v>-54.691679273287662</v>
+        <v>-68.364599091609577</v>
       </c>
       <c r="J27" s="1">
-        <v>-55.941533236592647</v>
+        <v>-69.926916545740809</v>
       </c>
       <c r="K27" s="1">
-        <v>-59.645317209705659</v>
+        <v>-74.556646512132076</v>
       </c>
       <c r="L27" s="1">
-        <v>-56.322073375932426</v>
+        <v>-70.402591719915534</v>
       </c>
       <c r="M27" s="1">
-        <v>-70.446423049666535</v>
+        <v>-88.058028812083165</v>
       </c>
       <c r="N27" s="1">
-        <v>-74.158685568614416</v>
+        <v>-92.698356960768024</v>
       </c>
       <c r="O27" s="1">
-        <v>-58.746221317888008</v>
+        <v>-73.432776647360015</v>
       </c>
       <c r="P27" s="1">
-        <v>-67.674759068935771</v>
+        <v>-84.593448836169713</v>
       </c>
       <c r="Q27" s="1">
-        <v>-65.291608195674925</v>
+        <v>-81.61451024459366</v>
       </c>
       <c r="R27" s="1">
-        <v>-66.062739763042742</v>
+        <v>-82.578424703803421</v>
       </c>
       <c r="S27" s="1">
-        <v>-55.47523560931122</v>
+        <v>-69.344044511639026</v>
       </c>
       <c r="T27" s="1">
-        <v>-59.012394678042632</v>
+        <v>-73.765493347553289</v>
       </c>
       <c r="U27" s="1">
-        <v>-50.76824872159807</v>
+        <v>-63.460310901997588</v>
       </c>
       <c r="V27" s="1">
-        <v>-29.162452694707397</v>
+        <v>-36.453065868384243</v>
       </c>
       <c r="W27" s="1">
-        <v>-37.48841233353216</v>
+        <v>-46.860515416915199</v>
       </c>
       <c r="X27" s="1">
-        <v>-30.863672647342074</v>
+        <v>-38.579590809177596</v>
       </c>
       <c r="Y27" s="1">
-        <v>-40.114982049153021</v>
+        <v>-50.143727561441274</v>
       </c>
       <c r="Z27" s="1">
-        <v>-32.867011143622662</v>
+        <v>-41.083763929528331</v>
       </c>
       <c r="AA27" s="1">
-        <v>-33.8971050442752</v>
+        <v>-42.371381305344002</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -13329,76 +13329,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>31.824055584394443</v>
+        <v>39.780069480493054</v>
       </c>
       <c r="E28" s="1">
-        <v>36.867935904104456</v>
+        <v>46.08491988013057</v>
       </c>
       <c r="F28" s="1">
-        <v>44.800226553117902</v>
+        <v>56.000283191397379</v>
       </c>
       <c r="G28" s="1">
-        <v>46.81563215467142</v>
+        <v>58.519540193339274</v>
       </c>
       <c r="H28" s="1">
-        <v>46.454237489746951</v>
+        <v>58.067796862183691</v>
       </c>
       <c r="I28" s="1">
-        <v>51.186252042731525</v>
+        <v>63.982815053414406</v>
       </c>
       <c r="J28" s="1">
-        <v>57.226287941222402</v>
+        <v>71.532859926528005</v>
       </c>
       <c r="K28" s="1">
-        <v>53.395343606665222</v>
+        <v>66.744179508331527</v>
       </c>
       <c r="L28" s="1">
-        <v>46.979807083822095</v>
+        <v>58.724758854777619</v>
       </c>
       <c r="M28" s="1">
-        <v>59.422896705536004</v>
+        <v>74.278620881920006</v>
       </c>
       <c r="N28" s="1">
-        <v>62.806832469368835</v>
+        <v>78.50854058671105</v>
       </c>
       <c r="O28" s="1">
-        <v>62.506588540742861</v>
+        <v>78.133235675928574</v>
       </c>
       <c r="P28" s="1">
-        <v>57.928653619199999</v>
+        <v>72.410817023999996</v>
       </c>
       <c r="Q28" s="1">
-        <v>55.939379748687053</v>
+        <v>69.924224685858817</v>
       </c>
       <c r="R28" s="1">
-        <v>47.875341841367032</v>
+        <v>59.84417730170879</v>
       </c>
       <c r="S28" s="1">
-        <v>40.686351359223394</v>
+        <v>50.857939199029246</v>
       </c>
       <c r="T28" s="1">
-        <v>42.726774395894779</v>
+        <v>53.408467994868474</v>
       </c>
       <c r="U28" s="1">
-        <v>40.985233424711673</v>
+        <v>51.231541780889593</v>
       </c>
       <c r="V28" s="1">
-        <v>31.402766418680205</v>
+        <v>39.253458023350255</v>
       </c>
       <c r="W28" s="1">
-        <v>31.206918681840843</v>
+        <v>39.008648352301051</v>
       </c>
       <c r="X28" s="1">
-        <v>38.513244724770814</v>
+        <v>48.141555905963514</v>
       </c>
       <c r="Y28" s="1">
-        <v>39.838535825227765</v>
+        <v>49.79816978153471</v>
       </c>
       <c r="Z28" s="1">
-        <v>28.048205870530563</v>
+        <v>35.060257338163204</v>
       </c>
       <c r="AA28" s="1">
-        <v>32.64786294841344</v>
+        <v>40.809828685516798</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -13412,76 +13412,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>16.33707684023501</v>
+        <v>20.421346050293764</v>
       </c>
       <c r="E29" s="1">
-        <v>17.179174423756802</v>
+        <v>21.473968029696003</v>
       </c>
       <c r="F29" s="1">
-        <v>13.947201059291137</v>
+        <v>17.434001324113922</v>
       </c>
       <c r="G29" s="1">
-        <v>14.592431908454396</v>
+        <v>18.240539885567994</v>
       </c>
       <c r="H29" s="1">
-        <v>11.613920468926464</v>
+        <v>14.517400586158081</v>
       </c>
       <c r="I29" s="1">
-        <v>10.057498751139841</v>
+        <v>12.571873438924801</v>
       </c>
       <c r="J29" s="1">
-        <v>11.479538195693566</v>
+        <v>14.349422744616957</v>
       </c>
       <c r="K29" s="1">
-        <v>2.1563050740940803</v>
+        <v>2.6953813426176003</v>
       </c>
       <c r="L29" s="1">
-        <v>1.7533501440000003</v>
+        <v>2.1916876800000002</v>
       </c>
       <c r="M29" s="1">
-        <v>2.5512304272998403</v>
+        <v>3.1890380341248004</v>
       </c>
       <c r="N29" s="1">
-        <v>1.5181029123686394</v>
+        <v>1.8976286404607992</v>
       </c>
       <c r="O29" s="1">
-        <v>1.80418050588672</v>
+        <v>2.2552256323584001</v>
       </c>
       <c r="P29" s="1">
-        <v>3.4062776952422404</v>
+        <v>4.2578471190528004</v>
       </c>
       <c r="Q29" s="1">
-        <v>5.299305804988415</v>
+        <v>6.6241322562355185</v>
       </c>
       <c r="R29" s="1">
-        <v>5.9998840396185598</v>
+        <v>7.4998550495231999</v>
       </c>
       <c r="S29" s="1">
-        <v>5.5050737025023997</v>
+        <v>6.8813421281279998</v>
       </c>
       <c r="T29" s="1">
-        <v>3.1425949900800005</v>
+        <v>3.9282437376000008</v>
       </c>
       <c r="U29" s="1">
-        <v>6.5421124892098534</v>
+        <v>8.1776406115123166</v>
       </c>
       <c r="V29" s="1">
-        <v>4.3305791245516794</v>
+        <v>5.4132239056895992</v>
       </c>
       <c r="W29" s="1">
-        <v>2.9259496418181121</v>
+        <v>3.6574370522726403</v>
       </c>
       <c r="X29" s="1">
-        <v>4.232153766297599</v>
+        <v>5.290192207871999</v>
       </c>
       <c r="Y29" s="1">
-        <v>2.4611024535552</v>
+        <v>3.0763780669439997</v>
       </c>
       <c r="Z29" s="1">
-        <v>11.350074202521599</v>
+        <v>14.187592753151998</v>
       </c>
       <c r="AA29" s="1">
-        <v>14.100059627716609</v>
+        <v>17.625074534645762</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -13495,76 +13495,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-37.995521900543984</v>
+        <v>-47.494402375679982</v>
       </c>
       <c r="E30" s="1">
-        <v>-39.802117812387841</v>
+        <v>-49.752647265484804</v>
       </c>
       <c r="F30" s="1">
-        <v>-37.722119788953606</v>
+        <v>-47.152649736192004</v>
       </c>
       <c r="G30" s="1">
-        <v>-47.852176659775466</v>
+        <v>-59.815220824719333</v>
       </c>
       <c r="H30" s="1">
-        <v>-44.418542799421438</v>
+        <v>-55.523178499276796</v>
       </c>
       <c r="I30" s="1">
-        <v>-56.383174508543981</v>
+        <v>-70.478968135679978</v>
       </c>
       <c r="J30" s="1">
-        <v>-52.112138081402883</v>
+        <v>-65.140172601753605</v>
       </c>
       <c r="K30" s="1">
-        <v>-58.539306306148745</v>
+        <v>-73.174132882685939</v>
       </c>
       <c r="L30" s="1">
-        <v>-46.089795589373949</v>
+        <v>-57.612244486717437</v>
       </c>
       <c r="M30" s="1">
-        <v>-75.608132065689603</v>
+        <v>-94.510165082111996</v>
       </c>
       <c r="N30" s="1">
-        <v>-74.880527387276089</v>
+        <v>-93.600659234095104</v>
       </c>
       <c r="O30" s="1">
-        <v>-67.794081893607014</v>
+        <v>-84.742602367008772</v>
       </c>
       <c r="P30" s="1">
-        <v>-64.986241424189032</v>
+        <v>-81.232801780236287</v>
       </c>
       <c r="Q30" s="1">
-        <v>-67.297607385926867</v>
+        <v>-84.122009232408587</v>
       </c>
       <c r="R30" s="1">
-        <v>-57.991726307829367</v>
+        <v>-72.489657884786709</v>
       </c>
       <c r="S30" s="1">
-        <v>-62.417427552829423</v>
+        <v>-78.021784441036772</v>
       </c>
       <c r="T30" s="1">
-        <v>-49.803867156853563</v>
+        <v>-62.254833946066952</v>
       </c>
       <c r="U30" s="1">
-        <v>-44.105275023753222</v>
+        <v>-55.131593779691528</v>
       </c>
       <c r="V30" s="1">
-        <v>-28.289608042571363</v>
+        <v>-35.362010053214206</v>
       </c>
       <c r="W30" s="1">
-        <v>-31.990111857947454</v>
+        <v>-39.987639822434318</v>
       </c>
       <c r="X30" s="1">
-        <v>-35.572225867775991</v>
+        <v>-44.465282334719987</v>
       </c>
       <c r="Y30" s="1">
-        <v>-34.829458900254714</v>
+        <v>-43.536823625318391</v>
       </c>
       <c r="Z30" s="1">
-        <v>-31.555486246502394</v>
+        <v>-39.44435780812799</v>
       </c>
       <c r="AA30" s="1">
-        <v>-30.964468625965043</v>
+        <v>-38.705585782456303</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -13578,76 +13578,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>32.453163283267578</v>
+        <v>40.566454104084471</v>
       </c>
       <c r="E31" s="1">
-        <v>35.793709053876633</v>
+        <v>44.742136317345789</v>
       </c>
       <c r="F31" s="1">
-        <v>40.070064137306105</v>
+        <v>50.087580171632631</v>
       </c>
       <c r="G31" s="1">
-        <v>47.644754380554254</v>
+        <v>59.555942975692815</v>
       </c>
       <c r="H31" s="1">
-        <v>45.975327824904184</v>
+        <v>57.46915978113023</v>
       </c>
       <c r="I31" s="1">
-        <v>56.5271480696832</v>
+        <v>70.658935087103998</v>
       </c>
       <c r="J31" s="1">
-        <v>51.325164453888</v>
+        <v>64.156455567359998</v>
       </c>
       <c r="K31" s="1">
-        <v>51.347248077864968</v>
+        <v>64.184060097331212</v>
       </c>
       <c r="L31" s="1">
-        <v>52.948933495750659</v>
+        <v>66.186166869688321</v>
       </c>
       <c r="M31" s="1">
-        <v>54.702876825452535</v>
+        <v>68.378596031815675</v>
       </c>
       <c r="N31" s="1">
-        <v>63.431710330060788</v>
+        <v>79.289637912575984</v>
       </c>
       <c r="O31" s="1">
-        <v>55.906927364800517</v>
+        <v>69.883659206000644</v>
       </c>
       <c r="P31" s="1">
-        <v>55.148078245478395</v>
+        <v>68.935097806847992</v>
       </c>
       <c r="Q31" s="1">
-        <v>51.085976496242687</v>
+        <v>63.85747062030336</v>
       </c>
       <c r="R31" s="1">
-        <v>47.376848069591034</v>
+        <v>59.221060086988793</v>
       </c>
       <c r="S31" s="1">
-        <v>44.028167926579194</v>
+        <v>55.03520990822399</v>
       </c>
       <c r="T31" s="1">
-        <v>42.321549125438672</v>
+        <v>52.901936406798342</v>
       </c>
       <c r="U31" s="1">
-        <v>35.240433455569303</v>
+        <v>44.050541819461628</v>
       </c>
       <c r="V31" s="1">
-        <v>26.232732128378881</v>
+        <v>32.790915160473602</v>
       </c>
       <c r="W31" s="1">
-        <v>34.456432685875193</v>
+        <v>43.070540857343993</v>
       </c>
       <c r="X31" s="1">
-        <v>36.258423983308795</v>
+        <v>45.323029979135995</v>
       </c>
       <c r="Y31" s="1">
-        <v>35.691013187960827</v>
+        <v>44.613766484951036</v>
       </c>
       <c r="Z31" s="1">
-        <v>30.087768917606397</v>
+        <v>37.609711147007999</v>
       </c>
       <c r="AA31" s="1">
-        <v>28.678322493849596</v>
+        <v>35.847903117311994</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -13661,76 +13661,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>16.471035046055118</v>
+        <v>20.588793807568898</v>
       </c>
       <c r="E32" s="1">
-        <v>16.550893839136851</v>
+        <v>20.688617298921063</v>
       </c>
       <c r="F32" s="1">
-        <v>15.570386636653858</v>
+        <v>19.462983295817324</v>
       </c>
       <c r="G32" s="1">
-        <v>13.750074808152883</v>
+        <v>17.187593510191103</v>
       </c>
       <c r="H32" s="1">
-        <v>11.146068335001601</v>
+        <v>13.932585418752002</v>
       </c>
       <c r="I32" s="1">
-        <v>9.1906381444939758</v>
+        <v>11.488297680617469</v>
       </c>
       <c r="J32" s="1">
-        <v>10.909039933846978</v>
+        <v>13.636299917308722</v>
       </c>
       <c r="K32" s="1">
-        <v>2.0091192016896007</v>
+        <v>2.5113990021120007</v>
       </c>
       <c r="L32" s="1">
-        <v>1.9152106625433607</v>
+        <v>2.3940133281792009</v>
       </c>
       <c r="M32" s="1">
-        <v>2.527189986734899</v>
+        <v>3.158987483418624</v>
       </c>
       <c r="N32" s="1">
-        <v>1.4451612844032</v>
+        <v>1.8064516055040001</v>
       </c>
       <c r="O32" s="1">
-        <v>1.9349370930659333</v>
+        <v>2.4186713663324166</v>
       </c>
       <c r="P32" s="1">
-        <v>2.8433216814612483</v>
+        <v>3.5541521018265603</v>
       </c>
       <c r="Q32" s="1">
-        <v>5.243635237115658</v>
+        <v>6.5545440463945726</v>
       </c>
       <c r="R32" s="1">
-        <v>5.5877389497925627</v>
+        <v>6.9846736872407034</v>
       </c>
       <c r="S32" s="1">
-        <v>5.7895490954959259</v>
+        <v>7.2369363693699071</v>
       </c>
       <c r="T32" s="1">
-        <v>3.551386532069376</v>
+        <v>4.4392331650867201</v>
       </c>
       <c r="U32" s="1">
-        <v>6.2911873533306455</v>
+        <v>7.8639841916633069</v>
       </c>
       <c r="V32" s="1">
-        <v>3.5087381016713621</v>
+        <v>4.3859226270892027</v>
       </c>
       <c r="W32" s="1">
-        <v>2.7281753121728105</v>
+        <v>3.4102191402160131</v>
       </c>
       <c r="X32" s="1">
-        <v>4.303057896603649</v>
+        <v>5.3788223707545608</v>
       </c>
       <c r="Y32" s="1">
-        <v>2.5615556149248002</v>
+        <v>3.201944518656</v>
       </c>
       <c r="Z32" s="1">
-        <v>11.236573460496382</v>
+        <v>14.045716825620477</v>
       </c>
       <c r="AA32" s="1">
-        <v>15.09481905899176</v>
+        <v>18.8685238237397</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -13744,76 +13744,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-32.597611038719997</v>
+        <v>-40.747013798399998</v>
       </c>
       <c r="E33" s="1">
-        <v>-35.622360742625283</v>
+        <v>-44.527950928281605</v>
       </c>
       <c r="F33" s="1">
-        <v>-45.247948185403395</v>
+        <v>-56.559935231754245</v>
       </c>
       <c r="G33" s="1">
-        <v>-43.676315190647195</v>
+        <v>-54.595393988308992</v>
       </c>
       <c r="H33" s="1">
-        <v>-49.627418308116482</v>
+        <v>-62.034272885145604</v>
       </c>
       <c r="I33" s="1">
-        <v>-54.691679273287683</v>
+        <v>-68.364599091609605</v>
       </c>
       <c r="J33" s="1">
-        <v>-54.875980222562312</v>
+        <v>-68.594975278202895</v>
       </c>
       <c r="K33" s="1">
-        <v>-61.45457044658059</v>
+        <v>-76.818213058225737</v>
       </c>
       <c r="L33" s="1">
-        <v>-52.009602195550372</v>
+        <v>-65.012002744437964</v>
       </c>
       <c r="M33" s="1">
-        <v>-72.564177748775748</v>
+        <v>-90.705222185969689</v>
       </c>
       <c r="N33" s="1">
-        <v>-71.235511182950404</v>
+        <v>-89.044388978688005</v>
       </c>
       <c r="O33" s="1">
-        <v>-71.870570133706522</v>
+        <v>-89.838212667133149</v>
       </c>
       <c r="P33" s="1">
-        <v>-61.137541689358414</v>
+        <v>-76.421927111698011</v>
       </c>
       <c r="Q33" s="1">
-        <v>-63.909196384677415</v>
+        <v>-79.886495480846776</v>
       </c>
       <c r="R33" s="1">
-        <v>-59.043990810242576</v>
+        <v>-73.80498851280322</v>
       </c>
       <c r="S33" s="1">
-        <v>-58.267577612229672</v>
+        <v>-72.834472015287091</v>
       </c>
       <c r="T33" s="1">
-        <v>-55.55186201925256</v>
+        <v>-69.439827524065706</v>
       </c>
       <c r="U33" s="1">
-        <v>-52.777006906189293</v>
+        <v>-65.971258632736621</v>
       </c>
       <c r="V33" s="1">
-        <v>-25.573227747666493</v>
+        <v>-31.966534684583117</v>
       </c>
       <c r="W33" s="1">
-        <v>-32.265200198473472</v>
+        <v>-40.331500248091842</v>
       </c>
       <c r="X33" s="1">
-        <v>-33.831880619301266</v>
+        <v>-42.289850774126585</v>
       </c>
       <c r="Y33" s="1">
-        <v>-37.792717050243311</v>
+        <v>-47.240896312804139</v>
       </c>
       <c r="Z33" s="1">
-        <v>-29.11094706341413</v>
+        <v>-36.388683829267663</v>
       </c>
       <c r="AA33" s="1">
-        <v>-31.223945972385053</v>
+        <v>-39.029932465481316</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -13827,76 +13827,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>31.797543822999558</v>
+        <v>39.746929778749447</v>
       </c>
       <c r="E34" s="1">
-        <v>40.288273975927112</v>
+        <v>50.360342469908886</v>
       </c>
       <c r="F34" s="1">
-        <v>44.747314665086002</v>
+        <v>55.934143331357504</v>
       </c>
       <c r="G34" s="1">
-        <v>46.301107484227543</v>
+        <v>57.876384355284429</v>
       </c>
       <c r="H34" s="1">
-        <v>41.977140670743175</v>
+        <v>52.471425838428971</v>
       </c>
       <c r="I34" s="1">
-        <v>56.498791216526122</v>
+        <v>70.623489020657658</v>
       </c>
       <c r="J34" s="1">
-        <v>54.984801130433731</v>
+        <v>68.731001413042165</v>
       </c>
       <c r="K34" s="1">
-        <v>52.25293810114561</v>
+        <v>65.316172626432007</v>
       </c>
       <c r="L34" s="1">
-        <v>47.399477965907558</v>
+        <v>59.249347457384445</v>
       </c>
       <c r="M34" s="1">
-        <v>55.268857331309356</v>
+        <v>69.086071664136696</v>
       </c>
       <c r="N34" s="1">
-        <v>61.465327309828901</v>
+        <v>76.831659137286124</v>
       </c>
       <c r="O34" s="1">
-        <v>58.772614148189064</v>
+        <v>73.465767685236329</v>
       </c>
       <c r="P34" s="1">
-        <v>48.42897233128982</v>
+        <v>60.536215414112277</v>
       </c>
       <c r="Q34" s="1">
-        <v>52.159398359843749</v>
+        <v>65.199247949804686</v>
       </c>
       <c r="R34" s="1">
-        <v>47.406770289424458</v>
+        <v>59.258462861780572</v>
       </c>
       <c r="S34" s="1">
-        <v>45.38500424450703</v>
+        <v>56.731255305633788</v>
       </c>
       <c r="T34" s="1">
-        <v>43.513492933249587</v>
+        <v>54.391866166561982</v>
       </c>
       <c r="U34" s="1">
-        <v>39.727822379837029</v>
+        <v>49.659777974796285</v>
       </c>
       <c r="V34" s="1">
-        <v>26.213877352161607</v>
+        <v>32.767346690202011</v>
       </c>
       <c r="W34" s="1">
-        <v>29.065638248460584</v>
+        <v>36.33204781057573</v>
       </c>
       <c r="X34" s="1">
-        <v>32.779272808864675</v>
+        <v>40.974091011080844</v>
       </c>
       <c r="Y34" s="1">
-        <v>37.12707348182493</v>
+        <v>46.408841852281164</v>
       </c>
       <c r="Z34" s="1">
-        <v>27.767723811825253</v>
+        <v>34.709654764781568</v>
       </c>
       <c r="AA34" s="1">
-        <v>28.913832354329401</v>
+        <v>36.142290442911751</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -13910,76 +13910,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>16.820587012032512</v>
+        <v>21.025733765040641</v>
       </c>
       <c r="E35" s="1">
-        <v>18.071804326815201</v>
+        <v>22.589755408519</v>
       </c>
       <c r="F35" s="1">
-        <v>14.504646580455699</v>
+        <v>18.130808225569623</v>
       </c>
       <c r="G35" s="1">
-        <v>14.90164357333569</v>
+        <v>18.627054466669613</v>
       </c>
       <c r="H35" s="1">
-        <v>11.724561014291693</v>
+        <v>14.655701267864616</v>
       </c>
       <c r="I35" s="1">
-        <v>9.5600835986191814</v>
+        <v>11.950104498273976</v>
       </c>
       <c r="J35" s="1">
-        <v>12.177494117991737</v>
+        <v>15.22186764748967</v>
       </c>
       <c r="K35" s="1">
-        <v>1.8570183038101096</v>
+        <v>2.321272879762637</v>
       </c>
       <c r="L35" s="1">
-        <v>1.8941429582659586</v>
+        <v>2.3676786978324484</v>
       </c>
       <c r="M35" s="1">
-        <v>2.4003950238829117</v>
+        <v>3.0004937798536395</v>
       </c>
       <c r="N35" s="1">
-        <v>1.3726488717969854</v>
+        <v>1.7158110897462318</v>
       </c>
       <c r="O35" s="1">
-        <v>1.8025567434314222</v>
+        <v>2.2531959292892778</v>
       </c>
       <c r="P35" s="1">
-        <v>2.7842583112581121</v>
+        <v>3.4803228890726401</v>
       </c>
       <c r="Q35" s="1">
-        <v>5.9697881797603882</v>
+        <v>7.4622352247004855</v>
       </c>
       <c r="R35" s="1">
-        <v>6.961619012438458</v>
+        <v>8.7020237655480734</v>
       </c>
       <c r="S35" s="1">
-        <v>5.9621916829483013</v>
+        <v>7.4527396036853766</v>
       </c>
       <c r="T35" s="1">
-        <v>3.1177188697374731</v>
+        <v>3.8971485871718414</v>
       </c>
       <c r="U35" s="1">
-        <v>6.6836485767167986</v>
+        <v>8.3545607208959982</v>
       </c>
       <c r="V35" s="1">
-        <v>4.1166334422977338</v>
+        <v>5.145791802872167</v>
       </c>
       <c r="W35" s="1">
-        <v>2.839858197037056</v>
+        <v>3.5498227462963201</v>
       </c>
       <c r="X35" s="1">
-        <v>3.9367091358906969</v>
+        <v>4.9208864198633711</v>
       </c>
       <c r="Y35" s="1">
-        <v>2.5608022162145279</v>
+        <v>3.2010027702681598</v>
       </c>
       <c r="Z35" s="1">
-        <v>12.285876238811134</v>
+        <v>15.357345298513918</v>
       </c>
       <c r="AA35" s="1">
-        <v>14.229434868708879</v>
+        <v>17.786793585886098</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -13993,76 +13993,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-37.534217011199992</v>
+        <v>-46.917771263999988</v>
       </c>
       <c r="E36" s="1">
-        <v>-39.379727990705355</v>
+        <v>-49.224659988381696</v>
       </c>
       <c r="F36" s="1">
-        <v>-44.741171165726882</v>
+        <v>-55.926463957158603</v>
       </c>
       <c r="G36" s="1">
-        <v>-42.81198390055858</v>
+        <v>-53.514979875698224</v>
       </c>
       <c r="H36" s="1">
-        <v>-49.612822008614081</v>
+        <v>-62.0160275107676</v>
       </c>
       <c r="I36" s="1">
-        <v>-53.029052223379722</v>
+        <v>-66.286315279224652</v>
       </c>
       <c r="J36" s="1">
-        <v>-54.777949345271509</v>
+        <v>-68.472436681589386</v>
       </c>
       <c r="K36" s="1">
-        <v>-55.541719385677908</v>
+        <v>-69.427149232097378</v>
       </c>
       <c r="L36" s="1">
-        <v>-55.150574249713031</v>
+        <v>-68.938217812141289</v>
       </c>
       <c r="M36" s="1">
-        <v>-66.952280466403082</v>
+        <v>-83.690350583003848</v>
       </c>
       <c r="N36" s="1">
-        <v>-67.632721238576337</v>
+        <v>-84.540901548220418</v>
       </c>
       <c r="O36" s="1">
-        <v>-58.652227363779389</v>
+        <v>-73.315284204724236</v>
       </c>
       <c r="P36" s="1">
-        <v>-66.91680176736368</v>
+        <v>-83.646002209204596</v>
       </c>
       <c r="Q36" s="1">
-        <v>-60.172746113134004</v>
+        <v>-75.21593264141751</v>
       </c>
       <c r="R36" s="1">
-        <v>-60.249218663894986</v>
+        <v>-75.311523329868734</v>
       </c>
       <c r="S36" s="1">
-        <v>-53.788788446788168</v>
+        <v>-67.235985558485211</v>
       </c>
       <c r="T36" s="1">
-        <v>-58.917974846557769</v>
+        <v>-73.647468558197204</v>
       </c>
       <c r="U36" s="1">
-        <v>-51.174394711370844</v>
+        <v>-63.967993389213554</v>
       </c>
       <c r="V36" s="1">
-        <v>-29.11579277039586</v>
+        <v>-36.394740962994824</v>
       </c>
       <c r="W36" s="1">
-        <v>-35.269098323387048</v>
+        <v>-44.086372904233812</v>
       </c>
       <c r="X36" s="1">
-        <v>-29.925416998862882</v>
+        <v>-37.4067712485786</v>
       </c>
       <c r="Y36" s="1">
-        <v>-38.510382767186897</v>
+        <v>-48.137978458983625</v>
       </c>
       <c r="Z36" s="1">
-        <v>-29.974714162983862</v>
+        <v>-37.468392703729826</v>
       </c>
       <c r="AA36" s="1">
-        <v>-33.192045259354273</v>
+        <v>-41.490056574192842</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -14076,76 +14076,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>29.634560560188106</v>
+        <v>37.043200700235133</v>
       </c>
       <c r="E37" s="1">
-        <v>36.808947206657898</v>
+        <v>46.011184008322374</v>
       </c>
       <c r="F37" s="1">
-        <v>40.857806616443519</v>
+        <v>51.0722582705544</v>
       </c>
       <c r="G37" s="1">
-        <v>43.594716662430017</v>
+        <v>54.493395828037521</v>
       </c>
       <c r="H37" s="1">
-        <v>46.825871389664911</v>
+        <v>58.532339237081139</v>
       </c>
       <c r="I37" s="1">
-        <v>50.1215780002427</v>
+        <v>62.651972500303373</v>
       </c>
       <c r="J37" s="1">
-        <v>54.387864059337772</v>
+        <v>67.984830074172208</v>
       </c>
       <c r="K37" s="1">
-        <v>53.822506355518534</v>
+        <v>67.278132944398166</v>
       </c>
       <c r="L37" s="1">
-        <v>42.845584060445752</v>
+        <v>53.556980075557192</v>
       </c>
       <c r="M37" s="1">
-        <v>55.33460141219512</v>
+        <v>69.168251765243895</v>
       </c>
       <c r="N37" s="1">
-        <v>63.309287129123788</v>
+        <v>79.136608911404736</v>
       </c>
       <c r="O37" s="1">
-        <v>61.206451499095401</v>
+        <v>76.508064373869246</v>
       </c>
       <c r="P37" s="1">
-        <v>56.167622549176322</v>
+        <v>70.209528186470408</v>
       </c>
       <c r="Q37" s="1">
-        <v>55.849876741089155</v>
+        <v>69.812345926361445</v>
       </c>
       <c r="R37" s="1">
-        <v>47.339138012743717</v>
+        <v>59.173922515929647</v>
       </c>
       <c r="S37" s="1">
-        <v>37.887130385708822</v>
+        <v>47.358912982136026</v>
       </c>
       <c r="T37" s="1">
-        <v>41.017703420058979</v>
+        <v>51.272129275073723</v>
       </c>
       <c r="U37" s="1">
-        <v>38.558907605968734</v>
+        <v>48.198634507460916</v>
       </c>
       <c r="V37" s="1">
-        <v>30.146655761932994</v>
+        <v>37.683319702416242</v>
       </c>
       <c r="W37" s="1">
-        <v>31.456574031295563</v>
+        <v>39.320717539119457</v>
       </c>
       <c r="X37" s="1">
-        <v>38.451623533211183</v>
+        <v>48.064529416513977</v>
       </c>
       <c r="Y37" s="1">
-        <v>39.009894280063023</v>
+        <v>48.762367850078775</v>
       </c>
       <c r="Z37" s="1">
-        <v>26.387752082995149</v>
+        <v>32.984690103743937</v>
       </c>
       <c r="AA37" s="1">
-        <v>32.282206883391211</v>
+        <v>40.352758604239014</v>
       </c>
     </row>
   </sheetData>
